--- a/input/time_series_factor.xlsx
+++ b/input/time_series_factor.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patryk\git\SimPaths_HU\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFB8280C-38DD-47FF-844F-C72275152563}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8317AE17-CD2D-4440-8E45-7FFD18CE5464}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-83" yWindow="0" windowWidth="14566" windowHeight="17363" tabRatio="973" firstSheet="9" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" tabRatio="973" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="PL_disability_adjustment" sheetId="25" r:id="rId1"/>
-    <sheet name="Info" sheetId="1" r:id="rId2"/>
+    <sheet name="Info" sheetId="1" r:id="rId1"/>
+    <sheet name="IT_disability_adjustment" sheetId="25" r:id="rId2"/>
     <sheet name="IT_students_adjustment" sheetId="24" r:id="rId3"/>
     <sheet name="IT_retirement_adjustment" sheetId="23" r:id="rId4"/>
     <sheet name="IT_cohabitation_adjustment" sheetId="15" r:id="rId5"/>
@@ -893,504 +893,52 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8855BE1A-8357-468E-B95E-E2868B6CF276}">
-  <dimension ref="A1:B62"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="12.59765625" customWidth="1"/>
+    <col min="2" max="2" width="10.73046875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A2">
-        <v>2010</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A3">
-        <v>2011</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A4">
-        <v>2012</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A5">
-        <v>2013</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A6">
-        <v>2014</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A7">
-        <v>2015</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A8">
-        <v>2016</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A9">
-        <v>2017</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A10">
-        <v>2018</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A11">
-        <v>2019</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A12">
-        <v>2020</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A13">
-        <v>2021</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A14">
-        <v>2022</v>
-      </c>
-      <c r="B14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A15">
-        <v>2023</v>
-      </c>
-      <c r="B15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A16">
-        <v>2024</v>
-      </c>
-      <c r="B16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A17">
-        <v>2025</v>
-      </c>
-      <c r="B17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A18">
-        <v>2026</v>
-      </c>
-      <c r="B18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A19">
-        <v>2027</v>
-      </c>
-      <c r="B19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A20">
-        <v>2028</v>
-      </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A21">
-        <v>2029</v>
-      </c>
-      <c r="B21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A22">
-        <v>2030</v>
-      </c>
-      <c r="B22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A23">
-        <v>2031</v>
-      </c>
-      <c r="B23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A24">
-        <v>2032</v>
-      </c>
-      <c r="B24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A25">
-        <v>2033</v>
-      </c>
-      <c r="B25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A26">
-        <v>2034</v>
-      </c>
-      <c r="B26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A27">
-        <v>2035</v>
-      </c>
-      <c r="B27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A28">
-        <v>2036</v>
-      </c>
-      <c r="B28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A29">
-        <v>2037</v>
-      </c>
-      <c r="B29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A30">
-        <v>2038</v>
-      </c>
-      <c r="B30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A31">
-        <v>2039</v>
-      </c>
-      <c r="B31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A32">
-        <v>2040</v>
-      </c>
-      <c r="B32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A33">
-        <v>2041</v>
-      </c>
-      <c r="B33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A34">
-        <v>2042</v>
-      </c>
-      <c r="B34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A35">
-        <v>2043</v>
-      </c>
-      <c r="B35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A36">
-        <v>2044</v>
-      </c>
-      <c r="B36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A37">
-        <v>2045</v>
-      </c>
-      <c r="B37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A38">
-        <v>2046</v>
-      </c>
-      <c r="B38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A39">
-        <v>2047</v>
-      </c>
-      <c r="B39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A40">
-        <v>2048</v>
-      </c>
-      <c r="B40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A41">
-        <v>2049</v>
-      </c>
-      <c r="B41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A42">
-        <v>2050</v>
-      </c>
-      <c r="B42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A43">
-        <v>2051</v>
-      </c>
-      <c r="B43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A44">
-        <v>2052</v>
-      </c>
-      <c r="B44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A45">
-        <v>2053</v>
-      </c>
-      <c r="B45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A46">
-        <v>2054</v>
-      </c>
-      <c r="B46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A47">
-        <v>2055</v>
-      </c>
-      <c r="B47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A48">
-        <v>2056</v>
-      </c>
-      <c r="B48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A49">
-        <v>2057</v>
-      </c>
-      <c r="B49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A50">
-        <v>2058</v>
-      </c>
-      <c r="B50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A51">
-        <v>2059</v>
-      </c>
-      <c r="B51">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A52">
-        <v>2060</v>
-      </c>
-      <c r="B52">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A53">
-        <v>2061</v>
-      </c>
-      <c r="B53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A54">
-        <v>2062</v>
-      </c>
-      <c r="B54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A55">
-        <v>2063</v>
-      </c>
-      <c r="B55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A56">
-        <v>2064</v>
-      </c>
-      <c r="B56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A57">
-        <v>2065</v>
-      </c>
-      <c r="B57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A58">
-        <v>2066</v>
-      </c>
-      <c r="B58">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A59">
-        <v>2067</v>
-      </c>
-      <c r="B59">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A60">
-        <v>2068</v>
-      </c>
-      <c r="B60">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A61">
-        <v>2069</v>
-      </c>
-      <c r="B61">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A62">
-        <v>2070</v>
-      </c>
-      <c r="B62">
-        <v>0</v>
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -2368,52 +1916,504 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8855BE1A-8357-468E-B95E-E2868B6CF276}">
+  <dimension ref="A1:B62"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="12.59765625" customWidth="1"/>
-    <col min="2" max="2" width="10.73046875" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
+      <c r="A2">
+        <v>2010</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
+      <c r="A3">
+        <v>2011</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
+      <c r="A4">
+        <v>2012</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A5">
+        <v>2013</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" t="s">
-        <v>10</v>
+      <c r="A6">
+        <v>2014</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A7">
+        <v>2015</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A8">
+        <v>2016</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A9">
+        <v>2017</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A10">
+        <v>2018</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A11">
+        <v>2019</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A12">
+        <v>2020</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A13">
+        <v>2021</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A14">
+        <v>2022</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A15">
+        <v>2023</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A16">
+        <v>2024</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A17">
+        <v>2025</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A18">
+        <v>2026</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A19">
+        <v>2027</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A20">
+        <v>2028</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A21">
+        <v>2029</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A22">
+        <v>2030</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A23">
+        <v>2031</v>
+      </c>
+      <c r="B23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A24">
+        <v>2032</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A25">
+        <v>2033</v>
+      </c>
+      <c r="B25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A26">
+        <v>2034</v>
+      </c>
+      <c r="B26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A27">
+        <v>2035</v>
+      </c>
+      <c r="B27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A28">
+        <v>2036</v>
+      </c>
+      <c r="B28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A29">
+        <v>2037</v>
+      </c>
+      <c r="B29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A30">
+        <v>2038</v>
+      </c>
+      <c r="B30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A31">
+        <v>2039</v>
+      </c>
+      <c r="B31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A32">
+        <v>2040</v>
+      </c>
+      <c r="B32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A33">
+        <v>2041</v>
+      </c>
+      <c r="B33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A34">
+        <v>2042</v>
+      </c>
+      <c r="B34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A35">
+        <v>2043</v>
+      </c>
+      <c r="B35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A36">
+        <v>2044</v>
+      </c>
+      <c r="B36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A37">
+        <v>2045</v>
+      </c>
+      <c r="B37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A38">
+        <v>2046</v>
+      </c>
+      <c r="B38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A39">
+        <v>2047</v>
+      </c>
+      <c r="B39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A40">
+        <v>2048</v>
+      </c>
+      <c r="B40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A41">
+        <v>2049</v>
+      </c>
+      <c r="B41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A42">
+        <v>2050</v>
+      </c>
+      <c r="B42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A43">
+        <v>2051</v>
+      </c>
+      <c r="B43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A44">
+        <v>2052</v>
+      </c>
+      <c r="B44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A45">
+        <v>2053</v>
+      </c>
+      <c r="B45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A46">
+        <v>2054</v>
+      </c>
+      <c r="B46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A47">
+        <v>2055</v>
+      </c>
+      <c r="B47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A48">
+        <v>2056</v>
+      </c>
+      <c r="B48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A49">
+        <v>2057</v>
+      </c>
+      <c r="B49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A50">
+        <v>2058</v>
+      </c>
+      <c r="B50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A51">
+        <v>2059</v>
+      </c>
+      <c r="B51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A52">
+        <v>2060</v>
+      </c>
+      <c r="B52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A53">
+        <v>2061</v>
+      </c>
+      <c r="B53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A54">
+        <v>2062</v>
+      </c>
+      <c r="B54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A55">
+        <v>2063</v>
+      </c>
+      <c r="B55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A56">
+        <v>2064</v>
+      </c>
+      <c r="B56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A57">
+        <v>2065</v>
+      </c>
+      <c r="B57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A58">
+        <v>2066</v>
+      </c>
+      <c r="B58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A59">
+        <v>2067</v>
+      </c>
+      <c r="B59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A60">
+        <v>2068</v>
+      </c>
+      <c r="B60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A61">
+        <v>2069</v>
+      </c>
+      <c r="B61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A62">
+        <v>2070</v>
+      </c>
+      <c r="B62">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/input/time_series_factor.xlsx
+++ b/input/time_series_factor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patryk\git\SimPaths_HU\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8317AE17-CD2D-4440-8E45-7FFD18CE5464}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F86CE648-DB9A-41CD-9228-83283CC4B545}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" tabRatio="973" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" tabRatio="973" firstSheet="6" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -23,9 +23,9 @@
     <sheet name="IT_utility_adj_sfemales" sheetId="17" r:id="rId8"/>
     <sheet name="IT_utility_adj_all" sheetId="26" r:id="rId9"/>
     <sheet name="IT_utility_adj_couples" sheetId="18" r:id="rId10"/>
-    <sheet name="IT_gdp" sheetId="20" r:id="rId11"/>
-    <sheet name="IT_inflation" sheetId="21" r:id="rId12"/>
-    <sheet name="IT_wage_growth" sheetId="22" r:id="rId13"/>
+    <sheet name="EL_gdp" sheetId="20" r:id="rId11"/>
+    <sheet name="EL_inflation" sheetId="21" r:id="rId12"/>
+    <sheet name="EL_wage_growth" sheetId="22" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -895,13 +895,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.59765625" customWidth="1"/>
-    <col min="2" max="2" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -909,7 +909,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -917,7 +917,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -925,7 +925,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -933,7 +933,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -949,9 +949,9 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83A8B1C6-B095-49F5-BE52-65A3AD804239}">
   <dimension ref="A1:B32"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -959,7 +959,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2010</v>
       </c>
@@ -967,7 +967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2011</v>
       </c>
@@ -975,7 +975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2012</v>
       </c>
@@ -983,7 +983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2013</v>
       </c>
@@ -991,7 +991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2014</v>
       </c>
@@ -999,7 +999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2015</v>
       </c>
@@ -1007,7 +1007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2016</v>
       </c>
@@ -1015,7 +1015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2017</v>
       </c>
@@ -1023,7 +1023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2018</v>
       </c>
@@ -1031,7 +1031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2019</v>
       </c>
@@ -1039,7 +1039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2020</v>
       </c>
@@ -1047,7 +1047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2021</v>
       </c>
@@ -1055,7 +1055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2022</v>
       </c>
@@ -1063,7 +1063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2023</v>
       </c>
@@ -1071,7 +1071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2024</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2025</v>
       </c>
@@ -1087,7 +1087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2026</v>
       </c>
@@ -1095,7 +1095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2027</v>
       </c>
@@ -1103,7 +1103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2028</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2029</v>
       </c>
@@ -1119,7 +1119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2030</v>
       </c>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2031</v>
       </c>
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2032</v>
       </c>
@@ -1143,7 +1143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2033</v>
       </c>
@@ -1151,7 +1151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2034</v>
       </c>
@@ -1159,7 +1159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2035</v>
       </c>
@@ -1167,7 +1167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2036</v>
       </c>
@@ -1175,7 +1175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>2037</v>
       </c>
@@ -1183,7 +1183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>2038</v>
       </c>
@@ -1191,7 +1191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>2039</v>
       </c>
@@ -1199,7 +1199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>2040</v>
       </c>
@@ -1215,9 +1215,9 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BB6812C-5BB0-43F7-B52C-EA13500B4AA8}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1225,260 +1225,260 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1995</v>
       </c>
-      <c r="B2">
-        <v>59.758000000000003</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B2" s="1">
+        <v>68.367999999999995</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1996</v>
       </c>
-      <c r="B3">
-        <v>67.820999999999998</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B3" s="1">
+        <v>73.352999999999994</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1997</v>
       </c>
-      <c r="B4">
-        <v>70.616</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B4" s="1">
+        <v>77.245000000000005</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1998</v>
       </c>
-      <c r="B5">
-        <v>71.754999999999995</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B5" s="1">
+        <v>76.066000000000003</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1999</v>
       </c>
-      <c r="B6">
-        <v>73.091999999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B6" s="1">
+        <v>79.936999999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2000</v>
       </c>
-      <c r="B7">
-        <v>74.376000000000005</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B7" s="1">
+        <v>78.608000000000004</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2001</v>
       </c>
-      <c r="B8">
-        <v>76.655000000000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B8" s="1">
+        <v>80.352999999999994</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2002</v>
       </c>
-      <c r="B9">
-        <v>79.188000000000002</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B9" s="1">
+        <v>82.727000000000004</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2003</v>
       </c>
-      <c r="B10">
-        <v>81.695999999999998</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B10" s="1">
+        <v>85.67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2004</v>
       </c>
-      <c r="B11">
-        <v>83.844999999999999</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B11" s="1">
+        <v>88.213999999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2005</v>
       </c>
-      <c r="B12">
-        <v>85.591999999999999</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B12" s="1">
+        <v>89.89</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2006</v>
       </c>
-      <c r="B13">
-        <v>87.489000000000004</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B13" s="1">
+        <v>92.915000000000006</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2007</v>
       </c>
-      <c r="B14">
-        <v>89.647000000000006</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B14" s="1">
+        <v>96.043000000000006</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2008</v>
       </c>
-      <c r="B15">
-        <v>91.802999999999997</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B15" s="1">
+        <v>99.944999999999993</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2009</v>
       </c>
-      <c r="B16">
-        <v>93.43</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B16" s="1">
+        <v>102.312</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2010</v>
       </c>
-      <c r="B17">
-        <v>93.988</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B17" s="1">
+        <v>103.521</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2011</v>
       </c>
-      <c r="B18">
-        <v>95.613</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B18" s="1">
+        <v>104.532</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2012</v>
       </c>
-      <c r="B19">
-        <v>97.241</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B19" s="1">
+        <v>104.182</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2013</v>
       </c>
-      <c r="B20">
-        <v>98.335999999999999</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B20" s="1">
+        <v>102.14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2014</v>
       </c>
-      <c r="B21">
-        <v>99.222999999999999</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B21" s="1">
+        <v>100.175</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2015</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2016</v>
       </c>
-      <c r="B23">
-        <v>101.248</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B23" s="1">
+        <v>99.51</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2017</v>
       </c>
-      <c r="B24">
-        <v>101.967</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B24" s="1">
+        <v>99.712999999999994</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2018</v>
       </c>
-      <c r="B25">
-        <v>103.05800000000001</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B25" s="1">
+        <v>99.478999999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2019</v>
       </c>
-      <c r="B26">
-        <v>104.13800000000001</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B26" s="1">
+        <v>99.721999999999994</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2020</v>
       </c>
-      <c r="B27">
-        <v>105.78</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B27" s="1">
+        <v>99.358999999999995</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2021</v>
       </c>
-      <c r="B28">
-        <v>107.13800000000001</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B28" s="1">
+        <v>100.74299999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>2022</v>
       </c>
-      <c r="B29">
-        <v>110.952</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B29" s="1">
+        <v>107.28700000000001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>2023</v>
       </c>
-      <c r="B30">
-        <v>117.408</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B30" s="1">
+        <v>113.59</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>2024</v>
       </c>
-      <c r="B31">
-        <v>118.22985599999998</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B31" s="1">
+        <v>117.17100000000001</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>2025</v>
       </c>
-      <c r="B32">
-        <v>119.41215455999999</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B32" s="1">
+        <v>119.865933</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>2026</v>
       </c>
-      <c r="B33">
-        <v>120.84510041471999</v>
+      <c r="B33" s="1">
+        <v>122.50298352599999</v>
       </c>
     </row>
   </sheetData>
@@ -1488,10 +1488,10 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0E899AF-6766-40B7-B849-58604785D824}">
-  <dimension ref="A1:B26"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:B28"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1499,204 +1499,220 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
+        <v>2000</v>
+      </c>
+      <c r="B2">
+        <v>71.010000000000005</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3">
         <v>2001</v>
       </c>
-      <c r="B2" s="1">
-        <v>75.900000000000006</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A3">
+      <c r="B3">
+        <v>73.59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4">
         <v>2002</v>
       </c>
-      <c r="B3" s="1">
-        <v>77.900000000000006</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A4">
+      <c r="B4">
+        <v>76.48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5">
         <v>2003</v>
       </c>
-      <c r="B4" s="1">
-        <v>80.099999999999994</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A5">
+      <c r="B5">
+        <v>79.12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6">
         <v>2004</v>
       </c>
-      <c r="B5" s="1">
-        <v>81.900000000000006</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A6">
+      <c r="B6">
+        <v>81.510000000000005</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7">
         <v>2005</v>
       </c>
-      <c r="B6" s="1">
-        <v>83.7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A7">
+      <c r="B7">
+        <v>84.35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8">
         <v>2006</v>
       </c>
-      <c r="B7" s="1">
-        <v>85.6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A8">
+      <c r="B8">
+        <v>87.14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9">
         <v>2007</v>
       </c>
-      <c r="B8" s="1">
-        <v>87.3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A9">
+      <c r="B9">
+        <v>89.75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10">
         <v>2008</v>
       </c>
-      <c r="B9" s="1">
-        <v>90.4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A10">
+      <c r="B10">
+        <v>93.55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11">
         <v>2009</v>
       </c>
-      <c r="B10" s="1">
-        <v>91.1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A11">
+      <c r="B11">
+        <v>94.81</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12">
         <v>2010</v>
       </c>
-      <c r="B11" s="1">
-        <v>92.6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A12">
+      <c r="B12">
+        <v>99.27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13">
         <v>2011</v>
       </c>
-      <c r="B12" s="1">
-        <v>95.3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A13">
+      <c r="B13">
+        <v>102.36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14">
         <v>2012</v>
       </c>
-      <c r="B13" s="1">
-        <v>98.4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A14">
+      <c r="B14">
+        <v>103.42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15">
         <v>2013</v>
       </c>
-      <c r="B14" s="1">
-        <v>99.7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A15">
+      <c r="B15">
+        <v>102.54</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16">
         <v>2014</v>
       </c>
-      <c r="B15" s="1">
-        <v>99.9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A16">
+      <c r="B16">
+        <v>101.11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17">
         <v>2015</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B17">
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A17">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18">
         <v>2016</v>
       </c>
-      <c r="B17" s="1">
-        <v>99.9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A18">
+      <c r="B18">
+        <v>100.02</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19">
         <v>2017</v>
       </c>
-      <c r="B18" s="1">
-        <v>101.3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A19">
+      <c r="B19">
+        <v>101.15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20">
         <v>2018</v>
       </c>
-      <c r="B19" s="1">
-        <v>102.5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A20">
+      <c r="B20">
+        <v>101.94</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21">
         <v>2019</v>
       </c>
-      <c r="B20" s="1">
-        <v>103.2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A21">
+      <c r="B21">
+        <v>102.46</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22">
         <v>2020</v>
       </c>
-      <c r="B21" s="1">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A22">
+      <c r="B22">
+        <v>101.17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23">
         <v>2021</v>
       </c>
-      <c r="B22" s="1">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A23">
+      <c r="B23">
+        <v>101.75</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24">
         <v>2022</v>
       </c>
-      <c r="B23" s="1">
-        <v>114.2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A24">
+      <c r="B24">
+        <v>111.21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25">
         <v>2023</v>
       </c>
-      <c r="B24" s="1">
-        <v>120.9</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A25">
+      <c r="B25">
+        <v>115.84</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26">
         <v>2024</v>
       </c>
-      <c r="B25" s="1">
-        <v>122.3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A26">
+      <c r="B26">
+        <v>119.31</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27">
         <v>2025</v>
       </c>
-      <c r="B26" s="1">
-        <v>125.11289999999998</v>
+      <c r="B27">
+        <v>122.65068000000001</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>2026</v>
+      </c>
+      <c r="B28">
+        <v>125.47164563999999</v>
       </c>
     </row>
   </sheetData>
@@ -1708,9 +1724,9 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A47DFC1-F794-4B22-BEC7-BA8732D9DC19}">
   <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1718,127 +1734,127 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2000</v>
       </c>
-      <c r="B2">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B2" s="1">
+        <v>128.15096465286581</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2001</v>
       </c>
       <c r="B3" s="1">
-        <v>94.696969696969688</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+        <v>128.03671996497107</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2002</v>
       </c>
       <c r="B4" s="1">
-        <v>95.447302022929463</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+        <v>137.29079497907949</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2003</v>
       </c>
       <c r="B5" s="1">
-        <v>96.458091179129539</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+        <v>140.71452645770137</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2004</v>
       </c>
       <c r="B6" s="1">
-        <v>96.969601279946119</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+        <v>144.08593355961776</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2005</v>
       </c>
       <c r="B7" s="1">
-        <v>98.489061920652574</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+        <v>139.3663966278074</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2006</v>
       </c>
       <c r="B8" s="1">
-        <v>99.701901385755733</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+        <v>132.22655751919007</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2007</v>
       </c>
       <c r="B9" s="1">
-        <v>99.118181459098636</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+        <v>135.06654286598575</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2008</v>
       </c>
       <c r="B10" s="1">
-        <v>99.414479707049125</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+        <v>135.51873626699921</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2009</v>
       </c>
       <c r="B11" s="1">
-        <v>101.72603050834627</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+        <v>133.36614749967771</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2010</v>
       </c>
       <c r="B12" s="1">
-        <v>102.75471065763016</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+        <v>128.26970215909469</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2011</v>
       </c>
       <c r="B13" s="1">
-        <v>101.42652965227776</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+        <v>118.42733706743086</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2012</v>
       </c>
       <c r="B14" s="1">
-        <v>99.76433277263807</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+        <v>107.54421023227832</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2013</v>
       </c>
       <c r="B15" s="1">
-        <v>99.760488361636632</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+        <v>97.739635481004711</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2014</v>
       </c>
       <c r="B16" s="1">
-        <v>99.776500638569601</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+        <v>100.00109891317489</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2015</v>
       </c>
@@ -1846,68 +1862,68 @@
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2016</v>
       </c>
       <c r="B18" s="1">
-        <v>100.31583307445378</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+        <v>101.31307071918951</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2017</v>
       </c>
       <c r="B19" s="1">
-        <v>99.674064744528025</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+        <v>100.95018399516668</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2018</v>
       </c>
       <c r="B20" s="1">
-        <v>99.663582842724992</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+        <v>103.00176574455561</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2019</v>
       </c>
       <c r="B21" s="1">
-        <v>100.24057738572574</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
+        <v>104.53944086581215</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2020</v>
       </c>
       <c r="B22" s="1">
-        <v>104.62002008704387</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+        <v>109.82614521212921</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2021</v>
       </c>
       <c r="B23" s="1">
-        <v>102.11412151067323</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
+        <v>109.74610974610974</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2022</v>
       </c>
       <c r="B24" s="1">
-        <v>95.303158403285224</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+        <v>105.90574388793974</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2023</v>
       </c>
       <c r="B25" s="1">
-        <v>91.982544707795</v>
+        <v>107.81154082259054</v>
       </c>
     </row>
   </sheetData>
@@ -1918,9 +1934,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8855BE1A-8357-468E-B95E-E2868B6CF276}">
   <dimension ref="A1:B62"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1928,7 +1944,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2010</v>
       </c>
@@ -1936,7 +1952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2011</v>
       </c>
@@ -1944,7 +1960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2012</v>
       </c>
@@ -1952,7 +1968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2013</v>
       </c>
@@ -1960,7 +1976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2014</v>
       </c>
@@ -1968,7 +1984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2015</v>
       </c>
@@ -1976,7 +1992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2016</v>
       </c>
@@ -1984,7 +2000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2017</v>
       </c>
@@ -1992,7 +2008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2018</v>
       </c>
@@ -2000,7 +2016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2019</v>
       </c>
@@ -2008,7 +2024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2020</v>
       </c>
@@ -2016,7 +2032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2021</v>
       </c>
@@ -2024,7 +2040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2022</v>
       </c>
@@ -2032,7 +2048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2023</v>
       </c>
@@ -2040,7 +2056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2024</v>
       </c>
@@ -2048,7 +2064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2025</v>
       </c>
@@ -2056,7 +2072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2026</v>
       </c>
@@ -2064,7 +2080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2027</v>
       </c>
@@ -2072,7 +2088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2028</v>
       </c>
@@ -2080,7 +2096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2029</v>
       </c>
@@ -2088,7 +2104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2030</v>
       </c>
@@ -2096,7 +2112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2031</v>
       </c>
@@ -2104,7 +2120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2032</v>
       </c>
@@ -2112,7 +2128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2033</v>
       </c>
@@ -2120,7 +2136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2034</v>
       </c>
@@ -2128,7 +2144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2035</v>
       </c>
@@ -2136,7 +2152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2036</v>
       </c>
@@ -2144,7 +2160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>2037</v>
       </c>
@@ -2152,7 +2168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>2038</v>
       </c>
@@ -2160,7 +2176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>2039</v>
       </c>
@@ -2168,7 +2184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>2040</v>
       </c>
@@ -2176,7 +2192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>2041</v>
       </c>
@@ -2184,7 +2200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>2042</v>
       </c>
@@ -2192,7 +2208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>2043</v>
       </c>
@@ -2200,7 +2216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>2044</v>
       </c>
@@ -2208,7 +2224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>2045</v>
       </c>
@@ -2216,7 +2232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>2046</v>
       </c>
@@ -2224,7 +2240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>2047</v>
       </c>
@@ -2232,7 +2248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>2048</v>
       </c>
@@ -2240,7 +2256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>2049</v>
       </c>
@@ -2248,7 +2264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>2050</v>
       </c>
@@ -2256,7 +2272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>2051</v>
       </c>
@@ -2264,7 +2280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>2052</v>
       </c>
@@ -2272,7 +2288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>2053</v>
       </c>
@@ -2280,7 +2296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>2054</v>
       </c>
@@ -2288,7 +2304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>2055</v>
       </c>
@@ -2296,7 +2312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>2056</v>
       </c>
@@ -2304,7 +2320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>2057</v>
       </c>
@@ -2312,7 +2328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>2058</v>
       </c>
@@ -2320,7 +2336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>2059</v>
       </c>
@@ -2328,7 +2344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>2060</v>
       </c>
@@ -2336,7 +2352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>2061</v>
       </c>
@@ -2344,7 +2360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>2062</v>
       </c>
@@ -2352,7 +2368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>2063</v>
       </c>
@@ -2360,7 +2376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>2064</v>
       </c>
@@ -2368,7 +2384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>2065</v>
       </c>
@@ -2376,7 +2392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>2066</v>
       </c>
@@ -2384,7 +2400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>2067</v>
       </c>
@@ -2392,7 +2408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>2068</v>
       </c>
@@ -2400,7 +2416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>2069</v>
       </c>
@@ -2408,7 +2424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>2070</v>
       </c>
@@ -2424,9 +2440,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C683A821-437B-4D81-97F1-7CA9A663AC24}">
   <dimension ref="A1:B62"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2434,7 +2450,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2010</v>
       </c>
@@ -2442,7 +2458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2011</v>
       </c>
@@ -2450,7 +2466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2012</v>
       </c>
@@ -2458,7 +2474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2013</v>
       </c>
@@ -2466,7 +2482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2014</v>
       </c>
@@ -2474,7 +2490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2015</v>
       </c>
@@ -2482,7 +2498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2016</v>
       </c>
@@ -2490,7 +2506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2017</v>
       </c>
@@ -2498,7 +2514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2018</v>
       </c>
@@ -2506,7 +2522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2019</v>
       </c>
@@ -2514,7 +2530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2020</v>
       </c>
@@ -2522,7 +2538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2021</v>
       </c>
@@ -2530,7 +2546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2022</v>
       </c>
@@ -2538,7 +2554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2023</v>
       </c>
@@ -2546,7 +2562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2024</v>
       </c>
@@ -2554,7 +2570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2025</v>
       </c>
@@ -2562,7 +2578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2026</v>
       </c>
@@ -2570,7 +2586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2027</v>
       </c>
@@ -2578,7 +2594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2028</v>
       </c>
@@ -2586,7 +2602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2029</v>
       </c>
@@ -2594,7 +2610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2030</v>
       </c>
@@ -2602,7 +2618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2031</v>
       </c>
@@ -2610,7 +2626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2032</v>
       </c>
@@ -2618,7 +2634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2033</v>
       </c>
@@ -2626,7 +2642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2034</v>
       </c>
@@ -2634,7 +2650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2035</v>
       </c>
@@ -2642,7 +2658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2036</v>
       </c>
@@ -2650,7 +2666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>2037</v>
       </c>
@@ -2658,7 +2674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>2038</v>
       </c>
@@ -2666,7 +2682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>2039</v>
       </c>
@@ -2674,7 +2690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>2040</v>
       </c>
@@ -2682,7 +2698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>2041</v>
       </c>
@@ -2690,7 +2706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>2042</v>
       </c>
@@ -2698,7 +2714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>2043</v>
       </c>
@@ -2706,7 +2722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>2044</v>
       </c>
@@ -2714,7 +2730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>2045</v>
       </c>
@@ -2722,7 +2738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>2046</v>
       </c>
@@ -2730,7 +2746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>2047</v>
       </c>
@@ -2738,7 +2754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>2048</v>
       </c>
@@ -2746,7 +2762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>2049</v>
       </c>
@@ -2754,7 +2770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>2050</v>
       </c>
@@ -2762,7 +2778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>2051</v>
       </c>
@@ -2770,7 +2786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>2052</v>
       </c>
@@ -2778,7 +2794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>2053</v>
       </c>
@@ -2786,7 +2802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>2054</v>
       </c>
@@ -2794,7 +2810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>2055</v>
       </c>
@@ -2802,7 +2818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>2056</v>
       </c>
@@ -2810,7 +2826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>2057</v>
       </c>
@@ -2818,7 +2834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>2058</v>
       </c>
@@ -2826,7 +2842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>2059</v>
       </c>
@@ -2834,7 +2850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>2060</v>
       </c>
@@ -2842,7 +2858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>2061</v>
       </c>
@@ -2850,7 +2866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>2062</v>
       </c>
@@ -2858,7 +2874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>2063</v>
       </c>
@@ -2866,7 +2882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>2064</v>
       </c>
@@ -2874,7 +2890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>2065</v>
       </c>
@@ -2882,7 +2898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>2066</v>
       </c>
@@ -2890,7 +2906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>2067</v>
       </c>
@@ -2898,7 +2914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>2068</v>
       </c>
@@ -2906,7 +2922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>2069</v>
       </c>
@@ -2914,7 +2930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>2070</v>
       </c>
@@ -2930,9 +2946,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FF94849-A6CD-439B-B269-5434C4C1F099}">
   <dimension ref="A1:B62"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2940,7 +2956,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2010</v>
       </c>
@@ -2948,7 +2964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2011</v>
       </c>
@@ -2956,7 +2972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2012</v>
       </c>
@@ -2964,7 +2980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2013</v>
       </c>
@@ -2972,7 +2988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2014</v>
       </c>
@@ -2980,7 +2996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2015</v>
       </c>
@@ -2988,7 +3004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2016</v>
       </c>
@@ -2996,7 +3012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2017</v>
       </c>
@@ -3004,7 +3020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2018</v>
       </c>
@@ -3012,7 +3028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2019</v>
       </c>
@@ -3020,7 +3036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2020</v>
       </c>
@@ -3028,7 +3044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2021</v>
       </c>
@@ -3036,7 +3052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2022</v>
       </c>
@@ -3044,7 +3060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2023</v>
       </c>
@@ -3052,7 +3068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2024</v>
       </c>
@@ -3060,7 +3076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2025</v>
       </c>
@@ -3068,7 +3084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2026</v>
       </c>
@@ -3076,7 +3092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2027</v>
       </c>
@@ -3084,7 +3100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2028</v>
       </c>
@@ -3092,7 +3108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2029</v>
       </c>
@@ -3100,7 +3116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2030</v>
       </c>
@@ -3108,7 +3124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2031</v>
       </c>
@@ -3116,7 +3132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2032</v>
       </c>
@@ -3124,7 +3140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2033</v>
       </c>
@@ -3132,7 +3148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2034</v>
       </c>
@@ -3140,7 +3156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2035</v>
       </c>
@@ -3148,7 +3164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2036</v>
       </c>
@@ -3156,7 +3172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>2037</v>
       </c>
@@ -3164,7 +3180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>2038</v>
       </c>
@@ -3172,7 +3188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>2039</v>
       </c>
@@ -3180,7 +3196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>2040</v>
       </c>
@@ -3188,7 +3204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>2041</v>
       </c>
@@ -3196,7 +3212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>2042</v>
       </c>
@@ -3204,7 +3220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>2043</v>
       </c>
@@ -3212,7 +3228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>2044</v>
       </c>
@@ -3220,7 +3236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>2045</v>
       </c>
@@ -3228,7 +3244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>2046</v>
       </c>
@@ -3236,7 +3252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>2047</v>
       </c>
@@ -3244,7 +3260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>2048</v>
       </c>
@@ -3252,7 +3268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>2049</v>
       </c>
@@ -3260,7 +3276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>2050</v>
       </c>
@@ -3268,7 +3284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>2051</v>
       </c>
@@ -3276,7 +3292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>2052</v>
       </c>
@@ -3284,7 +3300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>2053</v>
       </c>
@@ -3292,7 +3308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>2054</v>
       </c>
@@ -3300,7 +3316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>2055</v>
       </c>
@@ -3308,7 +3324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>2056</v>
       </c>
@@ -3316,7 +3332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>2057</v>
       </c>
@@ -3324,7 +3340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>2058</v>
       </c>
@@ -3332,7 +3348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>2059</v>
       </c>
@@ -3340,7 +3356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>2060</v>
       </c>
@@ -3348,7 +3364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>2061</v>
       </c>
@@ -3356,7 +3372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>2062</v>
       </c>
@@ -3364,7 +3380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>2063</v>
       </c>
@@ -3372,7 +3388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>2064</v>
       </c>
@@ -3380,7 +3396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>2065</v>
       </c>
@@ -3388,7 +3404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>2066</v>
       </c>
@@ -3396,7 +3412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>2067</v>
       </c>
@@ -3404,7 +3420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>2068</v>
       </c>
@@ -3412,7 +3428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>2069</v>
       </c>
@@ -3420,7 +3436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>2070</v>
       </c>
@@ -3436,12 +3452,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D18E90C-6D91-4744-9FCB-A05B59544AB8}">
   <dimension ref="A1:F62"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="14.73046875" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3455,7 +3471,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2010</v>
       </c>
@@ -3469,7 +3485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2011</v>
       </c>
@@ -3483,7 +3499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2012</v>
       </c>
@@ -3497,7 +3513,7 @@
         <v>-0.68042582690000331</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2013</v>
       </c>
@@ -3511,7 +3527,7 @@
         <v>-0.67229930191496556</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2014</v>
       </c>
@@ -3525,7 +3541,7 @@
         <v>-0.67897363322872639</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2015</v>
       </c>
@@ -3539,7 +3555,7 @@
         <v>-0.66203073162886494</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2016</v>
       </c>
@@ -3553,7 +3569,7 @@
         <v>-0.65127749552133463</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2017</v>
       </c>
@@ -3567,7 +3583,7 @@
         <v>-0.62856645997943639</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2018</v>
       </c>
@@ -3581,7 +3597,7 @@
         <v>-0.62262883931939683</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2019</v>
       </c>
@@ -3595,7 +3611,7 @@
         <v>-0.61386966551793498</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2020</v>
       </c>
@@ -3609,7 +3625,7 @@
         <v>-0.59884444696646777</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2021</v>
       </c>
@@ -3623,7 +3639,7 @@
         <v>-0.58212592838721533</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2022</v>
       </c>
@@ -3637,7 +3653,7 @@
         <v>-0.58476026852042595</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2023</v>
       </c>
@@ -3651,7 +3667,7 @@
         <v>-0.56894577426477011</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2024</v>
       </c>
@@ -3665,7 +3681,7 @@
         <v>-0.55774239163231498</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2025</v>
       </c>
@@ -3679,7 +3695,7 @@
         <v>-0.5546484315400706</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2026</v>
       </c>
@@ -3693,7 +3709,7 @@
         <v>-0.54633744534475526</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2027</v>
       </c>
@@ -3707,7 +3723,7 @@
         <v>-0.53660398326743075</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2028</v>
       </c>
@@ -3721,7 +3737,7 @@
         <v>-0.52636891781716488</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2029</v>
       </c>
@@ -3735,7 +3751,7 @@
         <v>-0.52739427357167223</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2030</v>
       </c>
@@ -3749,7 +3765,7 @@
         <v>-0.522335868711721</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2031</v>
       </c>
@@ -3763,7 +3779,7 @@
         <v>-0.51932161850484515</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2032</v>
       </c>
@@ -3777,7 +3793,7 @@
         <v>-0.51851186880903399</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2033</v>
       </c>
@@ -3791,7 +3807,7 @@
         <v>-0.52248458236888451</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2034</v>
       </c>
@@ -3805,7 +3821,7 @@
         <v>-0.51756454907723248</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2035</v>
       </c>
@@ -3819,7 +3835,7 @@
         <v>-0.51707659305484055</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2036</v>
       </c>
@@ -3833,7 +3849,7 @@
         <v>-0.51785189045280133</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>2037</v>
       </c>
@@ -3847,7 +3863,7 @@
         <v>-0.52133458277805855</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>2038</v>
       </c>
@@ -3861,7 +3877,7 @@
         <v>-0.52255964231049601</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>2039</v>
       </c>
@@ -3875,7 +3891,7 @@
         <v>-0.52461978177447943</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>2040</v>
       </c>
@@ -3889,7 +3905,7 @@
         <v>-0.52602689591038243</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>2041</v>
       </c>
@@ -3903,7 +3919,7 @@
         <v>-0.52818471105801446</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>2042</v>
       </c>
@@ -3917,7 +3933,7 @@
         <v>-0.52582640158760352</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>2043</v>
       </c>
@@ -3931,7 +3947,7 @@
         <v>-0.52884537398341225</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>2044</v>
       </c>
@@ -3945,7 +3961,7 @@
         <v>-0.53136207561516069</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>2045</v>
       </c>
@@ -3959,7 +3975,7 @@
         <v>-0.53392813259970762</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>2046</v>
       </c>
@@ -3973,7 +3989,7 @@
         <v>-0.53502526357346303</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>2047</v>
       </c>
@@ -3987,7 +4003,7 @@
         <v>-0.5361827911656164</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>2048</v>
       </c>
@@ -4001,7 +4017,7 @@
         <v>-0.53742998980006962</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>2049</v>
       </c>
@@ -4015,7 +4031,7 @@
         <v>-0.53265366720456808</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>2050</v>
       </c>
@@ -4029,7 +4045,7 @@
         <v>-0.52672262067763742</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>2051</v>
       </c>
@@ -4043,7 +4059,7 @@
         <v>-0.52246561759781496</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>2052</v>
       </c>
@@ -4057,7 +4073,7 @@
         <v>-0.51992475724234222</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>2053</v>
       </c>
@@ -4071,7 +4087,7 @@
         <v>-0.51600574555924328</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>2054</v>
       </c>
@@ -4085,7 +4101,7 @@
         <v>-0.51576972424348644</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>2055</v>
       </c>
@@ -4099,7 +4115,7 @@
         <v>-0.51800776098642443</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>2056</v>
       </c>
@@ -4113,7 +4129,7 @@
         <v>-0.51952270196948724</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>2057</v>
       </c>
@@ -4127,7 +4143,7 @@
         <v>-0.52097143042496585</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>2058</v>
       </c>
@@ -4141,7 +4157,7 @@
         <v>-0.51855272309252176</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>2059</v>
       </c>
@@ -4155,7 +4171,7 @@
         <v>-0.51809916084156005</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>2060</v>
       </c>
@@ -4169,7 +4185,7 @@
         <v>-0.51977389607061364</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>2061</v>
       </c>
@@ -4183,7 +4199,7 @@
         <v>-0.51599900885427696</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>2062</v>
       </c>
@@ -4197,7 +4213,7 @@
         <v>-0.51480700328602169</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>2063</v>
       </c>
@@ -4211,7 +4227,7 @@
         <v>-0.51568068499828201</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>2064</v>
       </c>
@@ -4225,7 +4241,7 @@
         <v>-0.51597773825575943</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>2065</v>
       </c>
@@ -4239,7 +4255,7 @@
         <v>-0.50918163905100955</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>2066</v>
       </c>
@@ -4253,7 +4269,7 @@
         <v>-0.51037220329257249</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>2067</v>
       </c>
@@ -4267,7 +4283,7 @@
         <v>-0.50578085391324401</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>2068</v>
       </c>
@@ -4281,7 +4297,7 @@
         <v>-0.50041296740445906</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>2069</v>
       </c>
@@ -4295,7 +4311,7 @@
         <v>-0.50041296740445906</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>2070</v>
       </c>
@@ -4317,9 +4333,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B00E6D01-ED8F-4196-BCE1-0F54EC92EC33}">
   <dimension ref="A1:F62"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4333,7 +4349,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2010</v>
       </c>
@@ -4347,7 +4363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2011</v>
       </c>
@@ -4361,7 +4377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2012</v>
       </c>
@@ -4375,7 +4391,7 @@
         <v>-0.44081411312763502</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2013</v>
       </c>
@@ -4389,7 +4405,7 @@
         <v>-0.41178003442893141</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2014</v>
       </c>
@@ -4403,7 +4419,7 @@
         <v>-0.38195691653651342</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2015</v>
       </c>
@@ -4417,7 +4433,7 @@
         <v>-0.35662154819469444</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2016</v>
       </c>
@@ -4431,7 +4447,7 @@
         <v>-0.33645665993640061</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2017</v>
       </c>
@@ -4445,7 +4461,7 @@
         <v>-0.31569377810596422</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2018</v>
       </c>
@@ -4459,7 +4475,7 @@
         <v>-0.29611480221652442</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2019</v>
       </c>
@@ -4473,7 +4489,7 @@
         <v>-0.279462622342386</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2020</v>
       </c>
@@ -4487,7 +4503,7 @@
         <v>-0.26591979180000819</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2021</v>
       </c>
@@ -4501,7 +4517,7 @@
         <v>-0.25543875103684177</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2022</v>
       </c>
@@ -4515,7 +4531,7 @@
         <v>-0.24930347300809638</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2023</v>
       </c>
@@ -4529,7 +4545,7 @@
         <v>-0.2471951557625644</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2024</v>
       </c>
@@ -4543,7 +4559,7 @@
         <v>-0.24727245707738721</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2025</v>
       </c>
@@ -4557,7 +4573,7 @@
         <v>-0.23666450179745918</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2026</v>
       </c>
@@ -4571,7 +4587,7 @@
         <v>-0.23784361977757321</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2027</v>
       </c>
@@ -4585,7 +4601,7 @@
         <v>-0.23889278870939884</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2028</v>
       </c>
@@ -4599,7 +4615,7 @@
         <v>-0.23893998110579662</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2029</v>
       </c>
@@ -4613,7 +4629,7 @@
         <v>-0.23843847695520243</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2030</v>
       </c>
@@ -4627,7 +4643,7 @@
         <v>-0.24968508459850719</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2031</v>
       </c>
@@ -4641,7 +4657,7 @@
         <v>-0.25091556848125485</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2032</v>
       </c>
@@ -4655,7 +4671,7 @@
         <v>-0.25300049353502324</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2033</v>
       </c>
@@ -4669,7 +4685,7 @@
         <v>-0.25769551121458001</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2034</v>
       </c>
@@ -4683,7 +4699,7 @@
         <v>-0.26297059722398985</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2035</v>
       </c>
@@ -4697,7 +4713,7 @@
         <v>-0.26957256055242024</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2036</v>
       </c>
@@ -4711,7 +4727,7 @@
         <v>-0.27813755313923438</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>2037</v>
       </c>
@@ -4725,7 +4741,7 @@
         <v>-0.27474637053283057</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>2038</v>
       </c>
@@ -4739,7 +4755,7 @@
         <v>-0.28518071039366039</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>2039</v>
       </c>
@@ -4753,7 +4769,7 @@
         <v>-0.2959050156529302</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>2040</v>
       </c>
@@ -4767,7 +4783,7 @@
         <v>-0.2928526070865794</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>2041</v>
       </c>
@@ -4781,7 +4797,7 @@
         <v>-0.30204917920681157</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>2042</v>
       </c>
@@ -4795,7 +4811,7 @@
         <v>-0.32304908725990761</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>2043</v>
       </c>
@@ -4809,7 +4825,7 @@
         <v>-0.32697846249115198</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>2044</v>
       </c>
@@ -4823,7 +4839,7 @@
         <v>-0.33007523822817458</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>2045</v>
       </c>
@@ -4837,7 +4853,7 @@
         <v>-0.34395374911145921</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>2046</v>
       </c>
@@ -4851,7 +4867,7 @@
         <v>-0.32911187304579681</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>2047</v>
       </c>
@@ -4865,7 +4881,7 @@
         <v>-0.32707905887567962</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>2048</v>
       </c>
@@ -4879,7 +4895,7 @@
         <v>-0.32548082652979621</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>2049</v>
       </c>
@@ -4893,7 +4909,7 @@
         <v>-0.32367111158351802</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>2050</v>
       </c>
@@ -4907,7 +4923,7 @@
         <v>-0.31183478961522498</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>2051</v>
       </c>
@@ -4921,7 +4937,7 @@
         <v>-0.30933783525634517</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>2052</v>
       </c>
@@ -4935,7 +4951,7 @@
         <v>-0.295502572399851</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>2053</v>
       </c>
@@ -4949,7 +4965,7 @@
         <v>-0.28426566851705959</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>2054</v>
       </c>
@@ -4963,7 +4979,7 @@
         <v>-0.2846970607117626</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>2055</v>
       </c>
@@ -4977,7 +4993,7 @@
         <v>-0.29652418423720162</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>2056</v>
       </c>
@@ -4991,7 +5007,7 @@
         <v>-0.31354110133198604</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>2057</v>
       </c>
@@ -5005,7 +5021,7 @@
         <v>-0.3278678462801522</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>2058</v>
       </c>
@@ -5019,7 +5035,7 @@
         <v>-0.33932540739172184</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>2059</v>
       </c>
@@ -5033,7 +5049,7 @@
         <v>-0.33891825783445723</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>2060</v>
       </c>
@@ -5047,7 +5063,7 @@
         <v>-0.33791821188593724</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>2061</v>
       </c>
@@ -5061,7 +5077,7 @@
         <v>-0.33627771003385082</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>2062</v>
       </c>
@@ -5075,7 +5091,7 @@
         <v>-0.33352763519739703</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>2063</v>
       </c>
@@ -5089,7 +5105,7 @@
         <v>-0.33028054032751103</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>2064</v>
       </c>
@@ -5103,7 +5119,7 @@
         <v>-0.32636589095194396</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>2065</v>
       </c>
@@ -5117,7 +5133,7 @@
         <v>-0.32296966045752384</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>2066</v>
       </c>
@@ -5131,7 +5147,7 @@
         <v>-0.3197457208767488</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>2067</v>
       </c>
@@ -5145,7 +5161,7 @@
         <v>-0.31773659008754962</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>2068</v>
       </c>
@@ -5159,7 +5175,7 @@
         <v>-0.31670999077073703</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>2069</v>
       </c>
@@ -5173,7 +5189,7 @@
         <v>-0.31670999077073703</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>2070</v>
       </c>
@@ -5195,9 +5211,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81CF35D1-EA41-4B4F-8246-ED1C76F988F0}">
   <dimension ref="A1:B32"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5205,7 +5221,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2010</v>
       </c>
@@ -5213,7 +5229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2011</v>
       </c>
@@ -5221,7 +5237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2012</v>
       </c>
@@ -5229,7 +5245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2013</v>
       </c>
@@ -5237,7 +5253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2014</v>
       </c>
@@ -5245,7 +5261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2015</v>
       </c>
@@ -5253,7 +5269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2016</v>
       </c>
@@ -5261,7 +5277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2017</v>
       </c>
@@ -5269,7 +5285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2018</v>
       </c>
@@ -5277,7 +5293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2019</v>
       </c>
@@ -5285,7 +5301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2020</v>
       </c>
@@ -5293,7 +5309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2021</v>
       </c>
@@ -5301,7 +5317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2022</v>
       </c>
@@ -5309,7 +5325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2023</v>
       </c>
@@ -5317,7 +5333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2024</v>
       </c>
@@ -5325,7 +5341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2025</v>
       </c>
@@ -5333,7 +5349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2026</v>
       </c>
@@ -5341,7 +5357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2027</v>
       </c>
@@ -5349,7 +5365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2028</v>
       </c>
@@ -5357,7 +5373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2029</v>
       </c>
@@ -5365,7 +5381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2030</v>
       </c>
@@ -5373,7 +5389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2031</v>
       </c>
@@ -5381,7 +5397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2032</v>
       </c>
@@ -5389,7 +5405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2033</v>
       </c>
@@ -5397,7 +5413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2034</v>
       </c>
@@ -5405,7 +5421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2035</v>
       </c>
@@ -5413,7 +5429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2036</v>
       </c>
@@ -5421,7 +5437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>2037</v>
       </c>
@@ -5429,7 +5445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>2038</v>
       </c>
@@ -5437,7 +5453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>2039</v>
       </c>
@@ -5445,7 +5461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>2040</v>
       </c>
@@ -5461,9 +5477,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D7429DD-438F-4396-BA37-1ECD20FCD2D9}">
   <dimension ref="A1:B32"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5471,7 +5487,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2010</v>
       </c>
@@ -5479,7 +5495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2011</v>
       </c>
@@ -5487,7 +5503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2012</v>
       </c>
@@ -5495,7 +5511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2013</v>
       </c>
@@ -5503,7 +5519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2014</v>
       </c>
@@ -5511,7 +5527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2015</v>
       </c>
@@ -5519,7 +5535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2016</v>
       </c>
@@ -5527,7 +5543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2017</v>
       </c>
@@ -5535,7 +5551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2018</v>
       </c>
@@ -5543,7 +5559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2019</v>
       </c>
@@ -5551,7 +5567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2020</v>
       </c>
@@ -5559,7 +5575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2021</v>
       </c>
@@ -5567,7 +5583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2022</v>
       </c>
@@ -5575,7 +5591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2023</v>
       </c>
@@ -5583,7 +5599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2024</v>
       </c>
@@ -5591,7 +5607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2025</v>
       </c>
@@ -5599,7 +5615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2026</v>
       </c>
@@ -5607,7 +5623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2027</v>
       </c>
@@ -5615,7 +5631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2028</v>
       </c>
@@ -5623,7 +5639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2029</v>
       </c>
@@ -5631,7 +5647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2030</v>
       </c>
@@ -5639,7 +5655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2031</v>
       </c>
@@ -5647,7 +5663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2032</v>
       </c>
@@ -5655,7 +5671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2033</v>
       </c>
@@ -5663,7 +5679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2034</v>
       </c>
@@ -5671,7 +5687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2035</v>
       </c>
@@ -5679,7 +5695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2036</v>
       </c>
@@ -5687,7 +5703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>2037</v>
       </c>
@@ -5695,7 +5711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>2038</v>
       </c>
@@ -5703,7 +5719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>2039</v>
       </c>
@@ -5711,7 +5727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>2040</v>
       </c>
@@ -5727,9 +5743,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24975FDF-8D77-4D4B-8592-0CCFC0F7BE8F}">
   <dimension ref="A1:B32"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5737,7 +5753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2010</v>
       </c>
@@ -5745,7 +5761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2011</v>
       </c>
@@ -5753,7 +5769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2012</v>
       </c>
@@ -5761,7 +5777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2013</v>
       </c>
@@ -5769,7 +5785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2014</v>
       </c>
@@ -5777,7 +5793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2015</v>
       </c>
@@ -5785,7 +5801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2016</v>
       </c>
@@ -5793,7 +5809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2017</v>
       </c>
@@ -5801,7 +5817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2018</v>
       </c>
@@ -5809,7 +5825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2019</v>
       </c>
@@ -5817,7 +5833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2020</v>
       </c>
@@ -5825,7 +5841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2021</v>
       </c>
@@ -5833,7 +5849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2022</v>
       </c>
@@ -5841,7 +5857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2023</v>
       </c>
@@ -5849,7 +5865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2024</v>
       </c>
@@ -5857,7 +5873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2025</v>
       </c>
@@ -5865,7 +5881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2026</v>
       </c>
@@ -5873,7 +5889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2027</v>
       </c>
@@ -5881,7 +5897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2028</v>
       </c>
@@ -5889,7 +5905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2029</v>
       </c>
@@ -5897,7 +5913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2030</v>
       </c>
@@ -5905,7 +5921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2031</v>
       </c>
@@ -5913,7 +5929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2032</v>
       </c>
@@ -5921,7 +5937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2033</v>
       </c>
@@ -5929,7 +5945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2034</v>
       </c>
@@ -5937,7 +5953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2035</v>
       </c>
@@ -5945,7 +5961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2036</v>
       </c>
@@ -5953,7 +5969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>2037</v>
       </c>
@@ -5961,7 +5977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>2038</v>
       </c>
@@ -5969,7 +5985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>2039</v>
       </c>
@@ -5977,7 +5993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>2040</v>
       </c>

--- a/input/time_series_factor.xlsx
+++ b/input/time_series_factor.xlsx
@@ -8,21 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patryk\git\SimPaths_HU\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F86CE648-DB9A-41CD-9228-83283CC4B545}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{338908C8-E9BC-454C-AF83-8F9709D243EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" tabRatio="973" firstSheet="6" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="973" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
-    <sheet name="IT_disability_adjustment" sheetId="25" r:id="rId2"/>
-    <sheet name="IT_students_adjustment" sheetId="24" r:id="rId3"/>
-    <sheet name="IT_retirement_adjustment" sheetId="23" r:id="rId4"/>
-    <sheet name="IT_cohabitation_adjustment" sheetId="15" r:id="rId5"/>
-    <sheet name="IT_fertility_adjustment" sheetId="19" r:id="rId6"/>
-    <sheet name="IT_utility_adj_smales" sheetId="16" r:id="rId7"/>
-    <sheet name="IT_utility_adj_sfemales" sheetId="17" r:id="rId8"/>
-    <sheet name="IT_utility_adj_all" sheetId="26" r:id="rId9"/>
-    <sheet name="IT_utility_adj_couples" sheetId="18" r:id="rId10"/>
+    <sheet name="EL_disability_adjustment" sheetId="25" r:id="rId2"/>
+    <sheet name="EL_students_adjustment" sheetId="24" r:id="rId3"/>
+    <sheet name="EL_retirement_adjustment" sheetId="23" r:id="rId4"/>
+    <sheet name="EL_cohabitation_adjustment" sheetId="15" r:id="rId5"/>
+    <sheet name="EL_fertility_adjustment" sheetId="19" r:id="rId6"/>
+    <sheet name="EL_utility_adj_smales" sheetId="16" r:id="rId7"/>
+    <sheet name="EL_utility_adj_sfemales" sheetId="17" r:id="rId8"/>
+    <sheet name="EL_utility_adj_all" sheetId="26" r:id="rId9"/>
+    <sheet name="EL_utility_adj_couples" sheetId="18" r:id="rId10"/>
     <sheet name="EL_gdp" sheetId="20" r:id="rId11"/>
     <sheet name="EL_inflation" sheetId="21" r:id="rId12"/>
     <sheet name="EL_wage_growth" sheetId="22" r:id="rId13"/>

--- a/input/time_series_factor.xlsx
+++ b/input/time_series_factor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patryk\git\SimPaths_HU\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{338908C8-E9BC-454C-AF83-8F9709D243EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E222142-63F1-4AFB-8F18-59446F9B7D8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="973" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="973" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -20,12 +20,16 @@
     <sheet name="EL_cohabitation_adjustment" sheetId="15" r:id="rId5"/>
     <sheet name="EL_fertility_adjustment" sheetId="19" r:id="rId6"/>
     <sheet name="EL_utility_adj_smales" sheetId="16" r:id="rId7"/>
-    <sheet name="EL_utility_adj_sfemales" sheetId="17" r:id="rId8"/>
-    <sheet name="EL_utility_adj_all" sheetId="26" r:id="rId9"/>
-    <sheet name="EL_utility_adj_couples" sheetId="18" r:id="rId10"/>
-    <sheet name="EL_gdp" sheetId="20" r:id="rId11"/>
-    <sheet name="EL_inflation" sheetId="21" r:id="rId12"/>
-    <sheet name="EL_wage_growth" sheetId="22" r:id="rId13"/>
+    <sheet name="EL_utility_adj_acmales" sheetId="27" r:id="rId8"/>
+    <sheet name="EL_utility_adj_sfemales" sheetId="17" r:id="rId9"/>
+    <sheet name="EL_utility_adj_acfemales" sheetId="28" r:id="rId10"/>
+    <sheet name="EL_utility_adj_malewdep" sheetId="29" r:id="rId11"/>
+    <sheet name="EL_utility_adj_femalewdep" sheetId="30" r:id="rId12"/>
+    <sheet name="EL_utility_adj_all" sheetId="26" r:id="rId13"/>
+    <sheet name="EL_utility_adj_couples" sheetId="18" r:id="rId14"/>
+    <sheet name="EL_gdp" sheetId="20" r:id="rId15"/>
+    <sheet name="EL_inflation" sheetId="21" r:id="rId16"/>
+    <sheet name="EL_wage_growth" sheetId="22" r:id="rId17"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -48,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="13">
   <si>
     <t>Year</t>
   </si>
@@ -947,6 +951,1070 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85645446-9201-42CB-87E8-20EA00191E4F}">
+  <dimension ref="A1:B32"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>2010</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2011</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2012</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>2013</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>2014</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>2015</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>2016</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>2017</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>2018</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>2019</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>2020</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>2021</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>2022</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>2023</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>2024</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>2025</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>2026</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>2027</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>2028</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>2029</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>2030</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>2031</v>
+      </c>
+      <c r="B23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>2032</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>2033</v>
+      </c>
+      <c r="B25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>2034</v>
+      </c>
+      <c r="B26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>2035</v>
+      </c>
+      <c r="B27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>2036</v>
+      </c>
+      <c r="B28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>2037</v>
+      </c>
+      <c r="B29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>2038</v>
+      </c>
+      <c r="B30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>2039</v>
+      </c>
+      <c r="B31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>2040</v>
+      </c>
+      <c r="B32">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B7E76CA-5DA8-43BB-9115-F3E6C3EA4241}">
+  <dimension ref="A1:B32"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>2010</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2011</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2012</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>2013</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>2014</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>2015</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>2016</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>2017</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>2018</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>2019</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>2020</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>2021</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>2022</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>2023</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>2024</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>2025</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>2026</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>2027</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>2028</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>2029</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>2030</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>2031</v>
+      </c>
+      <c r="B23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>2032</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>2033</v>
+      </c>
+      <c r="B25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>2034</v>
+      </c>
+      <c r="B26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>2035</v>
+      </c>
+      <c r="B27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>2036</v>
+      </c>
+      <c r="B28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>2037</v>
+      </c>
+      <c r="B29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>2038</v>
+      </c>
+      <c r="B30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>2039</v>
+      </c>
+      <c r="B31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>2040</v>
+      </c>
+      <c r="B32">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FF28F74-76DA-4C07-B56C-EC589ACC1585}">
+  <dimension ref="A1:B32"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>2010</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2011</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2012</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>2013</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>2014</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>2015</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>2016</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>2017</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>2018</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>2019</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>2020</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>2021</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>2022</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>2023</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>2024</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>2025</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>2026</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>2027</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>2028</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>2029</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>2030</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>2031</v>
+      </c>
+      <c r="B23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>2032</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>2033</v>
+      </c>
+      <c r="B25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>2034</v>
+      </c>
+      <c r="B26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>2035</v>
+      </c>
+      <c r="B27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>2036</v>
+      </c>
+      <c r="B28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>2037</v>
+      </c>
+      <c r="B29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>2038</v>
+      </c>
+      <c r="B30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>2039</v>
+      </c>
+      <c r="B31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>2040</v>
+      </c>
+      <c r="B32">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24975FDF-8D77-4D4B-8592-0CCFC0F7BE8F}">
+  <dimension ref="A1:B32"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>2010</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2011</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2012</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>2013</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>2014</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>2015</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>2016</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>2017</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>2018</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>2019</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>2020</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>2021</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>2022</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>2023</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>2024</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>2025</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>2026</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>2027</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>2028</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>2029</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>2030</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>2031</v>
+      </c>
+      <c r="B23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>2032</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>2033</v>
+      </c>
+      <c r="B25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>2034</v>
+      </c>
+      <c r="B26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>2035</v>
+      </c>
+      <c r="B27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>2036</v>
+      </c>
+      <c r="B28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>2037</v>
+      </c>
+      <c r="B29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>2038</v>
+      </c>
+      <c r="B30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>2039</v>
+      </c>
+      <c r="B31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>2040</v>
+      </c>
+      <c r="B32">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83A8B1C6-B095-49F5-BE52-65A3AD804239}">
   <dimension ref="A1:B32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1212,7 +2280,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BB6812C-5BB0-43F7-B52C-EA13500B4AA8}">
   <dimension ref="A1:B33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1486,7 +2554,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0E899AF-6766-40B7-B849-58604785D824}">
   <dimension ref="A1:B28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1721,7 +2789,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A47DFC1-F794-4B22-BEC7-BA8732D9DC19}">
   <dimension ref="A1:B25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5475,6 +6543,272 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37E3EDDD-1BCB-4A05-83B2-F96CC2E4221A}">
+  <dimension ref="A1:B32"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>2010</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2011</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2012</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>2013</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>2014</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>2015</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>2016</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>2017</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>2018</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>2019</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>2020</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>2021</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>2022</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>2023</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>2024</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>2025</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>2026</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>2027</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>2028</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>2029</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>2030</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>2031</v>
+      </c>
+      <c r="B23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>2032</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>2033</v>
+      </c>
+      <c r="B25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>2034</v>
+      </c>
+      <c r="B26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>2035</v>
+      </c>
+      <c r="B27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>2036</v>
+      </c>
+      <c r="B28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>2037</v>
+      </c>
+      <c r="B29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>2038</v>
+      </c>
+      <c r="B30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>2039</v>
+      </c>
+      <c r="B31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>2040</v>
+      </c>
+      <c r="B32">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D7429DD-438F-4396-BA37-1ECD20FCD2D9}">
   <dimension ref="A1:B32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5738,270 +7072,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24975FDF-8D77-4D4B-8592-0CCFC0F7BE8F}">
-  <dimension ref="A1:B32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>2010</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2011</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>2012</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>2013</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>2014</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>2015</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>2016</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>2017</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>2018</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>2019</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>2020</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>2021</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>2022</v>
-      </c>
-      <c r="B14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>2023</v>
-      </c>
-      <c r="B15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>2024</v>
-      </c>
-      <c r="B16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>2025</v>
-      </c>
-      <c r="B17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>2026</v>
-      </c>
-      <c r="B18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>2027</v>
-      </c>
-      <c r="B19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>2028</v>
-      </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>2029</v>
-      </c>
-      <c r="B21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>2030</v>
-      </c>
-      <c r="B22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>2031</v>
-      </c>
-      <c r="B23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>2032</v>
-      </c>
-      <c r="B24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>2033</v>
-      </c>
-      <c r="B25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>2034</v>
-      </c>
-      <c r="B26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>2035</v>
-      </c>
-      <c r="B27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>2036</v>
-      </c>
-      <c r="B28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>2037</v>
-      </c>
-      <c r="B29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>2038</v>
-      </c>
-      <c r="B30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>2039</v>
-      </c>
-      <c r="B31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>2040</v>
-      </c>
-      <c r="B32">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/input/time_series_factor.xlsx
+++ b/input/time_series_factor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyFiles\99 DEV ENV\JAS-MINE\SimPaths\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7EC5005-AAD9-4E8B-AC05-A7C58FC4F3F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{873043E0-3F2A-495E-99E5-37186431BFC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="12" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -21,26 +21,38 @@
     <sheet name="UK_utility_adj_sfemales" sheetId="17" r:id="rId6"/>
     <sheet name="UK_utility_adj_couples" sheetId="18" r:id="rId7"/>
     <sheet name="UK_gdp" sheetId="2" r:id="rId8"/>
-    <sheet name="UK_inflation" sheetId="7" r:id="rId9"/>
-    <sheet name="UK_wage_growth" sheetId="8" r:id="rId10"/>
-    <sheet name="UK_saving_returns" sheetId="9" r:id="rId11"/>
-    <sheet name="UK_debt_cost_low" sheetId="10" r:id="rId12"/>
-    <sheet name="UK_debt_cost_hi" sheetId="11" r:id="rId13"/>
-    <sheet name="UK_carer_hourly_wage" sheetId="13" r:id="rId14"/>
-    <sheet name="UK raw data" sheetId="12" r:id="rId15"/>
-    <sheet name="IT" sheetId="4" r:id="rId16"/>
+    <sheet name="UK_gdp_per_capita" sheetId="20" r:id="rId9"/>
+    <sheet name="UK_inflation" sheetId="7" r:id="rId10"/>
+    <sheet name="UK_wage_growth" sheetId="8" r:id="rId11"/>
+    <sheet name="UK_saving_returns" sheetId="9" r:id="rId12"/>
+    <sheet name="UK_debt_cost_low" sheetId="10" r:id="rId13"/>
+    <sheet name="UK_debt_cost_hi" sheetId="11" r:id="rId14"/>
+    <sheet name="UK_carer_hourly_wage" sheetId="13" r:id="rId15"/>
+    <sheet name="UK raw data" sheetId="12" r:id="rId16"/>
+    <sheet name="IT" sheetId="4" r:id="rId17"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="58">
   <si>
     <t>Year</t>
   </si>
@@ -209,6 +221,12 @@
   <si>
     <t>dynamic utility model</t>
   </si>
+  <si>
+    <t>GDP per capita</t>
+  </si>
+  <si>
+    <t>Gross Domestic Product per capita. National Accounts variables for Gross Domestic Product (YBHA), resident population (EBAQ), and price deflator (YBGB). Bank of England data from the “Millennium of Macroeconomic Data” series (see Our World in Data). Annual figures in 2015 prices (base-year).</t>
+  </si>
 </sst>
 </file>
 
@@ -218,7 +236,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -358,6 +376,11 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="35">
@@ -669,7 +692,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -712,8 +735,9 @@
     <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -733,8 +757,9 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="42"/>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -772,6 +797,7 @@
     <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="42" xr:uid="{560BB6F3-4F55-48B2-ABBB-CDD607AA1FE6}"/>
     <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
     <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
     <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
@@ -1055,13 +1081,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.54296875" customWidth="1"/>
+    <col min="2" max="2" width="10.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>25</v>
       </c>
@@ -1069,7 +1095,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>26</v>
       </c>
@@ -1077,7 +1103,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>27</v>
       </c>
@@ -1085,7 +1111,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>28</v>
       </c>
@@ -1093,7 +1119,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>43</v>
       </c>
@@ -1107,11 +1133,11 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F3F720F-7C77-40C9-9D26-48C5FF4C5828}">
-  <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC2B7FF6-C3ED-409F-83AB-FB5EAD53E39E}">
+  <dimension ref="A1:B42"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1119,249 +1145,346 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2">
+        <v>1987</v>
+      </c>
+      <c r="B2" s="1">
+        <v>48.34160833287882</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="2">
+        <v>1988</v>
+      </c>
+      <c r="B3" s="1">
+        <v>49.6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="2">
+        <v>1989</v>
+      </c>
+      <c r="B4" s="1">
+        <v>52.2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="2">
+        <v>1990</v>
+      </c>
+      <c r="B5" s="1">
+        <v>55.9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="2">
+        <v>1991</v>
+      </c>
+      <c r="B6" s="1">
+        <v>60.1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="2">
+        <v>1992</v>
+      </c>
+      <c r="B7" s="1">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="2">
+        <v>1993</v>
+      </c>
+      <c r="B8" s="1">
+        <v>64.2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="2">
+        <v>1994</v>
+      </c>
+      <c r="B9" s="1">
+        <v>65.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="2">
+        <v>1995</v>
+      </c>
+      <c r="B10" s="1">
+        <v>67.2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="2">
+        <v>1996</v>
+      </c>
+      <c r="B11" s="1">
+        <v>68.8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="2">
+        <v>1997</v>
+      </c>
+      <c r="B12" s="1">
+        <v>70.099999999999994</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="2">
+        <v>1998</v>
+      </c>
+      <c r="B13" s="1">
+        <v>71.2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="2">
+        <v>1999</v>
+      </c>
+      <c r="B14" s="1">
+        <v>72.099999999999994</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" s="2">
         <v>2000</v>
       </c>
-      <c r="B2">
-        <v>143.29576929253196</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
+      <c r="B15" s="1">
+        <v>72.7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" s="2">
         <v>2001</v>
       </c>
-      <c r="B3">
-        <v>143.98221858016308</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
+      <c r="B16" s="1">
+        <v>73.599999999999994</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" s="2">
         <v>2002</v>
       </c>
-      <c r="B4">
-        <v>146.66557346756156</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
+      <c r="B17" s="1">
+        <v>74.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="2">
         <v>2003</v>
       </c>
-      <c r="B5">
-        <v>149.63794972406183</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
+      <c r="B18" s="1">
+        <v>75.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" s="2">
         <v>2004</v>
       </c>
-      <c r="B6">
-        <v>154.58310870370369</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
+      <c r="B19" s="1">
+        <v>76.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" s="2">
         <v>2005</v>
       </c>
-      <c r="B7">
-        <v>158.46724928510457</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
+      <c r="B20" s="1">
+        <v>78.099999999999994</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" s="2">
         <v>2006</v>
       </c>
-      <c r="B8">
-        <v>162.59473676470591</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
+      <c r="B21" s="1">
+        <v>79.900000000000006</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" s="2">
         <v>2007</v>
       </c>
-      <c r="B9">
-        <v>165.95105268948654</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
+      <c r="B22" s="1">
+        <v>81.8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" s="2">
         <v>2008</v>
       </c>
-      <c r="B10">
-        <v>162.87314316214093</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
+      <c r="B23" s="1">
+        <v>84.7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" s="2">
         <v>2009</v>
       </c>
-      <c r="B11">
-        <v>161.37643170708242</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
+      <c r="B24" s="1">
+        <v>86.6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" s="2">
         <v>2010</v>
       </c>
-      <c r="B12">
-        <v>159.65128374347503</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
+      <c r="B25" s="1">
+        <v>89.4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" s="2">
         <v>2011</v>
       </c>
-      <c r="B13">
-        <v>155.56126007316206</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
+      <c r="B26" s="1">
+        <v>93.4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" s="2">
         <v>2012</v>
       </c>
-      <c r="B14">
-        <v>153.17917333506765</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="2">
+      <c r="B27" s="1">
+        <v>96.1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" s="2">
         <v>2013</v>
       </c>
-      <c r="B15">
-        <v>151.43864936548223</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="2">
+      <c r="B28" s="1">
+        <v>98.5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" s="2">
         <v>2014</v>
       </c>
-      <c r="B16">
-        <v>151.03810470833329</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="2">
+      <c r="B29" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" s="2">
         <v>2015</v>
       </c>
-      <c r="B17">
-        <v>154.63866195833333</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
+      <c r="B30" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" s="2">
         <v>2016</v>
       </c>
-      <c r="B18">
-        <v>157.19974334657394</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
+      <c r="B31" s="1">
+        <v>100.7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" s="2">
         <v>2017</v>
       </c>
-      <c r="B19">
-        <v>156.93085901031591</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
+      <c r="B32" s="1">
+        <v>103.4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" s="2">
         <v>2018</v>
       </c>
-      <c r="B20">
-        <v>157.85818999055712</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
+      <c r="B33" s="1">
+        <v>105.9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" s="2">
         <v>2019</v>
       </c>
-      <c r="B21">
-        <v>160.03142759740257</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="2">
+      <c r="B34" s="1">
+        <v>107.8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" s="2">
         <v>2020</v>
       </c>
-      <c r="B22">
-        <v>162.12163966045293</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
+      <c r="B35" s="1">
+        <v>108.7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" s="2">
         <v>2021</v>
       </c>
-      <c r="B23">
-        <v>168.45206453568233</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="2">
+      <c r="B36" s="1">
+        <v>111.6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37" s="2">
         <v>2022</v>
       </c>
-      <c r="B24">
-        <v>162.20759979943486</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="2">
+      <c r="B37" s="1">
+        <v>121.7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" s="2">
         <v>2023</v>
       </c>
-      <c r="B25">
-        <v>164.79602326504056</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="2">
+      <c r="B38" s="1">
+        <v>124.57395874315898</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" s="2">
         <v>2024</v>
       </c>
-      <c r="B26">
-        <v>163.94277212602779</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="2">
+      <c r="B39" s="1">
+        <v>126.63064241784659</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" s="2">
         <v>2025</v>
       </c>
-      <c r="B27">
-        <v>163.18350470648323</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="2">
+      <c r="B40" s="1">
+        <v>129.11704786530214</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41" s="2">
         <v>2026</v>
       </c>
-      <c r="B28">
-        <v>163.21856984752483</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="2">
+      <c r="B41" s="1">
+        <v>131.69938882260817</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42" s="2">
         <v>2027</v>
       </c>
-      <c r="B29">
-        <v>163.03155667222143</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="2">
-        <v>2028</v>
-      </c>
-      <c r="B30">
-        <v>163.81254899663941</v>
+      <c r="B42" s="1">
+        <v>135.1276862908702</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AE1C571-12D2-48EC-9676-C9293E844074}">
-  <dimension ref="A1:B38"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F3F720F-7C77-40C9-9D26-48C5FF4C5828}">
+  <dimension ref="A1:B30"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1369,300 +1492,236 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2">
-        <v>1986</v>
-      </c>
-      <c r="B2" s="3">
-        <v>4.6286405160227334E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>1987</v>
-      </c>
-      <c r="B3" s="3">
-        <v>3.011788658083403E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>1988</v>
-      </c>
-      <c r="B4" s="3">
-        <v>0.12856812528973971</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>1989</v>
-      </c>
-      <c r="B5" s="3">
-        <v>0.13600529394329053</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>1990</v>
-      </c>
-      <c r="B6" s="3">
-        <v>-4.1070497545090956E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>1991</v>
-      </c>
-      <c r="B7" s="3">
-        <v>5.7350544024686867E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>1992</v>
-      </c>
-      <c r="B8" s="3">
-        <v>5.7631202236563261E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>1993</v>
-      </c>
-      <c r="B9" s="3">
-        <v>7.8989706216779254E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>1994</v>
-      </c>
-      <c r="B10" s="3">
-        <v>-1.128760392020467E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>1995</v>
-      </c>
-      <c r="B11" s="3">
-        <v>9.2160859105373527E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>1996</v>
-      </c>
-      <c r="B12" s="3">
-        <v>8.5586180972958781E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>1997</v>
-      </c>
-      <c r="B13" s="3">
-        <v>0.13646101577698233</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>1998</v>
-      </c>
-      <c r="B14" s="3">
-        <v>0.12375668034877796</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>1999</v>
-      </c>
-      <c r="B15" s="3">
-        <v>0.14456105557563292</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16">
         <v>2000</v>
       </c>
-      <c r="B16" s="3">
-        <v>1.2753813678981984E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17">
+      <c r="B2">
+        <v>143.29576929253196</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="2">
         <v>2001</v>
       </c>
-      <c r="B17" s="3">
-        <v>-2.1653766849825229E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18">
+      <c r="B3">
+        <v>143.98221858016308</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="2">
         <v>2002</v>
       </c>
-      <c r="B18" s="3">
-        <v>-3.0859935638595126E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19">
+      <c r="B4">
+        <v>146.66557346756156</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="2">
         <v>2003</v>
       </c>
-      <c r="B19" s="3">
-        <v>0.13021265938759741</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20">
+      <c r="B5">
+        <v>149.63794972406183</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="2">
         <v>2004</v>
       </c>
-      <c r="B20" s="3">
-        <v>0.11284628713988498</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21">
+      <c r="B6">
+        <v>154.58310870370369</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="2">
         <v>2005</v>
       </c>
-      <c r="B21" s="3">
-        <v>9.5700435119939753E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22">
+      <c r="B7">
+        <v>158.46724928510457</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="2">
         <v>2006</v>
       </c>
-      <c r="B22" s="3">
-        <v>8.3497102825924818E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23">
+      <c r="B8">
+        <v>162.59473676470591</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="2">
         <v>2007</v>
       </c>
-      <c r="B23" s="3">
-        <v>5.4036728450648441E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24">
+      <c r="B9">
+        <v>165.95105268948654</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="2">
         <v>2008</v>
       </c>
-      <c r="B24" s="3">
-        <v>-0.16066262517109864</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25">
+      <c r="B10">
+        <v>162.87314316214093</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="2">
         <v>2009</v>
       </c>
-      <c r="B25" s="3">
-        <v>8.877196143526267E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26">
+      <c r="B11">
+        <v>161.37643170708242</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="2">
         <v>2010</v>
       </c>
-      <c r="B26" s="3">
-        <v>5.6774110668480482E-2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27">
+      <c r="B12">
+        <v>159.65128374347503</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="2">
         <v>2011</v>
       </c>
-      <c r="B27" s="3">
-        <v>-2.7392490880683962E-2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28">
+      <c r="B13">
+        <v>155.56126007316206</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="2">
         <v>2012</v>
       </c>
-      <c r="B28" s="3">
-        <v>-2.2124513898473808E-2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29">
+      <c r="B14">
+        <v>153.17917333506765</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" s="2">
         <v>2013</v>
       </c>
-      <c r="B29" s="3">
-        <v>7.5335930021486197E-2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30">
+      <c r="B15">
+        <v>151.43864936548223</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" s="2">
         <v>2014</v>
       </c>
-      <c r="B30" s="3">
-        <v>7.9340966880817376E-2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31">
+      <c r="B16">
+        <v>151.03810470833329</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" s="2">
         <v>2015</v>
       </c>
-      <c r="B31" s="3">
-        <v>4.2381070018058686E-2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32">
+      <c r="B17">
+        <v>154.63866195833333</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="2">
         <v>2016</v>
       </c>
-      <c r="B32" s="3">
-        <v>-4.8974784087532974E-2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33">
+      <c r="B18">
+        <v>157.19974334657394</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" s="2">
         <v>2017</v>
       </c>
-      <c r="B33" s="3">
-        <v>7.0170871889905673E-2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34">
+      <c r="B19">
+        <v>156.93085901031591</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" s="2">
         <v>2018</v>
       </c>
-      <c r="B34" s="3">
-        <v>2.840535022977253E-2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35">
+      <c r="B20">
+        <v>157.85818999055712</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" s="2">
         <v>2019</v>
       </c>
-      <c r="B35" s="3">
-        <v>6.3714730205470804E-3</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36">
+      <c r="B21">
+        <v>160.03142759740257</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" s="2">
         <v>2020</v>
       </c>
-      <c r="B36" s="3">
-        <v>-7.3040697759606754E-2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37">
+      <c r="B22">
+        <v>162.12163966045293</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" s="2">
         <v>2021</v>
       </c>
-      <c r="B37" s="3">
-        <v>4.9303785520141474E-2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38">
+      <c r="B23">
+        <v>168.45206453568233</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" s="2">
         <v>2022</v>
       </c>
-      <c r="B38" s="3">
-        <v>4.6286405160227334E-2</v>
+      <c r="B24">
+        <v>162.20759979943486</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" s="2">
+        <v>2023</v>
+      </c>
+      <c r="B25">
+        <v>164.79602326504056</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B26">
+        <v>163.94277212602779</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B27">
+        <v>163.18350470648323</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B28">
+        <v>163.21856984752483</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" s="2">
+        <v>2027</v>
+      </c>
+      <c r="B29">
+        <v>163.03155667222143</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" s="2">
+        <v>2028</v>
+      </c>
+      <c r="B30">
+        <v>163.81254899663941</v>
       </c>
     </row>
   </sheetData>
@@ -1671,11 +1730,11 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF70C8B1-8A2A-4CB2-AE85-70911F99E869}">
-  <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AE1C571-12D2-48EC-9676-C9293E844074}">
+  <dimension ref="A1:B38"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1683,236 +1742,300 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2">
+        <v>1986</v>
+      </c>
+      <c r="B2" s="3">
+        <v>4.6286405160227334E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>1987</v>
+      </c>
+      <c r="B3" s="3">
+        <v>3.011788658083403E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>1988</v>
+      </c>
+      <c r="B4" s="3">
+        <v>0.12856812528973971</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>1989</v>
+      </c>
+      <c r="B5" s="3">
+        <v>0.13600529394329053</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>1990</v>
+      </c>
+      <c r="B6" s="3">
+        <v>-4.1070497545090956E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>1991</v>
+      </c>
+      <c r="B7" s="3">
+        <v>5.7350544024686867E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>1992</v>
+      </c>
+      <c r="B8" s="3">
+        <v>5.7631202236563261E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>1993</v>
+      </c>
+      <c r="B9" s="3">
+        <v>7.8989706216779254E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10">
         <v>1994</v>
       </c>
-      <c r="B2" s="3">
-        <v>6.0198436757189541E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3">
+      <c r="B10" s="3">
+        <v>-1.128760392020467E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11">
         <v>1995</v>
       </c>
-      <c r="B3" s="3">
-        <v>0.16844999999999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4">
+      <c r="B11" s="3">
+        <v>9.2160859105373527E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12">
         <v>1996</v>
       </c>
-      <c r="B4" s="3">
-        <v>0.14020833333333335</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5">
+      <c r="B12" s="3">
+        <v>8.5586180972958781E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13">
         <v>1997</v>
       </c>
-      <c r="B5" s="3">
-        <v>0.13783333333333334</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6">
+      <c r="B13" s="3">
+        <v>0.13646101577698233</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14">
         <v>1998</v>
       </c>
-      <c r="B6" s="3">
-        <v>0.13462499999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7">
+      <c r="B14" s="3">
+        <v>0.12375668034877796</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15">
         <v>1999</v>
       </c>
-      <c r="B7" s="3">
-        <v>0.12176666666666668</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8">
+      <c r="B15" s="3">
+        <v>0.14456105557563292</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16">
         <v>2000</v>
       </c>
-      <c r="B8" s="3">
-        <v>0.11730833333333335</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9">
+      <c r="B16" s="3">
+        <v>1.2753813678981984E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17">
         <v>2001</v>
       </c>
-      <c r="B9" s="3">
-        <v>0.11916666666666666</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10">
+      <c r="B17" s="3">
+        <v>-2.1653766849825229E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18">
         <v>2002</v>
       </c>
-      <c r="B10" s="3">
-        <v>0.10499166666666665</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11">
+      <c r="B18" s="3">
+        <v>-3.0859935638595126E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19">
         <v>2003</v>
       </c>
-      <c r="B11" s="3">
-        <v>8.4600000000000009E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12">
+      <c r="B19" s="3">
+        <v>0.13021265938759741</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20">
         <v>2004</v>
       </c>
-      <c r="B12" s="3">
-        <v>8.0033333333333359E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13">
+      <c r="B20" s="3">
+        <v>0.11284628713988498</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21">
         <v>2005</v>
       </c>
-      <c r="B13" s="3">
-        <v>7.3700000000000002E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14">
+      <c r="B21" s="3">
+        <v>9.5700435119939753E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22">
         <v>2006</v>
       </c>
-      <c r="B14" s="3">
-        <v>7.1808333333333349E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15">
+      <c r="B22" s="3">
+        <v>8.3497102825924818E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23">
         <v>2007</v>
       </c>
-      <c r="B15" s="3">
-        <v>7.6283333333333328E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16">
+      <c r="B23" s="3">
+        <v>5.4036728450648441E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24">
         <v>2008</v>
       </c>
-      <c r="B16" s="3">
-        <v>9.0599999999999972E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17">
+      <c r="B24" s="3">
+        <v>-0.16066262517109864</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25">
         <v>2009</v>
       </c>
-      <c r="B17" s="3">
-        <v>0.10090833333333332</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18">
+      <c r="B25" s="3">
+        <v>8.877196143526267E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26">
         <v>2010</v>
       </c>
-      <c r="B18" s="3">
-        <v>9.2591666666666669E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19">
+      <c r="B26" s="3">
+        <v>5.6774110668480482E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27">
         <v>2011</v>
       </c>
-      <c r="B19" s="3">
-        <v>8.7499999999999981E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20">
+      <c r="B27" s="3">
+        <v>-2.7392490880683962E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28">
         <v>2012</v>
       </c>
-      <c r="B20" s="3">
-        <v>7.4383333333333329E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21">
+      <c r="B28" s="3">
+        <v>-2.2124513898473808E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29">
         <v>2013</v>
       </c>
-      <c r="B21" s="3">
-        <v>6.0299999999999999E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22">
+      <c r="B29" s="3">
+        <v>7.5335930021486197E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30">
         <v>2014</v>
       </c>
-      <c r="B22" s="3">
-        <v>4.9799999999999997E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23">
+      <c r="B30" s="3">
+        <v>7.9340966880817376E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31">
         <v>2015</v>
       </c>
-      <c r="B23" s="3">
-        <v>4.331666666666667E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24">
+      <c r="B31" s="3">
+        <v>4.2381070018058686E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32">
         <v>2016</v>
       </c>
-      <c r="B24" s="3">
-        <v>3.9683333333333334E-2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25">
+      <c r="B32" s="3">
+        <v>-4.8974784087532974E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33">
         <v>2017</v>
       </c>
-      <c r="B25" s="3">
-        <v>3.7991666666666667E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26">
+      <c r="B33" s="3">
+        <v>7.0170871889905673E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34">
         <v>2018</v>
       </c>
-      <c r="B26" s="3">
-        <v>3.7691666666666665E-2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27">
+      <c r="B34" s="3">
+        <v>2.840535022977253E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35">
         <v>2019</v>
       </c>
-      <c r="B27" s="3">
-        <v>3.6141666666666662E-2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28">
+      <c r="B35" s="3">
+        <v>6.3714730205470804E-3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36">
         <v>2020</v>
       </c>
-      <c r="B28" s="3">
-        <v>3.5466666666666667E-2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29">
+      <c r="B36" s="3">
+        <v>-7.3040697759606754E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37">
         <v>2021</v>
       </c>
-      <c r="B29" s="3">
-        <v>3.8266666666666664E-2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30">
+      <c r="B37" s="3">
+        <v>4.9303785520141474E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38">
         <v>2022</v>
       </c>
-      <c r="B30" s="3">
-        <v>6.0198436757189541E-2</v>
+      <c r="B38" s="3">
+        <v>4.6286405160227334E-2</v>
       </c>
     </row>
   </sheetData>
@@ -1921,11 +2044,11 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE5D1202-306C-4A3E-BE31-47D9872C9300}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF70C8B1-8A2A-4CB2-AE85-70911F99E869}">
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1933,236 +2056,236 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1994</v>
       </c>
       <c r="B2" s="3">
-        <v>0.15704228576200643</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.0198436757189541E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1995</v>
       </c>
       <c r="B3" s="3">
-        <v>0.22755833333333339</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.16844999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>1996</v>
       </c>
       <c r="B4" s="3">
-        <v>0.22240833333333332</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.14020833333333335</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>1997</v>
       </c>
       <c r="B5" s="3">
-        <v>0.22367499999999996</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.13783333333333334</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>1998</v>
       </c>
       <c r="B6" s="3">
-        <v>0.21951666666666669</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.13462499999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>1999</v>
       </c>
       <c r="B7" s="3">
-        <v>0.19584999999999997</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.12176666666666668</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>2000</v>
       </c>
       <c r="B8" s="3">
-        <v>0.18845833333333334</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.11730833333333335</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>2001</v>
       </c>
       <c r="B9" s="3">
-        <v>0.17802499999999999</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.11916666666666666</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>2002</v>
       </c>
       <c r="B10" s="3">
-        <v>0.15925000000000003</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.10499166666666665</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>2003</v>
       </c>
       <c r="B11" s="3">
-        <v>0.15108333333333335</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8.4600000000000009E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>2004</v>
       </c>
       <c r="B12" s="3">
-        <v>0.1561916666666667</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8.0033333333333359E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>2005</v>
       </c>
       <c r="B13" s="3">
-        <v>0.16120833333333334</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7.3700000000000002E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>2006</v>
       </c>
       <c r="B14" s="3">
-        <v>0.16125833333333334</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7.1808333333333349E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>2007</v>
       </c>
       <c r="B15" s="3">
-        <v>0.15259999999999999</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7.6283333333333328E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>2008</v>
       </c>
       <c r="B16" s="3">
-        <v>0.15983333333333333</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9.0599999999999972E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>2009</v>
       </c>
       <c r="B17" s="3">
-        <v>0.16043333333333332</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.10090833333333332</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>2010</v>
       </c>
       <c r="B18" s="3">
-        <v>0.16666666666666669</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9.2591666666666669E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>2011</v>
       </c>
       <c r="B19" s="3">
-        <v>0.16936666666666664</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8.7499999999999981E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>2012</v>
       </c>
       <c r="B20" s="3">
-        <v>0.17374999999999996</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7.4383333333333329E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>2013</v>
       </c>
       <c r="B21" s="3">
-        <v>0.17915</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.0299999999999999E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>2014</v>
       </c>
       <c r="B22" s="3">
-        <v>0.17576666666666668</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+        <v>4.9799999999999997E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>2015</v>
       </c>
       <c r="B23" s="3">
-        <v>0.17913333333333334</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+        <v>4.331666666666667E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>2016</v>
       </c>
       <c r="B24" s="3">
-        <v>0.17950833333333335</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+        <v>3.9683333333333334E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>2017</v>
       </c>
       <c r="B25" s="3">
-        <v>0.17944166666666667</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+        <v>3.7991666666666667E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>2018</v>
       </c>
       <c r="B26" s="3">
-        <v>0.18666666666666665</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+        <v>3.7691666666666665E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>2019</v>
       </c>
       <c r="B27" s="3">
-        <v>0.20248333333333332</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+        <v>3.6141666666666662E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>2020</v>
       </c>
       <c r="B28" s="3">
-        <v>0.20790000000000003</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+        <v>3.5466666666666667E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>2021</v>
       </c>
       <c r="B29" s="3">
-        <v>0.21439999999999998</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+        <v>3.8266666666666664E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>2022</v>
       </c>
       <c r="B30" s="3">
-        <v>0.15704228576200643</v>
+        <v>6.0198436757189541E-2</v>
       </c>
     </row>
   </sheetData>
@@ -2171,11 +2294,11 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4C9E94E-195D-449C-95FA-8827E1CD938F}">
-  <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE5D1202-306C-4A3E-BE31-47D9872C9300}">
+  <dimension ref="A1:B30"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2183,108 +2306,236 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2">
+        <v>1994</v>
+      </c>
+      <c r="B2" s="3">
+        <v>0.15704228576200643</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>1995</v>
+      </c>
+      <c r="B3" s="3">
+        <v>0.22755833333333339</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>1996</v>
+      </c>
+      <c r="B4" s="3">
+        <v>0.22240833333333332</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>1997</v>
+      </c>
+      <c r="B5" s="3">
+        <v>0.22367499999999996</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>1998</v>
+      </c>
+      <c r="B6" s="3">
+        <v>0.21951666666666669</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>1999</v>
+      </c>
+      <c r="B7" s="3">
+        <v>0.19584999999999997</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>2000</v>
+      </c>
+      <c r="B8" s="3">
+        <v>0.18845833333333334</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>2001</v>
+      </c>
+      <c r="B9" s="3">
+        <v>0.17802499999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>2002</v>
+      </c>
+      <c r="B10" s="3">
+        <v>0.15925000000000003</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>2003</v>
+      </c>
+      <c r="B11" s="3">
+        <v>0.15108333333333335</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>2004</v>
+      </c>
+      <c r="B12" s="3">
+        <v>0.1561916666666667</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>2005</v>
+      </c>
+      <c r="B13" s="3">
+        <v>0.16120833333333334</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>2006</v>
+      </c>
+      <c r="B14" s="3">
+        <v>0.16125833333333334</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>2007</v>
+      </c>
+      <c r="B15" s="3">
+        <v>0.15259999999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>2008</v>
+      </c>
+      <c r="B16" s="3">
+        <v>0.15983333333333333</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>2009</v>
+      </c>
+      <c r="B17" s="3">
+        <v>0.16043333333333332</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18">
         <v>2010</v>
       </c>
-      <c r="B2">
-        <v>9.0451221008231997</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3">
+      <c r="B18" s="3">
+        <v>0.16666666666666669</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19">
         <v>2011</v>
       </c>
-      <c r="B3" s="7">
-        <v>9.1220556745181991</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4">
+      <c r="B19" s="3">
+        <v>0.16936666666666664</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20">
         <v>2012</v>
       </c>
-      <c r="B4" s="7">
-        <v>8.9177939646201878</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5">
+      <c r="B20" s="3">
+        <v>0.17374999999999996</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21">
         <v>2013</v>
       </c>
-      <c r="B5" s="7">
-        <v>8.7106598984771573</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6">
+      <c r="B21" s="3">
+        <v>0.17915</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22">
         <v>2014</v>
       </c>
-      <c r="B6" s="7">
-        <v>8.58</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7">
+      <c r="B22" s="3">
+        <v>0.17576666666666668</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23">
         <v>2015</v>
       </c>
-      <c r="B7" s="7">
-        <v>8.7899999999999991</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8">
+      <c r="B23" s="3">
+        <v>0.17913333333333334</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24">
         <v>2016</v>
       </c>
-      <c r="B8" s="7">
-        <v>9.1360476663356494</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9">
+      <c r="B24" s="3">
+        <v>0.17950833333333335</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25">
         <v>2017</v>
       </c>
-      <c r="B9" s="7">
-        <v>9.2263056092843314</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10">
+      <c r="B25" s="3">
+        <v>0.17944166666666667</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26">
         <v>2018</v>
       </c>
-      <c r="B10" s="7">
-        <v>9.3767705382436262</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11">
+      <c r="B26" s="3">
+        <v>0.18666666666666665</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27">
         <v>2019</v>
       </c>
-      <c r="B11" s="7">
-        <v>9.6103896103896105</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12">
+      <c r="B27" s="3">
+        <v>0.20248333333333332</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28">
         <v>2020</v>
       </c>
-      <c r="B12" s="7">
-        <v>9.9724011039558409</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13">
+      <c r="B28" s="3">
+        <v>0.20790000000000003</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29">
         <v>2021</v>
       </c>
-      <c r="B13" s="7">
-        <v>9.9283154121863806</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14">
+      <c r="B29" s="3">
+        <v>0.21439999999999998</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30">
         <v>2022</v>
       </c>
-      <c r="B14" s="7">
-        <v>10.012761014679809</v>
+      <c r="B30" s="3">
+        <v>0.15704228576200643</v>
       </c>
     </row>
   </sheetData>
@@ -2293,11 +2544,133 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4C9E94E-195D-449C-95FA-8827E1CD938F}">
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>2010</v>
+      </c>
+      <c r="B2">
+        <v>9.0451221008231997</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2011</v>
+      </c>
+      <c r="B3" s="7">
+        <v>9.1220556745181991</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>2012</v>
+      </c>
+      <c r="B4" s="7">
+        <v>8.9177939646201878</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>2013</v>
+      </c>
+      <c r="B5" s="7">
+        <v>8.7106598984771573</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>2014</v>
+      </c>
+      <c r="B6" s="7">
+        <v>8.58</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>2015</v>
+      </c>
+      <c r="B7" s="7">
+        <v>8.7899999999999991</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>2016</v>
+      </c>
+      <c r="B8" s="7">
+        <v>9.1360476663356494</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>2017</v>
+      </c>
+      <c r="B9" s="7">
+        <v>9.2263056092843314</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>2018</v>
+      </c>
+      <c r="B10" s="7">
+        <v>9.3767705382436262</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>2019</v>
+      </c>
+      <c r="B11" s="7">
+        <v>9.6103896103896105</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>2020</v>
+      </c>
+      <c r="B12" s="7">
+        <v>9.9724011039558409</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>2021</v>
+      </c>
+      <c r="B13" s="7">
+        <v>9.9283154121863806</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>2022</v>
+      </c>
+      <c r="B14" s="7">
+        <v>10.012761014679809</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E8E4EE1-1BD6-4E11-9F6E-85D51F484400}">
   <dimension ref="A1:BG120"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>4</v>
       </c>
@@ -2364,8 +2737,11 @@
       <c r="BB1" s="4"/>
       <c r="BC1" s="4"/>
       <c r="BD1" s="4"/>
-    </row>
-    <row r="2" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="BF1" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:58" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
         <v>9</v>
       </c>
@@ -2405,8 +2781,11 @@
       <c r="BB2" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="3" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="BF2" s="13" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:58" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>15</v>
       </c>
@@ -2474,7 +2853,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -2549,7 +2928,7 @@
         <v>1.0242007015521464</v>
       </c>
     </row>
-    <row r="5" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>34</v>
       </c>
@@ -2598,7 +2977,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>51</v>
       </c>
@@ -2652,7 +3031,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:58" x14ac:dyDescent="0.35">
       <c r="E7" s="10">
         <f>E8-1</f>
         <v>1987</v>
@@ -2677,7 +3056,7 @@
       <c r="AS7" s="10"/>
       <c r="AT7" s="10"/>
     </row>
-    <row r="8" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>1988</v>
       </c>
@@ -2789,7 +3168,7 @@
         <v>3.7149797570850209</v>
       </c>
     </row>
-    <row r="9" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>1989</v>
       </c>
@@ -2946,7 +3325,7 @@
         <v>3.815384615384616</v>
       </c>
     </row>
-    <row r="10" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>1990</v>
       </c>
@@ -3105,7 +3484,7 @@
         <v>3.9157894736842116</v>
       </c>
     </row>
-    <row r="11" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>1991</v>
       </c>
@@ -3268,7 +3647,7 @@
         <v>4.2170040485829974</v>
       </c>
     </row>
-    <row r="12" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>1992</v>
       </c>
@@ -3431,7 +3810,7 @@
         <v>4.5182186234817827</v>
       </c>
     </row>
-    <row r="13" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>1993</v>
       </c>
@@ -3594,7 +3973,7 @@
         <v>4.6186234817813778</v>
       </c>
     </row>
-    <row r="14" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>1994</v>
       </c>
@@ -3757,7 +4136,7 @@
         <v>4.7190283400809738</v>
       </c>
     </row>
-    <row r="15" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>1995</v>
       </c>
@@ -3923,7 +4302,7 @@
         <v>4.8194331983805689</v>
       </c>
     </row>
-    <row r="16" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>1996</v>
       </c>
@@ -4089,7 +4468,7 @@
         <v>5.1206477732793543</v>
       </c>
     </row>
-    <row r="17" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>1997</v>
       </c>
@@ -4255,7 +4634,7 @@
         <v>5.2210526315789503</v>
       </c>
     </row>
-    <row r="18" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>1998</v>
       </c>
@@ -4421,7 +4800,7 @@
         <v>5.4218623481781414</v>
       </c>
     </row>
-    <row r="19" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>1999</v>
       </c>
@@ -4587,7 +4966,7 @@
         <v>5.4218623481781414</v>
       </c>
     </row>
-    <row r="20" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>2000</v>
       </c>
@@ -4753,7 +5132,7 @@
         <v>5.5222672064777356</v>
       </c>
     </row>
-    <row r="21" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>2001</v>
       </c>
@@ -4905,7 +5284,7 @@
         <v>5.7230769230769258</v>
       </c>
     </row>
-    <row r="22" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>2002</v>
       </c>
@@ -5057,7 +5436,7 @@
         <v>5.9238866396761161</v>
       </c>
     </row>
-    <row r="23" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>2003</v>
       </c>
@@ -5209,7 +5588,7 @@
         <v>6.0242914979757103</v>
       </c>
     </row>
-    <row r="24" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>2004</v>
       </c>
@@ -5361,7 +5740,7 @@
         <v>6.2251012145749014</v>
       </c>
     </row>
-    <row r="25" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <v>2005</v>
       </c>
@@ -5513,7 +5892,7 @@
         <v>6.5263157894736867</v>
       </c>
     </row>
-    <row r="26" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>2006</v>
       </c>
@@ -5665,7 +6044,7 @@
         <v>6.8275303643724712</v>
       </c>
     </row>
-    <row r="27" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <v>2007</v>
       </c>
@@ -5817,7 +6196,7 @@
         <v>7.0283400809716614</v>
       </c>
     </row>
-    <row r="28" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <v>2008</v>
       </c>
@@ -5983,7 +6362,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="29" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <v>2009</v>
       </c>
@@ -6148,7 +6527,7 @@
         <v>1969</v>
       </c>
     </row>
-    <row r="30" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <v>2010</v>
       </c>
@@ -6311,7 +6690,7 @@
         <v>1970</v>
       </c>
     </row>
-    <row r="31" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>2011</v>
       </c>
@@ -6474,7 +6853,7 @@
         <v>1971</v>
       </c>
     </row>
-    <row r="32" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <v>2012</v>
       </c>
@@ -6637,7 +7016,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="33" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>2013</v>
       </c>
@@ -6800,7 +7179,7 @@
         <v>1973</v>
       </c>
     </row>
-    <row r="34" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <v>2014</v>
       </c>
@@ -6963,7 +7342,7 @@
         <v>1974</v>
       </c>
     </row>
-    <row r="35" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
         <v>2015</v>
       </c>
@@ -7111,7 +7490,7 @@
         <v>1975</v>
       </c>
     </row>
-    <row r="36" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
         <v>2016</v>
       </c>
@@ -7233,7 +7612,7 @@
         <v>1976</v>
       </c>
     </row>
-    <row r="37" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
         <v>2017</v>
       </c>
@@ -7343,7 +7722,7 @@
         <v>1977</v>
       </c>
     </row>
-    <row r="38" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
         <v>2018</v>
       </c>
@@ -7453,7 +7832,7 @@
         <v>1978</v>
       </c>
     </row>
-    <row r="39" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
         <v>2019</v>
       </c>
@@ -7563,7 +7942,7 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="40" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
         <v>2020</v>
       </c>
@@ -7673,7 +8052,7 @@
         <v>1980</v>
       </c>
     </row>
-    <row r="41" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
         <v>2021</v>
       </c>
@@ -7783,7 +8162,7 @@
         <v>1981</v>
       </c>
     </row>
-    <row r="42" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A42">
         <f t="shared" ref="A42:A46" si="57">A41+1</f>
         <v>2022</v>
@@ -7894,7 +8273,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="43" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A43">
         <f t="shared" si="57"/>
         <v>2023</v>
@@ -8002,7 +8381,7 @@
         <v>1983</v>
       </c>
     </row>
-    <row r="44" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A44">
         <f t="shared" si="57"/>
         <v>2024</v>
@@ -8088,7 +8467,7 @@
         <v>1984</v>
       </c>
     </row>
-    <row r="45" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A45">
         <f t="shared" si="57"/>
         <v>2025</v>
@@ -8165,7 +8544,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="46" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A46">
         <f t="shared" si="57"/>
         <v>2026</v>
@@ -8242,7 +8621,7 @@
         <v>1986</v>
       </c>
     </row>
-    <row r="47" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:59" x14ac:dyDescent="0.35">
       <c r="E47" s="10">
         <f>E46+1</f>
         <v>2027</v>
@@ -8309,7 +8688,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="48" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:59" x14ac:dyDescent="0.35">
       <c r="P48" s="6">
         <v>40148</v>
       </c>
@@ -8367,7 +8746,7 @@
         <v>1988</v>
       </c>
     </row>
-    <row r="49" spans="16:59" x14ac:dyDescent="0.25">
+    <row r="49" spans="16:59" x14ac:dyDescent="0.35">
       <c r="P49" s="6">
         <v>40513</v>
       </c>
@@ -8425,7 +8804,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="50" spans="16:59" x14ac:dyDescent="0.25">
+    <row r="50" spans="16:59" x14ac:dyDescent="0.35">
       <c r="P50" s="6">
         <v>40878</v>
       </c>
@@ -8485,7 +8864,7 @@
         <v>1990</v>
       </c>
     </row>
-    <row r="51" spans="16:59" x14ac:dyDescent="0.25">
+    <row r="51" spans="16:59" x14ac:dyDescent="0.35">
       <c r="P51" s="6">
         <v>41244</v>
       </c>
@@ -8545,7 +8924,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="52" spans="16:59" x14ac:dyDescent="0.25">
+    <row r="52" spans="16:59" x14ac:dyDescent="0.35">
       <c r="P52" s="6">
         <v>41609</v>
       </c>
@@ -8593,7 +8972,7 @@
         <v>1992</v>
       </c>
     </row>
-    <row r="53" spans="16:59" x14ac:dyDescent="0.25">
+    <row r="53" spans="16:59" x14ac:dyDescent="0.35">
       <c r="P53" s="6">
         <v>41974</v>
       </c>
@@ -8641,7 +9020,7 @@
         <v>1993</v>
       </c>
     </row>
-    <row r="54" spans="16:59" x14ac:dyDescent="0.25">
+    <row r="54" spans="16:59" x14ac:dyDescent="0.35">
       <c r="P54" s="6">
         <v>42339</v>
       </c>
@@ -8689,7 +9068,7 @@
         <v>1994</v>
       </c>
     </row>
-    <row r="55" spans="16:59" x14ac:dyDescent="0.25">
+    <row r="55" spans="16:59" x14ac:dyDescent="0.35">
       <c r="P55" s="6">
         <v>42705</v>
       </c>
@@ -8737,7 +9116,7 @@
         <v>1995</v>
       </c>
     </row>
-    <row r="56" spans="16:59" x14ac:dyDescent="0.25">
+    <row r="56" spans="16:59" x14ac:dyDescent="0.35">
       <c r="P56" s="6">
         <v>43070</v>
       </c>
@@ -8785,7 +9164,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="57" spans="16:59" x14ac:dyDescent="0.25">
+    <row r="57" spans="16:59" x14ac:dyDescent="0.35">
       <c r="P57" s="6">
         <v>43435</v>
       </c>
@@ -8833,7 +9212,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="58" spans="16:59" x14ac:dyDescent="0.25">
+    <row r="58" spans="16:59" x14ac:dyDescent="0.35">
       <c r="P58" s="6">
         <v>43800</v>
       </c>
@@ -8881,7 +9260,7 @@
         <v>1998</v>
       </c>
     </row>
-    <row r="59" spans="16:59" x14ac:dyDescent="0.25">
+    <row r="59" spans="16:59" x14ac:dyDescent="0.35">
       <c r="P59" s="6">
         <v>44166</v>
       </c>
@@ -8929,7 +9308,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="60" spans="16:59" x14ac:dyDescent="0.25">
+    <row r="60" spans="16:59" x14ac:dyDescent="0.35">
       <c r="P60" s="6">
         <v>44531</v>
       </c>
@@ -8977,7 +9356,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="61" spans="16:59" x14ac:dyDescent="0.25">
+    <row r="61" spans="16:59" x14ac:dyDescent="0.35">
       <c r="AV61">
         <v>2001</v>
       </c>
@@ -9015,7 +9394,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="62" spans="16:59" x14ac:dyDescent="0.25">
+    <row r="62" spans="16:59" x14ac:dyDescent="0.35">
       <c r="AV62">
         <v>2002</v>
       </c>
@@ -9053,7 +9432,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="63" spans="16:59" x14ac:dyDescent="0.25">
+    <row r="63" spans="16:59" x14ac:dyDescent="0.35">
       <c r="AV63">
         <v>2003</v>
       </c>
@@ -9091,7 +9470,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="64" spans="16:59" x14ac:dyDescent="0.25">
+    <row r="64" spans="16:59" x14ac:dyDescent="0.35">
       <c r="AV64">
         <v>2004</v>
       </c>
@@ -9129,7 +9508,7 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="65" spans="48:59" x14ac:dyDescent="0.25">
+    <row r="65" spans="48:59" x14ac:dyDescent="0.35">
       <c r="AV65">
         <v>2005</v>
       </c>
@@ -9167,7 +9546,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="66" spans="48:59" x14ac:dyDescent="0.25">
+    <row r="66" spans="48:59" x14ac:dyDescent="0.35">
       <c r="AV66">
         <v>2006</v>
       </c>
@@ -9205,7 +9584,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="67" spans="48:59" x14ac:dyDescent="0.25">
+    <row r="67" spans="48:59" x14ac:dyDescent="0.35">
       <c r="AV67">
         <v>2007</v>
       </c>
@@ -9243,7 +9622,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="68" spans="48:59" x14ac:dyDescent="0.25">
+    <row r="68" spans="48:59" x14ac:dyDescent="0.35">
       <c r="AV68">
         <v>2008</v>
       </c>
@@ -9281,7 +9660,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="69" spans="48:59" x14ac:dyDescent="0.25">
+    <row r="69" spans="48:59" x14ac:dyDescent="0.35">
       <c r="AV69">
         <v>2009</v>
       </c>
@@ -9319,7 +9698,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="70" spans="48:59" x14ac:dyDescent="0.25">
+    <row r="70" spans="48:59" x14ac:dyDescent="0.35">
       <c r="AV70">
         <v>2010</v>
       </c>
@@ -9357,7 +9736,7 @@
         <v>2010</v>
       </c>
     </row>
-    <row r="71" spans="48:59" x14ac:dyDescent="0.25">
+    <row r="71" spans="48:59" x14ac:dyDescent="0.35">
       <c r="AV71">
         <v>2011</v>
       </c>
@@ -9395,7 +9774,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="72" spans="48:59" x14ac:dyDescent="0.25">
+    <row r="72" spans="48:59" x14ac:dyDescent="0.35">
       <c r="AV72">
         <v>2012</v>
       </c>
@@ -9433,7 +9812,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="73" spans="48:59" x14ac:dyDescent="0.25">
+    <row r="73" spans="48:59" x14ac:dyDescent="0.35">
       <c r="AV73">
         <v>2013</v>
       </c>
@@ -9471,7 +9850,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="74" spans="48:59" x14ac:dyDescent="0.25">
+    <row r="74" spans="48:59" x14ac:dyDescent="0.35">
       <c r="AV74">
         <v>2014</v>
       </c>
@@ -9509,7 +9888,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="75" spans="48:59" x14ac:dyDescent="0.25">
+    <row r="75" spans="48:59" x14ac:dyDescent="0.35">
       <c r="AV75">
         <v>2015</v>
       </c>
@@ -9547,7 +9926,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="76" spans="48:59" x14ac:dyDescent="0.25">
+    <row r="76" spans="48:59" x14ac:dyDescent="0.35">
       <c r="AV76">
         <v>2016</v>
       </c>
@@ -9585,7 +9964,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="77" spans="48:59" x14ac:dyDescent="0.25">
+    <row r="77" spans="48:59" x14ac:dyDescent="0.35">
       <c r="AV77">
         <v>2017</v>
       </c>
@@ -9623,7 +10002,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="78" spans="48:59" x14ac:dyDescent="0.25">
+    <row r="78" spans="48:59" x14ac:dyDescent="0.35">
       <c r="AV78">
         <v>2018</v>
       </c>
@@ -9661,7 +10040,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="79" spans="48:59" x14ac:dyDescent="0.25">
+    <row r="79" spans="48:59" x14ac:dyDescent="0.35">
       <c r="AV79">
         <v>2019</v>
       </c>
@@ -9699,7 +10078,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="80" spans="48:59" x14ac:dyDescent="0.25">
+    <row r="80" spans="48:59" x14ac:dyDescent="0.35">
       <c r="AV80">
         <v>2020</v>
       </c>
@@ -9737,7 +10116,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="81" spans="48:59" x14ac:dyDescent="0.25">
+    <row r="81" spans="48:59" x14ac:dyDescent="0.35">
       <c r="AV81">
         <v>2021</v>
       </c>
@@ -9775,7 +10154,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="82" spans="48:59" x14ac:dyDescent="0.25">
+    <row r="82" spans="48:59" x14ac:dyDescent="0.35">
       <c r="AV82">
         <f>AV81+1</f>
         <v>2022</v>
@@ -9789,7 +10168,7 @@
         <v>99.757148331179067</v>
       </c>
     </row>
-    <row r="83" spans="48:59" x14ac:dyDescent="0.25">
+    <row r="83" spans="48:59" x14ac:dyDescent="0.35">
       <c r="AV83">
         <f t="shared" ref="AV83:AV120" si="64">AV82+1</f>
         <v>2023</v>
@@ -9803,7 +10182,7 @@
         <v>102.17134130563514</v>
       </c>
     </row>
-    <row r="84" spans="48:59" x14ac:dyDescent="0.25">
+    <row r="84" spans="48:59" x14ac:dyDescent="0.35">
       <c r="AV84">
         <f t="shared" si="64"/>
         <v>2024</v>
@@ -9817,7 +10196,7 @@
         <v>104.64395944375532</v>
       </c>
     </row>
-    <row r="85" spans="48:59" x14ac:dyDescent="0.25">
+    <row r="85" spans="48:59" x14ac:dyDescent="0.35">
       <c r="AV85">
         <f t="shared" si="64"/>
         <v>2025</v>
@@ -9831,7 +10210,7 @@
         <v>107.17641667548857</v>
       </c>
     </row>
-    <row r="86" spans="48:59" x14ac:dyDescent="0.25">
+    <row r="86" spans="48:59" x14ac:dyDescent="0.35">
       <c r="AV86">
         <f t="shared" si="64"/>
         <v>2026</v>
@@ -9845,7 +10224,7 @@
         <v>109.77016114888056</v>
       </c>
     </row>
-    <row r="87" spans="48:59" x14ac:dyDescent="0.25">
+    <row r="87" spans="48:59" x14ac:dyDescent="0.35">
       <c r="AV87">
         <f t="shared" si="64"/>
         <v>2027</v>
@@ -9859,7 +10238,7 @@
         <v>112.42667605817564</v>
       </c>
     </row>
-    <row r="88" spans="48:59" x14ac:dyDescent="0.25">
+    <row r="88" spans="48:59" x14ac:dyDescent="0.35">
       <c r="AV88">
         <f t="shared" si="64"/>
         <v>2028</v>
@@ -9873,7 +10252,7 @@
         <v>115.1474804919594</v>
       </c>
     </row>
-    <row r="89" spans="48:59" x14ac:dyDescent="0.25">
+    <row r="89" spans="48:59" x14ac:dyDescent="0.35">
       <c r="AV89">
         <f t="shared" si="64"/>
         <v>2029</v>
@@ -9887,7 +10266,7 @@
         <v>117.9341303018269</v>
       </c>
     </row>
-    <row r="90" spans="48:59" x14ac:dyDescent="0.25">
+    <row r="90" spans="48:59" x14ac:dyDescent="0.35">
       <c r="AV90">
         <f t="shared" si="64"/>
         <v>2030</v>
@@ -9901,7 +10280,7 @@
         <v>120.78821899207334</v>
       </c>
     </row>
-    <row r="91" spans="48:59" x14ac:dyDescent="0.25">
+    <row r="91" spans="48:59" x14ac:dyDescent="0.35">
       <c r="AV91">
         <f t="shared" si="64"/>
         <v>2031</v>
@@ -9915,7 +10294,7 @@
         <v>123.7113786309158</v>
       </c>
     </row>
-    <row r="92" spans="48:59" x14ac:dyDescent="0.25">
+    <row r="92" spans="48:59" x14ac:dyDescent="0.35">
       <c r="AV92">
         <f t="shared" si="64"/>
         <v>2032</v>
@@ -9929,7 +10308,7 @@
         <v>126.70528078376718</v>
       </c>
     </row>
-    <row r="93" spans="48:59" x14ac:dyDescent="0.25">
+    <row r="93" spans="48:59" x14ac:dyDescent="0.35">
       <c r="AV93">
         <f t="shared" si="64"/>
         <v>2033</v>
@@ -9943,7 +10322,7 @@
         <v>129.77163746909605</v>
       </c>
     </row>
-    <row r="94" spans="48:59" x14ac:dyDescent="0.25">
+    <row r="94" spans="48:59" x14ac:dyDescent="0.35">
       <c r="AV94">
         <f t="shared" si="64"/>
         <v>2034</v>
@@ -9957,7 +10336,7 @@
         <v>132.912202137419</v>
       </c>
     </row>
-    <row r="95" spans="48:59" x14ac:dyDescent="0.25">
+    <row r="95" spans="48:59" x14ac:dyDescent="0.35">
       <c r="AV95">
         <f t="shared" si="64"/>
         <v>2035</v>
@@ -9971,7 +10350,7 @@
         <v>136.12877067398526</v>
       </c>
     </row>
-    <row r="96" spans="48:59" x14ac:dyDescent="0.25">
+    <row r="96" spans="48:59" x14ac:dyDescent="0.35">
       <c r="AV96">
         <f t="shared" si="64"/>
         <v>2036</v>
@@ -9985,7 +10364,7 @@
         <v>139.42318242572699</v>
       </c>
     </row>
-    <row r="97" spans="48:51" x14ac:dyDescent="0.25">
+    <row r="97" spans="48:51" x14ac:dyDescent="0.35">
       <c r="AV97">
         <f t="shared" si="64"/>
         <v>2037</v>
@@ -9999,7 +10378,7 @@
         <v>142.79732125306251</v>
       </c>
     </row>
-    <row r="98" spans="48:51" x14ac:dyDescent="0.25">
+    <row r="98" spans="48:51" x14ac:dyDescent="0.35">
       <c r="AV98">
         <f t="shared" si="64"/>
         <v>2038</v>
@@ -10013,7 +10392,7 @@
         <v>146.25311660715386</v>
       </c>
     </row>
-    <row r="99" spans="48:51" x14ac:dyDescent="0.25">
+    <row r="99" spans="48:51" x14ac:dyDescent="0.35">
       <c r="AV99">
         <f t="shared" si="64"/>
         <v>2039</v>
@@ -10027,7 +10406,7 @@
         <v>149.79254463323488</v>
       </c>
     </row>
-    <row r="100" spans="48:51" x14ac:dyDescent="0.25">
+    <row r="100" spans="48:51" x14ac:dyDescent="0.35">
       <c r="AV100">
         <f t="shared" si="64"/>
         <v>2040</v>
@@ -10041,7 +10420,7 @@
         <v>153.41762930064039</v>
       </c>
     </row>
-    <row r="101" spans="48:51" x14ac:dyDescent="0.25">
+    <row r="101" spans="48:51" x14ac:dyDescent="0.35">
       <c r="AV101">
         <f t="shared" si="64"/>
         <v>2041</v>
@@ -10055,7 +10434,7 @@
         <v>157.13044356018301</v>
       </c>
     </row>
-    <row r="102" spans="48:51" x14ac:dyDescent="0.25">
+    <row r="102" spans="48:51" x14ac:dyDescent="0.35">
       <c r="AV102">
         <f t="shared" si="64"/>
         <v>2042</v>
@@ -10069,7 +10448,7 @@
         <v>160.93311052953939</v>
       </c>
     </row>
-    <row r="103" spans="48:51" x14ac:dyDescent="0.25">
+    <row r="103" spans="48:51" x14ac:dyDescent="0.35">
       <c r="AV103">
         <f t="shared" si="64"/>
         <v>2043</v>
@@ -10083,7 +10462,7 @@
         <v>164.82780470732337</v>
       </c>
     </row>
-    <row r="104" spans="48:51" x14ac:dyDescent="0.25">
+    <row r="104" spans="48:51" x14ac:dyDescent="0.35">
       <c r="AV104">
         <f t="shared" si="64"/>
         <v>2044</v>
@@ -10097,7 +10476,7 @@
         <v>168.81675321654077</v>
       </c>
     </row>
-    <row r="105" spans="48:51" x14ac:dyDescent="0.25">
+    <row r="105" spans="48:51" x14ac:dyDescent="0.35">
       <c r="AV105">
         <f t="shared" si="64"/>
         <v>2045</v>
@@ -10111,7 +10490,7 @@
         <v>172.90223707813664</v>
       </c>
     </row>
-    <row r="106" spans="48:51" x14ac:dyDescent="0.25">
+    <row r="106" spans="48:51" x14ac:dyDescent="0.35">
       <c r="AV106">
         <f t="shared" si="64"/>
         <v>2046</v>
@@ -10125,7 +10504,7 @@
         <v>177.08659251536309</v>
       </c>
     </row>
-    <row r="107" spans="48:51" x14ac:dyDescent="0.25">
+    <row r="107" spans="48:51" x14ac:dyDescent="0.35">
       <c r="AV107">
         <f t="shared" si="64"/>
         <v>2047</v>
@@ -10139,7 +10518,7 @@
         <v>181.37221228971399</v>
       </c>
     </row>
-    <row r="108" spans="48:51" x14ac:dyDescent="0.25">
+    <row r="108" spans="48:51" x14ac:dyDescent="0.35">
       <c r="AV108">
         <f t="shared" si="64"/>
         <v>2048</v>
@@ -10153,7 +10532,7 @@
         <v>185.76154706918993</v>
       </c>
     </row>
-    <row r="109" spans="48:51" x14ac:dyDescent="0.25">
+    <row r="109" spans="48:51" x14ac:dyDescent="0.35">
       <c r="AV109">
         <f t="shared" si="64"/>
         <v>2049</v>
@@ -10167,7 +10546,7 @@
         <v>190.25710682967642</v>
       </c>
     </row>
-    <row r="110" spans="48:51" x14ac:dyDescent="0.25">
+    <row r="110" spans="48:51" x14ac:dyDescent="0.35">
       <c r="AV110">
         <f t="shared" si="64"/>
         <v>2050</v>
@@ -10181,7 +10560,7 @@
         <v>194.86146229023626</v>
       </c>
     </row>
-    <row r="111" spans="48:51" x14ac:dyDescent="0.25">
+    <row r="111" spans="48:51" x14ac:dyDescent="0.35">
       <c r="AV111">
         <f t="shared" si="64"/>
         <v>2051</v>
@@ -10195,7 +10574,7 @@
         <v>199.57724638313712</v>
       </c>
     </row>
-    <row r="112" spans="48:51" x14ac:dyDescent="0.25">
+    <row r="112" spans="48:51" x14ac:dyDescent="0.35">
       <c r="AV112">
         <f t="shared" si="64"/>
         <v>2052</v>
@@ -10209,7 +10588,7 @@
         <v>204.40715575945461</v>
       </c>
     </row>
-    <row r="113" spans="48:51" x14ac:dyDescent="0.25">
+    <row r="113" spans="48:51" x14ac:dyDescent="0.35">
       <c r="AV113">
         <f t="shared" si="64"/>
         <v>2053</v>
@@ -10223,7 +10602,7 @@
         <v>209.35395233111228</v>
       </c>
     </row>
-    <row r="114" spans="48:51" x14ac:dyDescent="0.25">
+    <row r="114" spans="48:51" x14ac:dyDescent="0.35">
       <c r="AV114">
         <f t="shared" si="64"/>
         <v>2054</v>
@@ -10237,7 +10616,7 @@
         <v>214.42046485023982</v>
       </c>
     </row>
-    <row r="115" spans="48:51" x14ac:dyDescent="0.25">
+    <row r="115" spans="48:51" x14ac:dyDescent="0.35">
       <c r="AV115">
         <f t="shared" si="64"/>
         <v>2055</v>
@@ -10251,7 +10630,7 @@
         <v>219.60959052675298</v>
       </c>
     </row>
-    <row r="116" spans="48:51" x14ac:dyDescent="0.25">
+    <row r="116" spans="48:51" x14ac:dyDescent="0.35">
       <c r="AV116">
         <f t="shared" si="64"/>
         <v>2056</v>
@@ -10265,7 +10644,7 @@
         <v>224.92429668508001</v>
       </c>
     </row>
-    <row r="117" spans="48:51" x14ac:dyDescent="0.25">
+    <row r="117" spans="48:51" x14ac:dyDescent="0.35">
       <c r="AV117">
         <f t="shared" si="64"/>
         <v>2057</v>
@@ -10279,7 +10658,7 @@
         <v>230.36762246098209</v>
       </c>
     </row>
-    <row r="118" spans="48:51" x14ac:dyDescent="0.25">
+    <row r="118" spans="48:51" x14ac:dyDescent="0.35">
       <c r="AV118">
         <f t="shared" si="64"/>
         <v>2058</v>
@@ -10293,7 +10672,7 @@
         <v>235.9426805394379</v>
       </c>
     </row>
-    <row r="119" spans="48:51" x14ac:dyDescent="0.25">
+    <row r="119" spans="48:51" x14ac:dyDescent="0.35">
       <c r="AV119">
         <f t="shared" si="64"/>
         <v>2059</v>
@@ -10307,7 +10686,7 @@
         <v>241.65265893458633</v>
       </c>
     </row>
-    <row r="120" spans="48:51" x14ac:dyDescent="0.25">
+    <row r="120" spans="48:51" x14ac:dyDescent="0.35">
       <c r="AV120">
         <f t="shared" si="64"/>
         <v>2060</v>
@@ -10326,12 +10705,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB137BA4-4035-472D-AA2B-29C110ABC52B}">
   <dimension ref="A1:B74"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10339,7 +10718,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1988</v>
       </c>
@@ -10347,7 +10726,7 @@
         <v>49.6</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1989</v>
       </c>
@@ -10355,7 +10734,7 @@
         <v>52.2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>1990</v>
       </c>
@@ -10363,7 +10742,7 @@
         <v>55.9</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>1991</v>
       </c>
@@ -10371,7 +10750,7 @@
         <v>60.1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>1992</v>
       </c>
@@ -10379,7 +10758,7 @@
         <v>62.6</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>1993</v>
       </c>
@@ -10387,7 +10766,7 @@
         <v>64.2</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>1994</v>
       </c>
@@ -10395,7 +10774,7 @@
         <v>65.5</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>1995</v>
       </c>
@@ -10403,7 +10782,7 @@
         <v>67.2</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>1996</v>
       </c>
@@ -10411,7 +10790,7 @@
         <v>68.8</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>1997</v>
       </c>
@@ -10419,7 +10798,7 @@
         <v>70.099999999999994</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>1998</v>
       </c>
@@ -10427,7 +10806,7 @@
         <v>71.2</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>1999</v>
       </c>
@@ -10435,7 +10814,7 @@
         <v>72.099999999999994</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>2000</v>
       </c>
@@ -10443,7 +10822,7 @@
         <v>72.7</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>2001</v>
       </c>
@@ -10451,7 +10830,7 @@
         <v>73.599999999999994</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>2002</v>
       </c>
@@ -10459,7 +10838,7 @@
         <v>74.5</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>2003</v>
       </c>
@@ -10467,7 +10846,7 @@
         <v>75.5</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>2004</v>
       </c>
@@ -10475,7 +10854,7 @@
         <v>76.5</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>2005</v>
       </c>
@@ -10483,7 +10862,7 @@
         <v>78.099999999999994</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>2006</v>
       </c>
@@ -10491,7 +10870,7 @@
         <v>79.900000000000006</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>2007</v>
       </c>
@@ -10499,7 +10878,7 @@
         <v>81.8</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>2008</v>
       </c>
@@ -10507,7 +10886,7 @@
         <v>84.7</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>2009</v>
       </c>
@@ -10515,7 +10894,7 @@
         <v>86.6</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>2010</v>
       </c>
@@ -10523,7 +10902,7 @@
         <v>89.4</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>2011</v>
       </c>
@@ -10531,7 +10910,7 @@
         <v>93.4</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>2012</v>
       </c>
@@ -10539,7 +10918,7 @@
         <v>96.1</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>2013</v>
       </c>
@@ -10547,7 +10926,7 @@
         <v>98.5</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>2014</v>
       </c>
@@ -10555,7 +10934,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>2015</v>
       </c>
@@ -10563,7 +10942,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>2016</v>
       </c>
@@ -10571,7 +10950,7 @@
         <v>100.7</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>2017</v>
       </c>
@@ -10579,7 +10958,7 @@
         <v>103.4</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>2018</v>
       </c>
@@ -10587,7 +10966,7 @@
         <v>105.9</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>2019</v>
       </c>
@@ -10595,7 +10974,7 @@
         <v>107.8</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>2020</v>
       </c>
@@ -10603,7 +10982,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>2021</v>
       </c>
@@ -10611,7 +10990,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>2022</v>
       </c>
@@ -10619,7 +10998,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>2023</v>
       </c>
@@ -10627,7 +11006,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>2024</v>
       </c>
@@ -10635,7 +11014,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>2025</v>
       </c>
@@ -10643,7 +11022,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>2026</v>
       </c>
@@ -10651,7 +11030,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>2027</v>
       </c>
@@ -10659,7 +11038,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>2028</v>
       </c>
@@ -10667,7 +11046,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>2029</v>
       </c>
@@ -10675,7 +11054,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>2030</v>
       </c>
@@ -10683,7 +11062,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>2031</v>
       </c>
@@ -10691,7 +11070,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>2032</v>
       </c>
@@ -10699,7 +11078,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>2033</v>
       </c>
@@ -10707,7 +11086,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>2034</v>
       </c>
@@ -10715,7 +11094,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>2035</v>
       </c>
@@ -10723,7 +11102,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>2036</v>
       </c>
@@ -10731,7 +11110,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>2037</v>
       </c>
@@ -10739,7 +11118,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>2038</v>
       </c>
@@ -10747,7 +11126,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>2039</v>
       </c>
@@ -10755,7 +11134,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>2040</v>
       </c>
@@ -10763,7 +11142,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>2041</v>
       </c>
@@ -10771,7 +11150,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>2042</v>
       </c>
@@ -10779,7 +11158,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>2043</v>
       </c>
@@ -10787,7 +11166,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>2044</v>
       </c>
@@ -10795,7 +11174,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>2045</v>
       </c>
@@ -10803,7 +11182,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>2046</v>
       </c>
@@ -10811,7 +11190,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>2047</v>
       </c>
@@ -10819,7 +11198,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>2048</v>
       </c>
@@ -10827,7 +11206,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>2049</v>
       </c>
@@ -10835,7 +11214,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>2050</v>
       </c>
@@ -10843,7 +11222,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>2051</v>
       </c>
@@ -10851,7 +11230,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>2052</v>
       </c>
@@ -10859,7 +11238,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>2053</v>
       </c>
@@ -10867,7 +11246,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>2054</v>
       </c>
@@ -10875,7 +11254,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>2055</v>
       </c>
@@ -10883,7 +11262,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>2056</v>
       </c>
@@ -10891,7 +11270,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>2057</v>
       </c>
@@ -10899,7 +11278,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>2058</v>
       </c>
@@ -10907,7 +11286,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>2059</v>
       </c>
@@ -10915,7 +11294,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>2060</v>
       </c>
@@ -10931,9 +11310,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6878765F-1722-41F9-8BBC-D6A1331F5260}">
   <dimension ref="A1:B32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10941,7 +11320,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>2010</v>
       </c>
@@ -10949,7 +11328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2011</v>
       </c>
@@ -10957,7 +11336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2012</v>
       </c>
@@ -10965,7 +11344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>2013</v>
       </c>
@@ -10973,7 +11352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>2014</v>
       </c>
@@ -10981,7 +11360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>2015</v>
       </c>
@@ -10989,7 +11368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>2016</v>
       </c>
@@ -10997,7 +11376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>2017</v>
       </c>
@@ -11005,7 +11384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>2018</v>
       </c>
@@ -11013,7 +11392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>2019</v>
       </c>
@@ -11021,7 +11400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>2020</v>
       </c>
@@ -11029,7 +11408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>2021</v>
       </c>
@@ -11037,7 +11416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>2022</v>
       </c>
@@ -11045,7 +11424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>2023</v>
       </c>
@@ -11053,7 +11432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>2024</v>
       </c>
@@ -11061,7 +11440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>2025</v>
       </c>
@@ -11069,7 +11448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>2026</v>
       </c>
@@ -11077,7 +11456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>2027</v>
       </c>
@@ -11085,7 +11464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>2028</v>
       </c>
@@ -11093,7 +11472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>2029</v>
       </c>
@@ -11101,7 +11480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>2030</v>
       </c>
@@ -11109,7 +11488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>2031</v>
       </c>
@@ -11117,7 +11496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>2032</v>
       </c>
@@ -11125,7 +11504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>2033</v>
       </c>
@@ -11133,7 +11512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>2034</v>
       </c>
@@ -11141,7 +11520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>2035</v>
       </c>
@@ -11149,7 +11528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>2036</v>
       </c>
@@ -11157,7 +11536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>2037</v>
       </c>
@@ -11165,7 +11544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>2038</v>
       </c>
@@ -11173,7 +11552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>2039</v>
       </c>
@@ -11181,7 +11560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>2040</v>
       </c>
@@ -11197,9 +11576,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D18E90C-6D91-4744-9FCB-A05B59544AB8}">
   <dimension ref="A1:F62"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -11213,7 +11592,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>2010</v>
       </c>
@@ -11227,7 +11606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2011</v>
       </c>
@@ -11241,7 +11620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2012</v>
       </c>
@@ -11255,7 +11634,7 @@
         <v>-0.68042582690000331</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>2013</v>
       </c>
@@ -11269,7 +11648,7 @@
         <v>-0.67229930191496556</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>2014</v>
       </c>
@@ -11283,7 +11662,7 @@
         <v>-0.67897363322872639</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>2015</v>
       </c>
@@ -11297,7 +11676,7 @@
         <v>-0.66203073162886494</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>2016</v>
       </c>
@@ -11311,7 +11690,7 @@
         <v>-0.65127749552133463</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>2017</v>
       </c>
@@ -11325,7 +11704,7 @@
         <v>-0.62856645997943639</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>2018</v>
       </c>
@@ -11339,7 +11718,7 @@
         <v>-0.62262883931939683</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>2019</v>
       </c>
@@ -11353,7 +11732,7 @@
         <v>-0.61386966551793498</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>2020</v>
       </c>
@@ -11367,7 +11746,7 @@
         <v>-0.59884444696646777</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>2021</v>
       </c>
@@ -11381,7 +11760,7 @@
         <v>-0.58212592838721533</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>2022</v>
       </c>
@@ -11395,7 +11774,7 @@
         <v>-0.58476026852042595</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>2023</v>
       </c>
@@ -11409,7 +11788,7 @@
         <v>-0.56894577426477011</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>2024</v>
       </c>
@@ -11423,7 +11802,7 @@
         <v>-0.55774239163231498</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>2025</v>
       </c>
@@ -11437,7 +11816,7 @@
         <v>-0.5546484315400706</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>2026</v>
       </c>
@@ -11451,7 +11830,7 @@
         <v>-0.54633744534475526</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>2027</v>
       </c>
@@ -11465,7 +11844,7 @@
         <v>-0.53660398326743075</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>2028</v>
       </c>
@@ -11479,7 +11858,7 @@
         <v>-0.52636891781716488</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>2029</v>
       </c>
@@ -11493,7 +11872,7 @@
         <v>-0.52739427357167223</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>2030</v>
       </c>
@@ -11507,7 +11886,7 @@
         <v>-0.522335868711721</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>2031</v>
       </c>
@@ -11521,7 +11900,7 @@
         <v>-0.51932161850484515</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>2032</v>
       </c>
@@ -11535,7 +11914,7 @@
         <v>-0.51851186880903399</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>2033</v>
       </c>
@@ -11549,7 +11928,7 @@
         <v>-0.52248458236888451</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>2034</v>
       </c>
@@ -11563,7 +11942,7 @@
         <v>-0.51756454907723248</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>2035</v>
       </c>
@@ -11577,7 +11956,7 @@
         <v>-0.51707659305484055</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>2036</v>
       </c>
@@ -11591,7 +11970,7 @@
         <v>-0.51785189045280133</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>2037</v>
       </c>
@@ -11605,7 +11984,7 @@
         <v>-0.52133458277805855</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>2038</v>
       </c>
@@ -11619,7 +11998,7 @@
         <v>-0.52255964231049601</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>2039</v>
       </c>
@@ -11633,7 +12012,7 @@
         <v>-0.52461978177447943</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>2040</v>
       </c>
@@ -11647,7 +12026,7 @@
         <v>-0.52602689591038243</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>2041</v>
       </c>
@@ -11661,7 +12040,7 @@
         <v>-0.52818471105801446</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>2042</v>
       </c>
@@ -11675,7 +12054,7 @@
         <v>-0.52582640158760352</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>2043</v>
       </c>
@@ -11689,7 +12068,7 @@
         <v>-0.52884537398341225</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>2044</v>
       </c>
@@ -11703,7 +12082,7 @@
         <v>-0.53136207561516069</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>2045</v>
       </c>
@@ -11717,7 +12096,7 @@
         <v>-0.53392813259970762</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>2046</v>
       </c>
@@ -11731,7 +12110,7 @@
         <v>-0.53502526357346303</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>2047</v>
       </c>
@@ -11745,7 +12124,7 @@
         <v>-0.5361827911656164</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>2048</v>
       </c>
@@ -11759,7 +12138,7 @@
         <v>-0.53742998980006962</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>2049</v>
       </c>
@@ -11773,7 +12152,7 @@
         <v>-0.53265366720456808</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>2050</v>
       </c>
@@ -11787,7 +12166,7 @@
         <v>-0.52672262067763742</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>2051</v>
       </c>
@@ -11801,7 +12180,7 @@
         <v>-0.52246561759781496</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>2052</v>
       </c>
@@ -11815,7 +12194,7 @@
         <v>-0.51992475724234222</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>2053</v>
       </c>
@@ -11829,7 +12208,7 @@
         <v>-0.51600574555924328</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>2054</v>
       </c>
@@ -11843,7 +12222,7 @@
         <v>-0.51576972424348644</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>2055</v>
       </c>
@@ -11857,7 +12236,7 @@
         <v>-0.51800776098642443</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>2056</v>
       </c>
@@ -11871,7 +12250,7 @@
         <v>-0.51952270196948724</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>2057</v>
       </c>
@@ -11885,7 +12264,7 @@
         <v>-0.52097143042496585</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>2058</v>
       </c>
@@ -11899,7 +12278,7 @@
         <v>-0.51855272309252176</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>2059</v>
       </c>
@@ -11913,7 +12292,7 @@
         <v>-0.51809916084156005</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>2060</v>
       </c>
@@ -11927,7 +12306,7 @@
         <v>-0.51977389607061364</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>2061</v>
       </c>
@@ -11941,7 +12320,7 @@
         <v>-0.51599900885427696</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>2062</v>
       </c>
@@ -11955,7 +12334,7 @@
         <v>-0.51480700328602169</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>2063</v>
       </c>
@@ -11969,7 +12348,7 @@
         <v>-0.51568068499828201</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>2064</v>
       </c>
@@ -11983,7 +12362,7 @@
         <v>-0.51597773825575943</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>2065</v>
       </c>
@@ -11997,7 +12376,7 @@
         <v>-0.50918163905100955</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>2066</v>
       </c>
@@ -12011,7 +12390,7 @@
         <v>-0.51037220329257249</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>2067</v>
       </c>
@@ -12025,7 +12404,7 @@
         <v>-0.50578085391324401</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>2068</v>
       </c>
@@ -12039,7 +12418,7 @@
         <v>-0.50041296740445906</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>2069</v>
       </c>
@@ -12053,7 +12432,7 @@
         <v>-0.50041296740445906</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>2070</v>
       </c>
@@ -12075,9 +12454,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B00E6D01-ED8F-4196-BCE1-0F54EC92EC33}">
   <dimension ref="A1:F62"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -12091,7 +12470,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>2010</v>
       </c>
@@ -12105,7 +12484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2011</v>
       </c>
@@ -12119,7 +12498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2012</v>
       </c>
@@ -12133,7 +12512,7 @@
         <v>-0.44081411312763502</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>2013</v>
       </c>
@@ -12147,7 +12526,7 @@
         <v>-0.41178003442893141</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>2014</v>
       </c>
@@ -12161,7 +12540,7 @@
         <v>-0.38195691653651342</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>2015</v>
       </c>
@@ -12175,7 +12554,7 @@
         <v>-0.35662154819469444</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>2016</v>
       </c>
@@ -12189,7 +12568,7 @@
         <v>-0.33645665993640061</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>2017</v>
       </c>
@@ -12203,7 +12582,7 @@
         <v>-0.31569377810596422</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>2018</v>
       </c>
@@ -12217,7 +12596,7 @@
         <v>-0.29611480221652442</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>2019</v>
       </c>
@@ -12231,7 +12610,7 @@
         <v>-0.279462622342386</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>2020</v>
       </c>
@@ -12245,7 +12624,7 @@
         <v>-0.26591979180000819</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>2021</v>
       </c>
@@ -12259,7 +12638,7 @@
         <v>-0.25543875103684177</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>2022</v>
       </c>
@@ -12273,7 +12652,7 @@
         <v>-0.24930347300809638</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>2023</v>
       </c>
@@ -12287,7 +12666,7 @@
         <v>-0.2471951557625644</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>2024</v>
       </c>
@@ -12301,7 +12680,7 @@
         <v>-0.24727245707738721</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>2025</v>
       </c>
@@ -12315,7 +12694,7 @@
         <v>-0.23666450179745918</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>2026</v>
       </c>
@@ -12329,7 +12708,7 @@
         <v>-0.23784361977757321</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>2027</v>
       </c>
@@ -12343,7 +12722,7 @@
         <v>-0.23889278870939884</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>2028</v>
       </c>
@@ -12357,7 +12736,7 @@
         <v>-0.23893998110579662</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>2029</v>
       </c>
@@ -12371,7 +12750,7 @@
         <v>-0.23843847695520243</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>2030</v>
       </c>
@@ -12385,7 +12764,7 @@
         <v>-0.24968508459850719</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>2031</v>
       </c>
@@ -12399,7 +12778,7 @@
         <v>-0.25091556848125485</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>2032</v>
       </c>
@@ -12413,7 +12792,7 @@
         <v>-0.25300049353502324</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>2033</v>
       </c>
@@ -12427,7 +12806,7 @@
         <v>-0.25769551121458001</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>2034</v>
       </c>
@@ -12441,7 +12820,7 @@
         <v>-0.26297059722398985</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>2035</v>
       </c>
@@ -12455,7 +12834,7 @@
         <v>-0.26957256055242024</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>2036</v>
       </c>
@@ -12469,7 +12848,7 @@
         <v>-0.27813755313923438</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>2037</v>
       </c>
@@ -12483,7 +12862,7 @@
         <v>-0.27474637053283057</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>2038</v>
       </c>
@@ -12497,7 +12876,7 @@
         <v>-0.28518071039366039</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>2039</v>
       </c>
@@ -12511,7 +12890,7 @@
         <v>-0.2959050156529302</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>2040</v>
       </c>
@@ -12525,7 +12904,7 @@
         <v>-0.2928526070865794</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>2041</v>
       </c>
@@ -12539,7 +12918,7 @@
         <v>-0.30204917920681157</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>2042</v>
       </c>
@@ -12553,7 +12932,7 @@
         <v>-0.32304908725990761</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>2043</v>
       </c>
@@ -12567,7 +12946,7 @@
         <v>-0.32697846249115198</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>2044</v>
       </c>
@@ -12581,7 +12960,7 @@
         <v>-0.33007523822817458</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>2045</v>
       </c>
@@ -12595,7 +12974,7 @@
         <v>-0.34395374911145921</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>2046</v>
       </c>
@@ -12609,7 +12988,7 @@
         <v>-0.32911187304579681</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>2047</v>
       </c>
@@ -12623,7 +13002,7 @@
         <v>-0.32707905887567962</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>2048</v>
       </c>
@@ -12637,7 +13016,7 @@
         <v>-0.32548082652979621</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>2049</v>
       </c>
@@ -12651,7 +13030,7 @@
         <v>-0.32367111158351802</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>2050</v>
       </c>
@@ -12665,7 +13044,7 @@
         <v>-0.31183478961522498</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>2051</v>
       </c>
@@ -12679,7 +13058,7 @@
         <v>-0.30933783525634517</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>2052</v>
       </c>
@@ -12693,7 +13072,7 @@
         <v>-0.295502572399851</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>2053</v>
       </c>
@@ -12707,7 +13086,7 @@
         <v>-0.28426566851705959</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>2054</v>
       </c>
@@ -12721,7 +13100,7 @@
         <v>-0.2846970607117626</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>2055</v>
       </c>
@@ -12735,7 +13114,7 @@
         <v>-0.29652418423720162</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>2056</v>
       </c>
@@ -12749,7 +13128,7 @@
         <v>-0.31354110133198604</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>2057</v>
       </c>
@@ -12763,7 +13142,7 @@
         <v>-0.3278678462801522</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>2058</v>
       </c>
@@ -12777,7 +13156,7 @@
         <v>-0.33932540739172184</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>2059</v>
       </c>
@@ -12791,7 +13170,7 @@
         <v>-0.33891825783445723</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>2060</v>
       </c>
@@ -12805,7 +13184,7 @@
         <v>-0.33791821188593724</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>2061</v>
       </c>
@@ -12819,7 +13198,7 @@
         <v>-0.33627771003385082</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>2062</v>
       </c>
@@ -12833,7 +13212,7 @@
         <v>-0.33352763519739703</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>2063</v>
       </c>
@@ -12847,7 +13226,7 @@
         <v>-0.33028054032751103</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>2064</v>
       </c>
@@ -12861,7 +13240,7 @@
         <v>-0.32636589095194396</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>2065</v>
       </c>
@@ -12875,7 +13254,7 @@
         <v>-0.32296966045752384</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>2066</v>
       </c>
@@ -12889,7 +13268,7 @@
         <v>-0.3197457208767488</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>2067</v>
       </c>
@@ -12903,7 +13282,7 @@
         <v>-0.31773659008754962</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>2068</v>
       </c>
@@ -12917,7 +13296,7 @@
         <v>-0.31670999077073703</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>2069</v>
       </c>
@@ -12931,7 +13310,7 @@
         <v>-0.31670999077073703</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>2070</v>
       </c>
@@ -12953,9 +13332,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81CF35D1-EA41-4B4F-8246-ED1C76F988F0}">
   <dimension ref="A1:B32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -12963,7 +13342,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>2010</v>
       </c>
@@ -12971,7 +13350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2011</v>
       </c>
@@ -12979,7 +13358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2012</v>
       </c>
@@ -12987,7 +13366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>2013</v>
       </c>
@@ -12995,7 +13374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>2014</v>
       </c>
@@ -13003,7 +13382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>2015</v>
       </c>
@@ -13011,7 +13390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>2016</v>
       </c>
@@ -13019,7 +13398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>2017</v>
       </c>
@@ -13027,7 +13406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>2018</v>
       </c>
@@ -13035,7 +13414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>2019</v>
       </c>
@@ -13043,7 +13422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>2020</v>
       </c>
@@ -13051,7 +13430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>2021</v>
       </c>
@@ -13059,7 +13438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>2022</v>
       </c>
@@ -13067,7 +13446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>2023</v>
       </c>
@@ -13075,7 +13454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>2024</v>
       </c>
@@ -13083,7 +13462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>2025</v>
       </c>
@@ -13091,7 +13470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>2026</v>
       </c>
@@ -13099,7 +13478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>2027</v>
       </c>
@@ -13107,7 +13486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>2028</v>
       </c>
@@ -13115,7 +13494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>2029</v>
       </c>
@@ -13123,7 +13502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>2030</v>
       </c>
@@ -13131,7 +13510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>2031</v>
       </c>
@@ -13139,7 +13518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>2032</v>
       </c>
@@ -13147,7 +13526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>2033</v>
       </c>
@@ -13155,7 +13534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>2034</v>
       </c>
@@ -13163,7 +13542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>2035</v>
       </c>
@@ -13171,7 +13550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>2036</v>
       </c>
@@ -13179,7 +13558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>2037</v>
       </c>
@@ -13187,7 +13566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>2038</v>
       </c>
@@ -13195,7 +13574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>2039</v>
       </c>
@@ -13203,7 +13582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>2040</v>
       </c>
@@ -13219,9 +13598,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D7429DD-438F-4396-BA37-1ECD20FCD2D9}">
   <dimension ref="A1:B32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -13229,7 +13608,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>2010</v>
       </c>
@@ -13237,7 +13616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2011</v>
       </c>
@@ -13245,7 +13624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2012</v>
       </c>
@@ -13253,7 +13632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>2013</v>
       </c>
@@ -13261,7 +13640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>2014</v>
       </c>
@@ -13269,7 +13648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>2015</v>
       </c>
@@ -13277,7 +13656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>2016</v>
       </c>
@@ -13285,7 +13664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>2017</v>
       </c>
@@ -13293,7 +13672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>2018</v>
       </c>
@@ -13301,7 +13680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>2019</v>
       </c>
@@ -13309,7 +13688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>2020</v>
       </c>
@@ -13317,7 +13696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>2021</v>
       </c>
@@ -13325,7 +13704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>2022</v>
       </c>
@@ -13333,7 +13712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>2023</v>
       </c>
@@ -13341,7 +13720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>2024</v>
       </c>
@@ -13349,7 +13728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>2025</v>
       </c>
@@ -13357,7 +13736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>2026</v>
       </c>
@@ -13365,7 +13744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>2027</v>
       </c>
@@ -13373,7 +13752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>2028</v>
       </c>
@@ -13381,7 +13760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>2029</v>
       </c>
@@ -13389,7 +13768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>2030</v>
       </c>
@@ -13397,7 +13776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>2031</v>
       </c>
@@ -13405,7 +13784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>2032</v>
       </c>
@@ -13413,7 +13792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>2033</v>
       </c>
@@ -13421,7 +13800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>2034</v>
       </c>
@@ -13429,7 +13808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>2035</v>
       </c>
@@ -13437,7 +13816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>2036</v>
       </c>
@@ -13445,7 +13824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>2037</v>
       </c>
@@ -13453,7 +13832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>2038</v>
       </c>
@@ -13461,7 +13840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>2039</v>
       </c>
@@ -13469,7 +13848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>2040</v>
       </c>
@@ -13485,9 +13864,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83A8B1C6-B095-49F5-BE52-65A3AD804239}">
   <dimension ref="A1:B32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -13495,7 +13874,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>2010</v>
       </c>
@@ -13503,7 +13882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2011</v>
       </c>
@@ -13511,7 +13890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2012</v>
       </c>
@@ -13519,7 +13898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>2013</v>
       </c>
@@ -13527,7 +13906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>2014</v>
       </c>
@@ -13535,7 +13914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>2015</v>
       </c>
@@ -13543,7 +13922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>2016</v>
       </c>
@@ -13551,7 +13930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>2017</v>
       </c>
@@ -13559,7 +13938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>2018</v>
       </c>
@@ -13567,7 +13946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>2019</v>
       </c>
@@ -13575,7 +13954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>2020</v>
       </c>
@@ -13583,7 +13962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>2021</v>
       </c>
@@ -13591,7 +13970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>2022</v>
       </c>
@@ -13599,7 +13978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>2023</v>
       </c>
@@ -13607,7 +13986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>2024</v>
       </c>
@@ -13615,7 +13994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>2025</v>
       </c>
@@ -13623,7 +14002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>2026</v>
       </c>
@@ -13631,7 +14010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>2027</v>
       </c>
@@ -13639,7 +14018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>2028</v>
       </c>
@@ -13647,7 +14026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>2029</v>
       </c>
@@ -13655,7 +14034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>2030</v>
       </c>
@@ -13663,7 +14042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>2031</v>
       </c>
@@ -13671,7 +14050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>2032</v>
       </c>
@@ -13679,7 +14058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>2033</v>
       </c>
@@ -13687,7 +14066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>2034</v>
       </c>
@@ -13695,7 +14074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>2035</v>
       </c>
@@ -13703,7 +14082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>2036</v>
       </c>
@@ -13711,7 +14090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>2037</v>
       </c>
@@ -13719,7 +14098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>2038</v>
       </c>
@@ -13727,7 +14106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>2039</v>
       </c>
@@ -13735,7 +14114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>2040</v>
       </c>
@@ -13751,9 +14130,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5368A556-88DB-4602-9465-944BD364475C}">
   <dimension ref="A1:B116"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -13761,7 +14140,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1947</v>
       </c>
@@ -13769,7 +14148,7 @@
         <v>16.598309271060831</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>1948</v>
       </c>
@@ -13777,7 +14156,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>1949</v>
       </c>
@@ -13785,7 +14164,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>1950</v>
       </c>
@@ -13793,7 +14172,7 @@
         <v>18.2</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>1951</v>
       </c>
@@ -13801,7 +14180,7 @@
         <v>18.899999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>1952</v>
       </c>
@@ -13809,7 +14188,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>1953</v>
       </c>
@@ -13817,7 +14196,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>1954</v>
       </c>
@@ -13825,7 +14204,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>1955</v>
       </c>
@@ -13833,7 +14212,7 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>1956</v>
       </c>
@@ -13841,7 +14220,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>1957</v>
       </c>
@@ -13849,7 +14228,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>1958</v>
       </c>
@@ -13857,7 +14236,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>1959</v>
       </c>
@@ -13865,7 +14244,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>1960</v>
       </c>
@@ -13873,7 +14252,7 @@
         <v>25.5</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>1961</v>
       </c>
@@ -13881,7 +14260,7 @@
         <v>26.2</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>1962</v>
       </c>
@@ -13889,7 +14268,7 @@
         <v>26.5</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>1963</v>
       </c>
@@ -13897,7 +14276,7 @@
         <v>27.8</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>1964</v>
       </c>
@@ -13905,7 +14284,7 @@
         <v>29.4</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>1965</v>
       </c>
@@ -13913,7 +14292,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>1966</v>
       </c>
@@ -13921,7 +14300,7 @@
         <v>30.5</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>1967</v>
       </c>
@@ -13929,7 +14308,7 @@
         <v>31.3</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>1968</v>
       </c>
@@ -13937,7 +14316,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>1969</v>
       </c>
@@ -13945,7 +14324,7 @@
         <v>33.6</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <v>1970</v>
       </c>
@@ -13953,7 +14332,7 @@
         <v>34.5</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>1971</v>
       </c>
@@ -13961,7 +14340,7 @@
         <v>35.799999999999997</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <v>1972</v>
       </c>
@@ -13969,7 +14348,7 @@
         <v>37.299999999999997</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <v>1973</v>
       </c>
@@ -13977,7 +14356,7 @@
         <v>39.799999999999997</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <v>1974</v>
       </c>
@@ -13985,7 +14364,7 @@
         <v>38.799999999999997</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <v>1975</v>
       </c>
@@ -13993,7 +14372,7 @@
         <v>38.200000000000003</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>1976</v>
       </c>
@@ -14001,7 +14380,7 @@
         <v>39.299999999999997</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <v>1977</v>
       </c>
@@ -14009,7 +14388,7 @@
         <v>40.299999999999997</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>1978</v>
       </c>
@@ -14017,7 +14396,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <v>1979</v>
       </c>
@@ -14025,7 +14404,7 @@
         <v>43.5</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
         <v>1980</v>
       </c>
@@ -14033,7 +14412,7 @@
         <v>42.6</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
         <v>1981</v>
       </c>
@@ -14041,7 +14420,7 @@
         <v>42.3</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
         <v>1982</v>
       </c>
@@ -14049,7 +14428,7 @@
         <v>43.2</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
         <v>1983</v>
       </c>
@@ -14057,7 +14436,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
         <v>1984</v>
       </c>
@@ -14065,7 +14444,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
         <v>1985</v>
       </c>
@@ -14073,7 +14452,7 @@
         <v>47.9</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
         <v>1986</v>
       </c>
@@ -14081,7 +14460,7 @@
         <v>49.4</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
         <v>1987</v>
       </c>
@@ -14089,7 +14468,7 @@
         <v>52.1</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
         <v>1988</v>
       </c>
@@ -14097,7 +14476,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
         <v>1989</v>
       </c>
@@ -14105,7 +14484,7 @@
         <v>56.3</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
         <v>1990</v>
       </c>
@@ -14113,7 +14492,7 @@
         <v>56.7</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
         <v>1991</v>
       </c>
@@ -14121,7 +14500,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
         <v>1992</v>
       </c>
@@ -14129,7 +14508,7 @@
         <v>56.2</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
         <v>1993</v>
       </c>
@@ -14137,7 +14516,7 @@
         <v>57.5</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
         <v>1994</v>
       </c>
@@ -14145,7 +14524,7 @@
         <v>59.7</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
         <v>1995</v>
       </c>
@@ -14153,7 +14532,7 @@
         <v>61.2</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
         <v>1996</v>
       </c>
@@ -14161,7 +14540,7 @@
         <v>62.6</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
         <v>1997</v>
       </c>
@@ -14169,7 +14548,7 @@
         <v>65.7</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" s="2">
         <v>1998</v>
       </c>
@@ -14177,7 +14556,7 @@
         <v>67.8</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
         <v>1999</v>
       </c>
@@ -14185,7 +14564,7 @@
         <v>69.8</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" s="2">
         <v>2000</v>
       </c>
@@ -14193,7 +14572,7 @@
         <v>72.400000000000006</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" s="2">
         <v>2001</v>
       </c>
@@ -14201,7 +14580,7 @@
         <v>73.900000000000006</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" s="2">
         <v>2002</v>
       </c>
@@ -14209,7 +14588,7 @@
         <v>75.5</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" s="2">
         <v>2003</v>
       </c>
@@ -14217,7 +14596,7 @@
         <v>77.7</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" s="2">
         <v>2004</v>
       </c>
@@ -14225,7 +14604,7 @@
         <v>79.599999999999994</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" s="2">
         <v>2005</v>
       </c>
@@ -14233,7 +14612,7 @@
         <v>81.599999999999994</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" s="2">
         <v>2006</v>
       </c>
@@ -14241,7 +14620,7 @@
         <v>83.7</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" s="2">
         <v>2007</v>
       </c>
@@ -14249,7 +14628,7 @@
         <v>85.7</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" s="2">
         <v>2008</v>
       </c>
@@ -14257,7 +14636,7 @@
         <v>85.4</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" s="2">
         <v>2009</v>
       </c>
@@ -14265,7 +14644,7 @@
         <v>81.8</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" s="2">
         <v>2010</v>
       </c>
@@ -14273,7 +14652,7 @@
         <v>83.6</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" s="2">
         <v>2011</v>
       </c>
@@ -14281,7 +14660,7 @@
         <v>84.8</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" s="2">
         <v>2012</v>
       </c>
@@ -14289,7 +14668,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" s="2">
         <v>2013</v>
       </c>
@@ -14297,7 +14676,7 @@
         <v>87.6</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" s="2">
         <v>2014</v>
       </c>
@@ -14305,7 +14684,7 @@
         <v>90.3</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" s="2">
         <v>2015</v>
       </c>
@@ -14313,7 +14692,7 @@
         <v>92.6</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" s="2">
         <v>2016</v>
       </c>
@@ -14321,7 +14700,7 @@
         <v>94.7</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" s="2">
         <v>2017</v>
       </c>
@@ -14329,7 +14708,7 @@
         <v>96.8</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" s="2">
         <v>2018</v>
       </c>
@@ -14337,7 +14716,7 @@
         <v>98.4</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" s="2">
         <v>2019</v>
       </c>
@@ -14345,7 +14724,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" s="2">
         <v>2020</v>
       </c>
@@ -14353,7 +14732,7 @@
         <v>90.6</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" s="2">
         <v>2021</v>
       </c>
@@ -14361,7 +14740,7 @@
         <v>97.4</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" s="2">
         <v>2022</v>
       </c>
@@ -14369,7 +14748,7 @@
         <v>99.757148331179067</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" s="2">
         <v>2023</v>
       </c>
@@ -14377,7 +14756,7 @@
         <v>102.17134130563514</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" s="2">
         <v>2024</v>
       </c>
@@ -14385,7 +14764,7 @@
         <v>104.64395944375532</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" s="2">
         <v>2025</v>
       </c>
@@ -14393,7 +14772,7 @@
         <v>107.17641667548857</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" s="2">
         <v>2026</v>
       </c>
@@ -14401,7 +14780,7 @@
         <v>109.77016114888056</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" s="2">
         <v>2027</v>
       </c>
@@ -14409,7 +14788,7 @@
         <v>112.42667605817564</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" s="2">
         <v>2028</v>
       </c>
@@ -14417,7 +14796,7 @@
         <v>115.1474804919594</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" s="2">
         <v>2029</v>
       </c>
@@ -14425,7 +14804,7 @@
         <v>117.9341303018269</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" s="2">
         <v>2030</v>
       </c>
@@ -14433,7 +14812,7 @@
         <v>120.78821899207334</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" s="2">
         <v>2031</v>
       </c>
@@ -14441,7 +14820,7 @@
         <v>123.7113786309158</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" s="2">
         <v>2032</v>
       </c>
@@ -14449,7 +14828,7 @@
         <v>126.70528078376718</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" s="2">
         <v>2033</v>
       </c>
@@ -14457,7 +14836,7 @@
         <v>129.77163746909605</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" s="2">
         <v>2034</v>
       </c>
@@ -14465,7 +14844,7 @@
         <v>132.912202137419</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" s="2">
         <v>2035</v>
       </c>
@@ -14473,7 +14852,7 @@
         <v>136.12877067398526</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" s="2">
         <v>2036</v>
       </c>
@@ -14481,7 +14860,7 @@
         <v>139.42318242572699</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" s="2">
         <v>2037</v>
       </c>
@@ -14489,7 +14868,7 @@
         <v>142.79732125306251</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" s="2">
         <v>2038</v>
       </c>
@@ -14497,7 +14876,7 @@
         <v>146.25311660715386</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" s="2">
         <v>2039</v>
       </c>
@@ -14505,7 +14884,7 @@
         <v>149.79254463323488</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" s="2">
         <v>2040</v>
       </c>
@@ -14513,7 +14892,7 @@
         <v>153.41762930064039</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" s="2">
         <v>2041</v>
       </c>
@@ -14521,7 +14900,7 @@
         <v>157.13044356018301</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" s="2">
         <v>2042</v>
       </c>
@@ -14529,7 +14908,7 @@
         <v>160.93311052953939</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" s="2">
         <v>2043</v>
       </c>
@@ -14537,7 +14916,7 @@
         <v>164.82780470732337</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" s="2">
         <v>2044</v>
       </c>
@@ -14545,7 +14924,7 @@
         <v>168.81675321654077</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" s="2">
         <v>2045</v>
       </c>
@@ -14553,7 +14932,7 @@
         <v>172.90223707813664</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" s="2">
         <v>2046</v>
       </c>
@@ -14561,7 +14940,7 @@
         <v>177.08659251536309</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" s="2">
         <v>2047</v>
       </c>
@@ -14569,7 +14948,7 @@
         <v>181.37221228971399</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" s="2">
         <v>2048</v>
       </c>
@@ -14577,7 +14956,7 @@
         <v>185.76154706918993</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" s="2">
         <v>2049</v>
       </c>
@@ -14585,7 +14964,7 @@
         <v>190.25710682967642</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" s="2">
         <v>2050</v>
       </c>
@@ -14593,7 +14972,7 @@
         <v>194.86146229023626</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" s="2">
         <v>2051</v>
       </c>
@@ -14601,7 +14980,7 @@
         <v>199.57724638313712</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" s="2">
         <v>2052</v>
       </c>
@@ -14609,7 +14988,7 @@
         <v>204.40715575945461</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" s="2">
         <v>2053</v>
       </c>
@@ -14617,7 +14996,7 @@
         <v>209.35395233111228</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" s="2">
         <v>2054</v>
       </c>
@@ -14625,7 +15004,7 @@
         <v>214.42046485023982</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" s="2">
         <v>2055</v>
       </c>
@@ -14633,7 +15012,7 @@
         <v>219.60959052675298</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" s="2">
         <v>2056</v>
       </c>
@@ -14641,7 +15020,7 @@
         <v>224.92429668508001</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" s="2">
         <v>2057</v>
       </c>
@@ -14649,7 +15028,7 @@
         <v>230.36762246098209</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" s="2">
         <v>2058</v>
       </c>
@@ -14657,7 +15036,7 @@
         <v>235.9426805394379</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" s="2">
         <v>2059</v>
       </c>
@@ -14665,7 +15044,7 @@
         <v>241.65265893458633</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115" s="2">
         <v>2060</v>
       </c>
@@ -14673,7 +15052,7 @@
         <v>247.50082281274493</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116" s="2">
         <v>2061</v>
       </c>
@@ -14687,11 +15066,11 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC2B7FF6-C3ED-409F-83AB-FB5EAD53E39E}">
-  <dimension ref="A1:B42"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1F9D479-EFA7-49EA-8FEF-14D2ED86AAD3}">
+  <dimension ref="A1:B104"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -14699,336 +15078,831 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2">
+        <v>1920</v>
+      </c>
+      <c r="B2">
+        <v>5200.0978371770443</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>1921</v>
+      </c>
+      <c r="B3">
+        <v>4655.4637316883</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>1922</v>
+      </c>
+      <c r="B4">
+        <v>4869.9927431417173</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>1923</v>
+      </c>
+      <c r="B5">
+        <v>4983.697491210316</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>1924</v>
+      </c>
+      <c r="B6">
+        <v>5173.8326436945708</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>1925</v>
+      </c>
+      <c r="B7">
+        <v>5337.3742659332484</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>1926</v>
+      </c>
+      <c r="B8">
+        <v>5145.7895590668668</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>1927</v>
+      </c>
+      <c r="B9">
+        <v>5515.5541155959372</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>1928</v>
+      </c>
+      <c r="B10">
+        <v>5530.7680117342179</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>1929</v>
+      </c>
+      <c r="B11">
+        <v>5670.2650825557139</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>1930</v>
+      </c>
+      <c r="B12">
+        <v>5588.6947789055148</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>1931</v>
+      </c>
+      <c r="B13">
+        <v>5298.8967746674807</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>1932</v>
+      </c>
+      <c r="B14">
+        <v>5274.2664803335301</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>1933</v>
+      </c>
+      <c r="B15">
+        <v>5422.0285091241731</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>1934</v>
+      </c>
+      <c r="B16">
+        <v>5729.4045575524087</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>1935</v>
+      </c>
+      <c r="B17">
+        <v>5914.7289699490993</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>1936</v>
+      </c>
+      <c r="B18">
+        <v>6165.9977755350665</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>1937</v>
+      </c>
+      <c r="B19">
+        <v>6347.7961142588765</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>1938</v>
+      </c>
+      <c r="B20">
+        <v>6368.5820723593424</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>1939</v>
+      </c>
+      <c r="B21">
+        <v>6614.8756610822402</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>1940</v>
+      </c>
+      <c r="B22">
+        <v>7208.204760727117</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>1941</v>
+      </c>
+      <c r="B23">
+        <v>7879.7325957203011</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>1942</v>
+      </c>
+      <c r="B24">
+        <v>7979.991675785287</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>1943</v>
+      </c>
+      <c r="B25">
+        <v>8034.1970531127899</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>1944</v>
+      </c>
+      <c r="B26">
+        <v>7647.8413130465497</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>1945</v>
+      </c>
+      <c r="B27">
+        <v>7263.849618234246</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>1946</v>
+      </c>
+      <c r="B28">
+        <v>7087.5305148924472</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>1947</v>
+      </c>
+      <c r="B29">
+        <v>6945.8745835944574</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>1948</v>
+      </c>
+      <c r="B30">
+        <v>7099.3623573343966</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>1949</v>
+      </c>
+      <c r="B31">
+        <v>7297.0120424995557</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>1950</v>
+      </c>
+      <c r="B32">
+        <v>7505.7230992114055</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>1951</v>
+      </c>
+      <c r="B33">
+        <v>7828.3646483662369</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>1952</v>
+      </c>
+      <c r="B34">
+        <v>7931.0292012729906</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>1953</v>
+      </c>
+      <c r="B35">
+        <v>8344.3899719175242</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>1954</v>
+      </c>
+      <c r="B36">
+        <v>8675.0808088696213</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>1955</v>
+      </c>
+      <c r="B37">
+        <v>8976.515750570632</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>1956</v>
+      </c>
+      <c r="B38">
+        <v>8948.4892482848263</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>1957</v>
+      </c>
+      <c r="B39">
+        <v>9201.8725975560519</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>1958</v>
+      </c>
+      <c r="B40">
+        <v>9155.2305180961321</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>1959</v>
+      </c>
+      <c r="B41">
+        <v>9559.6743210483928</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>1960</v>
+      </c>
+      <c r="B42">
+        <v>10188.565323875224</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>1961</v>
+      </c>
+      <c r="B43">
+        <v>10266.226156592171</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>1962</v>
+      </c>
+      <c r="B44">
+        <v>10410.578852019406</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>1963</v>
+      </c>
+      <c r="B45">
+        <v>10761.011137011137</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>1964</v>
+      </c>
+      <c r="B46">
+        <v>11203.303387444006</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>1965</v>
+      </c>
+      <c r="B47">
+        <v>11546.995099787844</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>1966</v>
+      </c>
+      <c r="B48">
+        <v>11576.537356463419</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>1967</v>
+      </c>
+      <c r="B49">
+        <v>11724.88683483243</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>1968</v>
+      </c>
+      <c r="B50">
+        <v>12367.083723589772</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>1969</v>
+      </c>
+      <c r="B51">
+        <v>12486.382322713256</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>1970</v>
+      </c>
+      <c r="B52">
+        <v>12940.597276608925</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A53">
+        <v>1971</v>
+      </c>
+      <c r="B53">
+        <v>13220.330062192639</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A54">
+        <v>1972</v>
+      </c>
+      <c r="B54">
+        <v>13823.009111097976</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A55">
+        <v>1973</v>
+      </c>
+      <c r="B55">
+        <v>14635.599117027308</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A56">
+        <v>1974</v>
+      </c>
+      <c r="B56">
+        <v>14333.559130272426</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A57">
+        <v>1975</v>
+      </c>
+      <c r="B57">
+        <v>14125.792661434536</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A58">
+        <v>1976</v>
+      </c>
+      <c r="B58">
+        <v>14535.028792006342</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A59">
+        <v>1977</v>
+      </c>
+      <c r="B59">
+        <v>14840.419781099839</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <v>1978</v>
+      </c>
+      <c r="B60">
+        <v>15544.684212021099</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A61">
+        <v>1979</v>
+      </c>
+      <c r="B61">
+        <v>16082.958103227069</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A62">
+        <v>1980</v>
+      </c>
+      <c r="B62">
+        <v>15729.100019201715</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A63">
+        <v>1981</v>
+      </c>
+      <c r="B63">
+        <v>15577.196452698096</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A64">
+        <v>1982</v>
+      </c>
+      <c r="B64">
+        <v>15906.731189162167</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A65">
+        <v>1983</v>
+      </c>
+      <c r="B65">
+        <v>16590.568835185262</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A66">
+        <v>1984</v>
+      </c>
+      <c r="B66">
+        <v>16900.90485550103</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A67">
+        <v>1985</v>
+      </c>
+      <c r="B67">
+        <v>17541.165362354186</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A68">
+        <v>1986</v>
+      </c>
+      <c r="B68">
+        <v>18073.544020019217</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A69">
         <v>1987</v>
       </c>
-      <c r="B2" s="1">
-        <v>48.34160833287882</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
+      <c r="B69">
+        <v>19018.04134061862</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A70">
         <v>1988</v>
       </c>
-      <c r="B3" s="1">
-        <v>49.6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
+      <c r="B70">
+        <v>19981.084310349343</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A71">
         <v>1989</v>
       </c>
-      <c r="B4" s="1">
-        <v>52.2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
+      <c r="B71">
+        <v>20389.248013097</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A72">
         <v>1990</v>
       </c>
-      <c r="B5" s="1">
-        <v>55.9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
+      <c r="B72">
+        <v>20472.234153774134</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A73">
         <v>1991</v>
       </c>
-      <c r="B6" s="1">
-        <v>60.1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
+      <c r="B73">
+        <v>20120.685235043897</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A74">
         <v>1992</v>
       </c>
-      <c r="B7" s="1">
-        <v>62.6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
+      <c r="B74">
+        <v>20109.857896725225</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A75">
         <v>1993</v>
       </c>
-      <c r="B8" s="1">
-        <v>64.2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
+      <c r="B75">
+        <v>20512.302168736918</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A76">
         <v>1994</v>
       </c>
-      <c r="B9" s="1">
-        <v>65.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
+      <c r="B76">
+        <v>21158.185938820705</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A77">
         <v>1995</v>
       </c>
-      <c r="B10" s="1">
-        <v>67.2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
+      <c r="B77">
+        <v>21619.659317921563</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A78">
         <v>1996</v>
       </c>
-      <c r="B11" s="1">
-        <v>68.8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
+      <c r="B78">
+        <v>22104.606107638232</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A79">
         <v>1997</v>
       </c>
-      <c r="B12" s="1">
-        <v>70.099999999999994</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
+      <c r="B79">
+        <v>23138.705389815397</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A80">
         <v>1998</v>
       </c>
-      <c r="B13" s="1">
-        <v>71.2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
+      <c r="B80">
+        <v>23843.146386487097</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A81">
         <v>1999</v>
       </c>
-      <c r="B14" s="1">
-        <v>72.099999999999994</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="2">
+      <c r="B81">
+        <v>24495.240267670692</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A82">
         <v>2000</v>
       </c>
-      <c r="B15" s="1">
-        <v>72.7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="2">
+      <c r="B82">
+        <v>25462.639981396853</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A83">
         <v>2001</v>
       </c>
-      <c r="B16" s="1">
-        <v>73.599999999999994</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="2">
+      <c r="B83">
+        <v>26028.483487100813</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A84">
         <v>2002</v>
       </c>
-      <c r="B17" s="1">
-        <v>74.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
+      <c r="B84">
+        <v>26390.448707218879</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A85">
         <v>2003</v>
       </c>
-      <c r="B18" s="1">
-        <v>75.5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
+      <c r="B85">
+        <v>27105.240293519386</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A86">
         <v>2004</v>
       </c>
-      <c r="B19" s="1">
-        <v>76.5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
+      <c r="B86">
+        <v>27619.265304795474</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A87">
         <v>2005</v>
       </c>
-      <c r="B20" s="1">
-        <v>78.099999999999994</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
+      <c r="B87">
+        <v>28140.974000626593</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A88">
         <v>2006</v>
       </c>
-      <c r="B21" s="1">
-        <v>79.900000000000006</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="2">
+      <c r="B88">
+        <v>28622.291353302138</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A89">
         <v>2007</v>
       </c>
-      <c r="B22" s="1">
-        <v>81.8</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
+      <c r="B89">
+        <v>29132.694045972472</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A90">
         <v>2008</v>
       </c>
-      <c r="B23" s="1">
-        <v>84.7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="2">
+      <c r="B90">
+        <v>28812.974465148378</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A91">
         <v>2009</v>
       </c>
-      <c r="B24" s="1">
-        <v>86.6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="2">
+      <c r="B91">
+        <v>27294.907553026798</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A92">
         <v>2010</v>
       </c>
-      <c r="B25" s="1">
-        <v>89.4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="2">
+      <c r="B92">
+        <v>27685.949451575107</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A93">
         <v>2011</v>
       </c>
-      <c r="B26" s="1">
-        <v>93.4</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="2">
+      <c r="B93">
+        <v>27767.946490809612</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A94">
         <v>2012</v>
       </c>
-      <c r="B27" s="1">
-        <v>96.1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="2">
+      <c r="B94">
+        <v>28005.045558945629</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A95">
         <v>2013</v>
       </c>
-      <c r="B28" s="1">
-        <v>98.5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="2">
+      <c r="B95">
+        <v>28316.027741260437</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A96">
         <v>2014</v>
       </c>
-      <c r="B29" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="2">
+      <c r="B96">
+        <v>28996.192569721788</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A97">
         <v>2015</v>
       </c>
-      <c r="B30" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="2">
+      <c r="B97">
+        <v>29443.99889380531</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A98">
         <v>2016</v>
       </c>
-      <c r="B31" s="1">
-        <v>100.7</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="2">
+      <c r="B98">
+        <v>29751.483903548309</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A99">
         <v>2017</v>
       </c>
-      <c r="B32" s="1">
-        <v>103.4</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="2">
+      <c r="B99">
+        <v>30403.843180757089</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A100">
         <v>2018</v>
       </c>
-      <c r="B33" s="1">
-        <v>105.9</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="2">
+      <c r="B100">
+        <v>30668.769802651481</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A101">
         <v>2019</v>
       </c>
-      <c r="B34" s="1">
-        <v>107.8</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="2">
+      <c r="B101">
+        <v>31002.03517519747</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A102">
         <v>2020</v>
       </c>
-      <c r="B35" s="1">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="2">
+      <c r="B102">
+        <v>27759.109717537787</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A103">
         <v>2021</v>
       </c>
-      <c r="B36" s="1">
-        <v>111.6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="2">
+      <c r="B103">
+        <v>30051.71648774618</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A104">
         <v>2022</v>
       </c>
-      <c r="B37" s="1">
-        <v>121.7</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="2">
-        <v>2023</v>
-      </c>
-      <c r="B38" s="1">
-        <v>124.57395874315898</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="2">
-        <v>2024</v>
-      </c>
-      <c r="B39" s="1">
-        <v>126.63064241784659</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="2">
-        <v>2025</v>
-      </c>
-      <c r="B40" s="1">
-        <v>129.11704786530214</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B41" s="1">
-        <v>131.69938882260817</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="2">
-        <v>2027</v>
-      </c>
-      <c r="B42" s="1">
-        <v>135.1276862908702</v>
+      <c r="B104">
+        <v>31204.771611147269</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/input/time_series_factor.xlsx
+++ b/input/time_series_factor.xlsx
@@ -1,38 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pineapple/IdeaProjects/SimPathsUK_refactored/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD0346D6-75AE-FA4B-AD5D-7967666D4770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{598F5936-5705-C244-984C-D3D690C829C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23260" yWindow="2060" windowWidth="25440" windowHeight="15400" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="23260" yWindow="2060" windowWidth="25440" windowHeight="15400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Info" sheetId="1" r:id="rId1"/>
-    <sheet name="UK_care_adjustment" sheetId="14" r:id="rId2"/>
-    <sheet name="UK_cohabitation_adjustment" sheetId="15" r:id="rId3"/>
-    <sheet name="UK_fertility_adjustment" sheetId="19" r:id="rId4"/>
-    <sheet name="UK_utility_adj_acmales" sheetId="20" r:id="rId5"/>
-    <sheet name="UK_utility_adj_singledepwomen" sheetId="23" r:id="rId6"/>
-    <sheet name="UK_utility_adj_singledepmen" sheetId="22" r:id="rId7"/>
-    <sheet name="UK_utility_adj_smales" sheetId="16" r:id="rId8"/>
-    <sheet name="UK_utility_adj_acfemales" sheetId="21" r:id="rId9"/>
-    <sheet name="UK_utility_adj_sfemales" sheetId="17" r:id="rId10"/>
-    <sheet name="UK_utility_adj_couples" sheetId="18" r:id="rId11"/>
-    <sheet name="UK_gdp" sheetId="2" r:id="rId12"/>
-    <sheet name="UK_inflation" sheetId="7" r:id="rId13"/>
-    <sheet name="UK_wage_growth" sheetId="8" r:id="rId14"/>
-    <sheet name="UK_saving_returns" sheetId="9" r:id="rId15"/>
-    <sheet name="UK_debt_cost_low" sheetId="10" r:id="rId16"/>
-    <sheet name="UK_debt_cost_hi" sheetId="11" r:id="rId17"/>
-    <sheet name="UK_carer_hourly_wage" sheetId="13" r:id="rId18"/>
-    <sheet name="UK raw data" sheetId="12" r:id="rId19"/>
-    <sheet name="IT" sheetId="4" r:id="rId20"/>
+    <sheet name="UK_students_adjustment" sheetId="24" r:id="rId1"/>
+    <sheet name="Info" sheetId="1" r:id="rId2"/>
+    <sheet name="UK_care_adjustment" sheetId="14" r:id="rId3"/>
+    <sheet name="UK_cohabitation_adjustment" sheetId="15" r:id="rId4"/>
+    <sheet name="UK_fertility_adjustment" sheetId="19" r:id="rId5"/>
+    <sheet name="UK_utility_adj_acmales" sheetId="20" r:id="rId6"/>
+    <sheet name="UK_utility_adj_singledepwomen" sheetId="23" r:id="rId7"/>
+    <sheet name="UK_utility_adj_singledepmen" sheetId="22" r:id="rId8"/>
+    <sheet name="UK_utility_adj_smales" sheetId="16" r:id="rId9"/>
+    <sheet name="UK_utility_adj_acfemales" sheetId="21" r:id="rId10"/>
+    <sheet name="UK_utility_adj_sfemales" sheetId="17" r:id="rId11"/>
+    <sheet name="UK_utility_adj_couples" sheetId="18" r:id="rId12"/>
+    <sheet name="UK_gdp" sheetId="2" r:id="rId13"/>
+    <sheet name="UK_inflation" sheetId="7" r:id="rId14"/>
+    <sheet name="UK_wage_growth" sheetId="8" r:id="rId15"/>
+    <sheet name="UK_saving_returns" sheetId="9" r:id="rId16"/>
+    <sheet name="UK_debt_cost_low" sheetId="10" r:id="rId17"/>
+    <sheet name="UK_debt_cost_hi" sheetId="11" r:id="rId18"/>
+    <sheet name="UK_carer_hourly_wage" sheetId="13" r:id="rId19"/>
+    <sheet name="UK raw data" sheetId="12" r:id="rId20"/>
+    <sheet name="IT" sheetId="4" r:id="rId21"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -55,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="56">
   <si>
     <t>Year</t>
   </si>
@@ -1068,6 +1069,3541 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A56B41E9-3C32-2C44-B860-85F5893FC338}">
+  <dimension ref="A1:B32"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>2010</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2011</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>2012</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>2013</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>2014</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>2015</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>2016</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>2017</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>2018</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>2019</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>2020</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>2021</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>2022</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>2023</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>2024</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>2025</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>2026</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>2027</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>2028</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>2029</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>2030</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>2031</v>
+      </c>
+      <c r="B23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>2032</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>2033</v>
+      </c>
+      <c r="B25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>2034</v>
+      </c>
+      <c r="B26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>2035</v>
+      </c>
+      <c r="B27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>2036</v>
+      </c>
+      <c r="B28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>2037</v>
+      </c>
+      <c r="B29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>2038</v>
+      </c>
+      <c r="B30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>2039</v>
+      </c>
+      <c r="B31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>2040</v>
+      </c>
+      <c r="B32">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74397DC0-DE0F-5146-BEAF-59D2E8FCDE98}">
+  <dimension ref="A1:B32"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>2010</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2011</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>2012</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>2013</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>2014</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>2015</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>2016</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>2017</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>2018</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>2019</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>2020</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>2021</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>2022</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>2023</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>2024</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>2025</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>2026</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>2027</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>2028</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>2029</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>2030</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>2031</v>
+      </c>
+      <c r="B23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>2032</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>2033</v>
+      </c>
+      <c r="B25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>2034</v>
+      </c>
+      <c r="B26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>2035</v>
+      </c>
+      <c r="B27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>2036</v>
+      </c>
+      <c r="B28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>2037</v>
+      </c>
+      <c r="B29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>2038</v>
+      </c>
+      <c r="B30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>2039</v>
+      </c>
+      <c r="B31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>2040</v>
+      </c>
+      <c r="B32">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D7429DD-438F-4396-BA37-1ECD20FCD2D9}">
+  <dimension ref="A1:B32"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>2010</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2011</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>2012</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>2013</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>2014</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>2015</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>2016</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>2017</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>2018</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>2019</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>2020</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>2021</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>2022</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>2023</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>2024</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>2025</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>2026</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>2027</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>2028</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>2029</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>2030</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>2031</v>
+      </c>
+      <c r="B23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>2032</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>2033</v>
+      </c>
+      <c r="B25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>2034</v>
+      </c>
+      <c r="B26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>2035</v>
+      </c>
+      <c r="B27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>2036</v>
+      </c>
+      <c r="B28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>2037</v>
+      </c>
+      <c r="B29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>2038</v>
+      </c>
+      <c r="B30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>2039</v>
+      </c>
+      <c r="B31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>2040</v>
+      </c>
+      <c r="B32">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83A8B1C6-B095-49F5-BE52-65A3AD804239}">
+  <dimension ref="A1:B32"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>2010</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2011</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>2012</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>2013</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>2014</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>2015</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>2016</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>2017</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>2018</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>2019</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>2020</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>2021</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>2022</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>2023</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>2024</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>2025</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>2026</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>2027</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>2028</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>2029</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>2030</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>2031</v>
+      </c>
+      <c r="B23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>2032</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>2033</v>
+      </c>
+      <c r="B25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>2034</v>
+      </c>
+      <c r="B26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>2035</v>
+      </c>
+      <c r="B27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>2036</v>
+      </c>
+      <c r="B28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>2037</v>
+      </c>
+      <c r="B29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>2038</v>
+      </c>
+      <c r="B30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>2039</v>
+      </c>
+      <c r="B31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>2040</v>
+      </c>
+      <c r="B32">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5368A556-88DB-4602-9465-944BD364475C}">
+  <dimension ref="A1:B116"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1947</v>
+      </c>
+      <c r="B2" s="1">
+        <v>16.598309271060831</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="2">
+        <v>1948</v>
+      </c>
+      <c r="B3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
+        <v>1949</v>
+      </c>
+      <c r="B4">
+        <v>17.600000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
+        <v>1950</v>
+      </c>
+      <c r="B5">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
+        <v>1951</v>
+      </c>
+      <c r="B6">
+        <v>18.899999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
+        <v>1952</v>
+      </c>
+      <c r="B7">
+        <v>19.100000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
+        <v>1953</v>
+      </c>
+      <c r="B8">
+        <v>20.2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
+        <v>1954</v>
+      </c>
+      <c r="B9">
+        <v>21.1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
+        <v>1955</v>
+      </c>
+      <c r="B10">
+        <v>21.9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
+        <v>1956</v>
+      </c>
+      <c r="B11">
+        <v>22.3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
+        <v>1957</v>
+      </c>
+      <c r="B12">
+        <v>22.7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" s="2">
+        <v>1958</v>
+      </c>
+      <c r="B13">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" s="2">
+        <v>1959</v>
+      </c>
+      <c r="B14">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" s="2">
+        <v>1960</v>
+      </c>
+      <c r="B15">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" s="2">
+        <v>1961</v>
+      </c>
+      <c r="B16">
+        <v>26.2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" s="2">
+        <v>1962</v>
+      </c>
+      <c r="B17">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" s="2">
+        <v>1963</v>
+      </c>
+      <c r="B18">
+        <v>27.8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" s="2">
+        <v>1964</v>
+      </c>
+      <c r="B19">
+        <v>29.4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" s="2">
+        <v>1965</v>
+      </c>
+      <c r="B20">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" s="2">
+        <v>1966</v>
+      </c>
+      <c r="B21">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" s="2">
+        <v>1967</v>
+      </c>
+      <c r="B22">
+        <v>31.3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" s="2">
+        <v>1968</v>
+      </c>
+      <c r="B23">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" s="2">
+        <v>1969</v>
+      </c>
+      <c r="B24">
+        <v>33.6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" s="2">
+        <v>1970</v>
+      </c>
+      <c r="B25">
+        <v>34.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" s="2">
+        <v>1971</v>
+      </c>
+      <c r="B26">
+        <v>35.799999999999997</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27" s="2">
+        <v>1972</v>
+      </c>
+      <c r="B27">
+        <v>37.299999999999997</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" s="2">
+        <v>1973</v>
+      </c>
+      <c r="B28">
+        <v>39.799999999999997</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" s="2">
+        <v>1974</v>
+      </c>
+      <c r="B29">
+        <v>38.799999999999997</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30" s="2">
+        <v>1975</v>
+      </c>
+      <c r="B30">
+        <v>38.200000000000003</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31" s="2">
+        <v>1976</v>
+      </c>
+      <c r="B31">
+        <v>39.299999999999997</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" s="2">
+        <v>1977</v>
+      </c>
+      <c r="B32">
+        <v>40.299999999999997</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" s="2">
+        <v>1978</v>
+      </c>
+      <c r="B33">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" s="2">
+        <v>1979</v>
+      </c>
+      <c r="B34">
+        <v>43.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" s="2">
+        <v>1980</v>
+      </c>
+      <c r="B35">
+        <v>42.6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" s="2">
+        <v>1981</v>
+      </c>
+      <c r="B36">
+        <v>42.3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37" s="2">
+        <v>1982</v>
+      </c>
+      <c r="B37">
+        <v>43.2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" s="2">
+        <v>1983</v>
+      </c>
+      <c r="B38">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" s="2">
+        <v>1984</v>
+      </c>
+      <c r="B39">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" s="2">
+        <v>1985</v>
+      </c>
+      <c r="B40">
+        <v>47.9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" s="2">
+        <v>1986</v>
+      </c>
+      <c r="B41">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" s="2">
+        <v>1987</v>
+      </c>
+      <c r="B42">
+        <v>52.1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43" s="2">
+        <v>1988</v>
+      </c>
+      <c r="B43">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44" s="2">
+        <v>1989</v>
+      </c>
+      <c r="B44">
+        <v>56.3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45" s="2">
+        <v>1990</v>
+      </c>
+      <c r="B45">
+        <v>56.7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46" s="2">
+        <v>1991</v>
+      </c>
+      <c r="B46">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47" s="2">
+        <v>1992</v>
+      </c>
+      <c r="B47">
+        <v>56.2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A48" s="2">
+        <v>1993</v>
+      </c>
+      <c r="B48">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49" s="2">
+        <v>1994</v>
+      </c>
+      <c r="B49">
+        <v>59.7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50" s="2">
+        <v>1995</v>
+      </c>
+      <c r="B50">
+        <v>61.2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A51" s="2">
+        <v>1996</v>
+      </c>
+      <c r="B51">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A52" s="2">
+        <v>1997</v>
+      </c>
+      <c r="B52">
+        <v>65.7</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A53" s="2">
+        <v>1998</v>
+      </c>
+      <c r="B53">
+        <v>67.8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A54" s="2">
+        <v>1999</v>
+      </c>
+      <c r="B54">
+        <v>69.8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A55" s="2">
+        <v>2000</v>
+      </c>
+      <c r="B55">
+        <v>72.400000000000006</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A56" s="2">
+        <v>2001</v>
+      </c>
+      <c r="B56">
+        <v>73.900000000000006</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A57" s="2">
+        <v>2002</v>
+      </c>
+      <c r="B57">
+        <v>75.5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A58" s="2">
+        <v>2003</v>
+      </c>
+      <c r="B58">
+        <v>77.7</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A59" s="2">
+        <v>2004</v>
+      </c>
+      <c r="B59">
+        <v>79.599999999999994</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A60" s="2">
+        <v>2005</v>
+      </c>
+      <c r="B60">
+        <v>81.599999999999994</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A61" s="2">
+        <v>2006</v>
+      </c>
+      <c r="B61">
+        <v>83.7</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A62" s="2">
+        <v>2007</v>
+      </c>
+      <c r="B62">
+        <v>85.7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A63" s="2">
+        <v>2008</v>
+      </c>
+      <c r="B63">
+        <v>85.4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A64" s="2">
+        <v>2009</v>
+      </c>
+      <c r="B64">
+        <v>81.8</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A65" s="2">
+        <v>2010</v>
+      </c>
+      <c r="B65">
+        <v>83.6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A66" s="2">
+        <v>2011</v>
+      </c>
+      <c r="B66">
+        <v>84.8</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A67" s="2">
+        <v>2012</v>
+      </c>
+      <c r="B67">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A68" s="2">
+        <v>2013</v>
+      </c>
+      <c r="B68">
+        <v>87.6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A69" s="2">
+        <v>2014</v>
+      </c>
+      <c r="B69">
+        <v>90.3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A70" s="2">
+        <v>2015</v>
+      </c>
+      <c r="B70">
+        <v>92.6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A71" s="2">
+        <v>2016</v>
+      </c>
+      <c r="B71">
+        <v>94.7</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A72" s="2">
+        <v>2017</v>
+      </c>
+      <c r="B72">
+        <v>96.8</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A73" s="2">
+        <v>2018</v>
+      </c>
+      <c r="B73">
+        <v>98.4</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A74" s="2">
+        <v>2019</v>
+      </c>
+      <c r="B74">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A75" s="2">
+        <v>2020</v>
+      </c>
+      <c r="B75">
+        <v>90.6</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A76" s="2">
+        <v>2021</v>
+      </c>
+      <c r="B76">
+        <v>97.4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A77" s="2">
+        <v>2022</v>
+      </c>
+      <c r="B77">
+        <v>99.757148331179067</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A78" s="2">
+        <v>2023</v>
+      </c>
+      <c r="B78">
+        <v>102.17134130563514</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A79" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B79">
+        <v>104.64395944375532</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A80" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B80">
+        <v>107.17641667548857</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A81" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B81">
+        <v>109.77016114888056</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A82" s="2">
+        <v>2027</v>
+      </c>
+      <c r="B82">
+        <v>112.42667605817564</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A83" s="2">
+        <v>2028</v>
+      </c>
+      <c r="B83">
+        <v>115.1474804919594</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A84" s="2">
+        <v>2029</v>
+      </c>
+      <c r="B84">
+        <v>117.9341303018269</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A85" s="2">
+        <v>2030</v>
+      </c>
+      <c r="B85">
+        <v>120.78821899207334</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A86" s="2">
+        <v>2031</v>
+      </c>
+      <c r="B86">
+        <v>123.7113786309158</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A87" s="2">
+        <v>2032</v>
+      </c>
+      <c r="B87">
+        <v>126.70528078376718</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A88" s="2">
+        <v>2033</v>
+      </c>
+      <c r="B88">
+        <v>129.77163746909605</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A89" s="2">
+        <v>2034</v>
+      </c>
+      <c r="B89">
+        <v>132.912202137419</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A90" s="2">
+        <v>2035</v>
+      </c>
+      <c r="B90">
+        <v>136.12877067398526</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A91" s="2">
+        <v>2036</v>
+      </c>
+      <c r="B91">
+        <v>139.42318242572699</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A92" s="2">
+        <v>2037</v>
+      </c>
+      <c r="B92">
+        <v>142.79732125306251</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A93" s="2">
+        <v>2038</v>
+      </c>
+      <c r="B93">
+        <v>146.25311660715386</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A94" s="2">
+        <v>2039</v>
+      </c>
+      <c r="B94">
+        <v>149.79254463323488</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A95" s="2">
+        <v>2040</v>
+      </c>
+      <c r="B95">
+        <v>153.41762930064039</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A96" s="2">
+        <v>2041</v>
+      </c>
+      <c r="B96">
+        <v>157.13044356018301</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A97" s="2">
+        <v>2042</v>
+      </c>
+      <c r="B97">
+        <v>160.93311052953939</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A98" s="2">
+        <v>2043</v>
+      </c>
+      <c r="B98">
+        <v>164.82780470732337</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A99" s="2">
+        <v>2044</v>
+      </c>
+      <c r="B99">
+        <v>168.81675321654077</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A100" s="2">
+        <v>2045</v>
+      </c>
+      <c r="B100">
+        <v>172.90223707813664</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A101" s="2">
+        <v>2046</v>
+      </c>
+      <c r="B101">
+        <v>177.08659251536309</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A102" s="2">
+        <v>2047</v>
+      </c>
+      <c r="B102">
+        <v>181.37221228971399</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A103" s="2">
+        <v>2048</v>
+      </c>
+      <c r="B103">
+        <v>185.76154706918993</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A104" s="2">
+        <v>2049</v>
+      </c>
+      <c r="B104">
+        <v>190.25710682967642</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A105" s="2">
+        <v>2050</v>
+      </c>
+      <c r="B105">
+        <v>194.86146229023626</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A106" s="2">
+        <v>2051</v>
+      </c>
+      <c r="B106">
+        <v>199.57724638313712</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A107" s="2">
+        <v>2052</v>
+      </c>
+      <c r="B107">
+        <v>204.40715575945461</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A108" s="2">
+        <v>2053</v>
+      </c>
+      <c r="B108">
+        <v>209.35395233111228</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A109" s="2">
+        <v>2054</v>
+      </c>
+      <c r="B109">
+        <v>214.42046485023982</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A110" s="2">
+        <v>2055</v>
+      </c>
+      <c r="B110">
+        <v>219.60959052675298</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A111" s="2">
+        <v>2056</v>
+      </c>
+      <c r="B111">
+        <v>224.92429668508001</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A112" s="2">
+        <v>2057</v>
+      </c>
+      <c r="B112">
+        <v>230.36762246098209</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A113" s="2">
+        <v>2058</v>
+      </c>
+      <c r="B113">
+        <v>235.9426805394379</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A114" s="2">
+        <v>2059</v>
+      </c>
+      <c r="B114">
+        <v>241.65265893458633</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A115" s="2">
+        <v>2060</v>
+      </c>
+      <c r="B115">
+        <v>247.50082281274493</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A116" s="2">
+        <v>2061</v>
+      </c>
+      <c r="B116">
+        <v>253.49051635954683</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC2B7FF6-C3ED-409F-83AB-FB5EAD53E39E}">
+  <dimension ref="A1:B42"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1987</v>
+      </c>
+      <c r="B2" s="1">
+        <v>48.34160833287882</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="2">
+        <v>1988</v>
+      </c>
+      <c r="B3" s="1">
+        <v>49.6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
+        <v>1989</v>
+      </c>
+      <c r="B4" s="1">
+        <v>52.2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
+        <v>1990</v>
+      </c>
+      <c r="B5" s="1">
+        <v>55.9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
+        <v>1991</v>
+      </c>
+      <c r="B6" s="1">
+        <v>60.1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
+        <v>1992</v>
+      </c>
+      <c r="B7" s="1">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
+        <v>1993</v>
+      </c>
+      <c r="B8" s="1">
+        <v>64.2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
+        <v>1994</v>
+      </c>
+      <c r="B9" s="1">
+        <v>65.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
+        <v>1995</v>
+      </c>
+      <c r="B10" s="1">
+        <v>67.2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
+        <v>1996</v>
+      </c>
+      <c r="B11" s="1">
+        <v>68.8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
+        <v>1997</v>
+      </c>
+      <c r="B12" s="1">
+        <v>70.099999999999994</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" s="2">
+        <v>1998</v>
+      </c>
+      <c r="B13" s="1">
+        <v>71.2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" s="2">
+        <v>1999</v>
+      </c>
+      <c r="B14" s="1">
+        <v>72.099999999999994</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" s="2">
+        <v>2000</v>
+      </c>
+      <c r="B15" s="1">
+        <v>72.7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" s="2">
+        <v>2001</v>
+      </c>
+      <c r="B16" s="1">
+        <v>73.599999999999994</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" s="2">
+        <v>2002</v>
+      </c>
+      <c r="B17" s="1">
+        <v>74.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" s="2">
+        <v>2003</v>
+      </c>
+      <c r="B18" s="1">
+        <v>75.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" s="2">
+        <v>2004</v>
+      </c>
+      <c r="B19" s="1">
+        <v>76.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" s="2">
+        <v>2005</v>
+      </c>
+      <c r="B20" s="1">
+        <v>78.099999999999994</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" s="2">
+        <v>2006</v>
+      </c>
+      <c r="B21" s="1">
+        <v>79.900000000000006</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" s="2">
+        <v>2007</v>
+      </c>
+      <c r="B22" s="1">
+        <v>81.8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" s="2">
+        <v>2008</v>
+      </c>
+      <c r="B23" s="1">
+        <v>84.7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" s="2">
+        <v>2009</v>
+      </c>
+      <c r="B24" s="1">
+        <v>86.6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" s="2">
+        <v>2010</v>
+      </c>
+      <c r="B25" s="1">
+        <v>89.4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" s="2">
+        <v>2011</v>
+      </c>
+      <c r="B26" s="1">
+        <v>93.4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27" s="2">
+        <v>2012</v>
+      </c>
+      <c r="B27" s="1">
+        <v>96.1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" s="2">
+        <v>2013</v>
+      </c>
+      <c r="B28" s="1">
+        <v>98.5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" s="2">
+        <v>2014</v>
+      </c>
+      <c r="B29" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30" s="2">
+        <v>2015</v>
+      </c>
+      <c r="B30" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31" s="2">
+        <v>2016</v>
+      </c>
+      <c r="B31" s="1">
+        <v>100.7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" s="2">
+        <v>2017</v>
+      </c>
+      <c r="B32" s="1">
+        <v>103.4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" s="2">
+        <v>2018</v>
+      </c>
+      <c r="B33" s="1">
+        <v>105.9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" s="2">
+        <v>2019</v>
+      </c>
+      <c r="B34" s="1">
+        <v>107.8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" s="2">
+        <v>2020</v>
+      </c>
+      <c r="B35" s="1">
+        <v>108.7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" s="2">
+        <v>2021</v>
+      </c>
+      <c r="B36" s="1">
+        <v>111.6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37" s="2">
+        <v>2022</v>
+      </c>
+      <c r="B37" s="1">
+        <v>121.7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" s="2">
+        <v>2023</v>
+      </c>
+      <c r="B38" s="1">
+        <v>124.57395874315898</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B39" s="1">
+        <v>126.63064241784659</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B40" s="1">
+        <v>129.11704786530214</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B41" s="1">
+        <v>131.69938882260817</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" s="2">
+        <v>2027</v>
+      </c>
+      <c r="B42" s="1">
+        <v>135.1276862908702</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F3F720F-7C77-40C9-9D26-48C5FF4C5828}">
+  <dimension ref="A1:B30"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>2000</v>
+      </c>
+      <c r="B2">
+        <v>143.29576929253196</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="2">
+        <v>2001</v>
+      </c>
+      <c r="B3">
+        <v>143.98221858016308</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
+        <v>2002</v>
+      </c>
+      <c r="B4">
+        <v>146.66557346756156</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
+        <v>2003</v>
+      </c>
+      <c r="B5">
+        <v>149.63794972406183</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
+        <v>2004</v>
+      </c>
+      <c r="B6">
+        <v>154.58310870370369</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
+        <v>2005</v>
+      </c>
+      <c r="B7">
+        <v>158.46724928510457</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
+        <v>2006</v>
+      </c>
+      <c r="B8">
+        <v>162.59473676470591</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
+        <v>2007</v>
+      </c>
+      <c r="B9">
+        <v>165.95105268948654</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
+        <v>2008</v>
+      </c>
+      <c r="B10">
+        <v>162.87314316214093</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
+        <v>2009</v>
+      </c>
+      <c r="B11">
+        <v>161.37643170708242</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
+        <v>2010</v>
+      </c>
+      <c r="B12">
+        <v>159.65128374347503</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" s="2">
+        <v>2011</v>
+      </c>
+      <c r="B13">
+        <v>155.56126007316206</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" s="2">
+        <v>2012</v>
+      </c>
+      <c r="B14">
+        <v>153.17917333506765</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" s="2">
+        <v>2013</v>
+      </c>
+      <c r="B15">
+        <v>151.43864936548223</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" s="2">
+        <v>2014</v>
+      </c>
+      <c r="B16">
+        <v>151.03810470833329</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" s="2">
+        <v>2015</v>
+      </c>
+      <c r="B17">
+        <v>154.63866195833333</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" s="2">
+        <v>2016</v>
+      </c>
+      <c r="B18">
+        <v>157.19974334657394</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" s="2">
+        <v>2017</v>
+      </c>
+      <c r="B19">
+        <v>156.93085901031591</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" s="2">
+        <v>2018</v>
+      </c>
+      <c r="B20">
+        <v>157.85818999055712</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" s="2">
+        <v>2019</v>
+      </c>
+      <c r="B21">
+        <v>160.03142759740257</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" s="2">
+        <v>2020</v>
+      </c>
+      <c r="B22">
+        <v>162.12163966045293</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" s="2">
+        <v>2021</v>
+      </c>
+      <c r="B23">
+        <v>168.45206453568233</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" s="2">
+        <v>2022</v>
+      </c>
+      <c r="B24">
+        <v>162.20759979943486</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" s="2">
+        <v>2023</v>
+      </c>
+      <c r="B25">
+        <v>164.79602326504056</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B26">
+        <v>163.94277212602779</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B27">
+        <v>163.18350470648323</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B28">
+        <v>163.21856984752483</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" s="2">
+        <v>2027</v>
+      </c>
+      <c r="B29">
+        <v>163.03155667222143</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30" s="2">
+        <v>2028</v>
+      </c>
+      <c r="B30">
+        <v>163.81254899663941</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AE1C571-12D2-48EC-9676-C9293E844074}">
+  <dimension ref="A1:B38"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1986</v>
+      </c>
+      <c r="B2" s="3">
+        <v>4.6286405160227334E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1987</v>
+      </c>
+      <c r="B3" s="3">
+        <v>3.011788658083403E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>1988</v>
+      </c>
+      <c r="B4" s="3">
+        <v>0.12856812528973971</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>1989</v>
+      </c>
+      <c r="B5" s="3">
+        <v>0.13600529394329053</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>1990</v>
+      </c>
+      <c r="B6" s="3">
+        <v>-4.1070497545090956E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>1991</v>
+      </c>
+      <c r="B7" s="3">
+        <v>5.7350544024686867E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>1992</v>
+      </c>
+      <c r="B8" s="3">
+        <v>5.7631202236563261E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>1993</v>
+      </c>
+      <c r="B9" s="3">
+        <v>7.8989706216779254E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>1994</v>
+      </c>
+      <c r="B10" s="3">
+        <v>-1.128760392020467E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>1995</v>
+      </c>
+      <c r="B11" s="3">
+        <v>9.2160859105373527E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>1996</v>
+      </c>
+      <c r="B12" s="3">
+        <v>8.5586180972958781E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>1997</v>
+      </c>
+      <c r="B13" s="3">
+        <v>0.13646101577698233</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>1998</v>
+      </c>
+      <c r="B14" s="3">
+        <v>0.12375668034877796</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>1999</v>
+      </c>
+      <c r="B15" s="3">
+        <v>0.14456105557563292</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>2000</v>
+      </c>
+      <c r="B16" s="3">
+        <v>1.2753813678981984E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>2001</v>
+      </c>
+      <c r="B17" s="3">
+        <v>-2.1653766849825229E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>2002</v>
+      </c>
+      <c r="B18" s="3">
+        <v>-3.0859935638595126E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>2003</v>
+      </c>
+      <c r="B19" s="3">
+        <v>0.13021265938759741</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>2004</v>
+      </c>
+      <c r="B20" s="3">
+        <v>0.11284628713988498</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>2005</v>
+      </c>
+      <c r="B21" s="3">
+        <v>9.5700435119939753E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>2006</v>
+      </c>
+      <c r="B22" s="3">
+        <v>8.3497102825924818E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>2007</v>
+      </c>
+      <c r="B23" s="3">
+        <v>5.4036728450648441E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>2008</v>
+      </c>
+      <c r="B24" s="3">
+        <v>-0.16066262517109864</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>2009</v>
+      </c>
+      <c r="B25" s="3">
+        <v>8.877196143526267E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>2010</v>
+      </c>
+      <c r="B26" s="3">
+        <v>5.6774110668480482E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>2011</v>
+      </c>
+      <c r="B27" s="3">
+        <v>-2.7392490880683962E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>2012</v>
+      </c>
+      <c r="B28" s="3">
+        <v>-2.2124513898473808E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>2013</v>
+      </c>
+      <c r="B29" s="3">
+        <v>7.5335930021486197E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>2014</v>
+      </c>
+      <c r="B30" s="3">
+        <v>7.9340966880817376E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>2015</v>
+      </c>
+      <c r="B31" s="3">
+        <v>4.2381070018058686E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>2016</v>
+      </c>
+      <c r="B32" s="3">
+        <v>-4.8974784087532974E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>2017</v>
+      </c>
+      <c r="B33" s="3">
+        <v>7.0170871889905673E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>2018</v>
+      </c>
+      <c r="B34" s="3">
+        <v>2.840535022977253E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>2019</v>
+      </c>
+      <c r="B35" s="3">
+        <v>6.3714730205470804E-3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>2020</v>
+      </c>
+      <c r="B36" s="3">
+        <v>-7.3040697759606754E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>2021</v>
+      </c>
+      <c r="B37" s="3">
+        <v>4.9303785520141474E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>2022</v>
+      </c>
+      <c r="B38" s="3">
+        <v>4.6286405160227334E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF70C8B1-8A2A-4CB2-AE85-70911F99E869}">
+  <dimension ref="A1:B30"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1994</v>
+      </c>
+      <c r="B2" s="3">
+        <v>6.0198436757189541E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1995</v>
+      </c>
+      <c r="B3" s="3">
+        <v>0.16844999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>1996</v>
+      </c>
+      <c r="B4" s="3">
+        <v>0.14020833333333335</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>1997</v>
+      </c>
+      <c r="B5" s="3">
+        <v>0.13783333333333334</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>1998</v>
+      </c>
+      <c r="B6" s="3">
+        <v>0.13462499999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>1999</v>
+      </c>
+      <c r="B7" s="3">
+        <v>0.12176666666666668</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>2000</v>
+      </c>
+      <c r="B8" s="3">
+        <v>0.11730833333333335</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>2001</v>
+      </c>
+      <c r="B9" s="3">
+        <v>0.11916666666666666</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>2002</v>
+      </c>
+      <c r="B10" s="3">
+        <v>0.10499166666666665</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>2003</v>
+      </c>
+      <c r="B11" s="3">
+        <v>8.4600000000000009E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>2004</v>
+      </c>
+      <c r="B12" s="3">
+        <v>8.0033333333333359E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>2005</v>
+      </c>
+      <c r="B13" s="3">
+        <v>7.3700000000000002E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>2006</v>
+      </c>
+      <c r="B14" s="3">
+        <v>7.1808333333333349E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>2007</v>
+      </c>
+      <c r="B15" s="3">
+        <v>7.6283333333333328E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>2008</v>
+      </c>
+      <c r="B16" s="3">
+        <v>9.0599999999999972E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>2009</v>
+      </c>
+      <c r="B17" s="3">
+        <v>0.10090833333333332</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>2010</v>
+      </c>
+      <c r="B18" s="3">
+        <v>9.2591666666666669E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>2011</v>
+      </c>
+      <c r="B19" s="3">
+        <v>8.7499999999999981E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>2012</v>
+      </c>
+      <c r="B20" s="3">
+        <v>7.4383333333333329E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>2013</v>
+      </c>
+      <c r="B21" s="3">
+        <v>6.0299999999999999E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>2014</v>
+      </c>
+      <c r="B22" s="3">
+        <v>4.9799999999999997E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>2015</v>
+      </c>
+      <c r="B23" s="3">
+        <v>4.331666666666667E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>2016</v>
+      </c>
+      <c r="B24" s="3">
+        <v>3.9683333333333334E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>2017</v>
+      </c>
+      <c r="B25" s="3">
+        <v>3.7991666666666667E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>2018</v>
+      </c>
+      <c r="B26" s="3">
+        <v>3.7691666666666665E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>2019</v>
+      </c>
+      <c r="B27" s="3">
+        <v>3.6141666666666662E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>2020</v>
+      </c>
+      <c r="B28" s="3">
+        <v>3.5466666666666667E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>2021</v>
+      </c>
+      <c r="B29" s="3">
+        <v>3.8266666666666664E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>2022</v>
+      </c>
+      <c r="B30" s="3">
+        <v>6.0198436757189541E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE5D1202-306C-4A3E-BE31-47D9872C9300}">
+  <dimension ref="A1:B30"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1994</v>
+      </c>
+      <c r="B2" s="3">
+        <v>0.15704228576200643</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1995</v>
+      </c>
+      <c r="B3" s="3">
+        <v>0.22755833333333339</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>1996</v>
+      </c>
+      <c r="B4" s="3">
+        <v>0.22240833333333332</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>1997</v>
+      </c>
+      <c r="B5" s="3">
+        <v>0.22367499999999996</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>1998</v>
+      </c>
+      <c r="B6" s="3">
+        <v>0.21951666666666669</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>1999</v>
+      </c>
+      <c r="B7" s="3">
+        <v>0.19584999999999997</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>2000</v>
+      </c>
+      <c r="B8" s="3">
+        <v>0.18845833333333334</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>2001</v>
+      </c>
+      <c r="B9" s="3">
+        <v>0.17802499999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>2002</v>
+      </c>
+      <c r="B10" s="3">
+        <v>0.15925000000000003</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>2003</v>
+      </c>
+      <c r="B11" s="3">
+        <v>0.15108333333333335</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>2004</v>
+      </c>
+      <c r="B12" s="3">
+        <v>0.1561916666666667</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>2005</v>
+      </c>
+      <c r="B13" s="3">
+        <v>0.16120833333333334</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>2006</v>
+      </c>
+      <c r="B14" s="3">
+        <v>0.16125833333333334</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>2007</v>
+      </c>
+      <c r="B15" s="3">
+        <v>0.15259999999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>2008</v>
+      </c>
+      <c r="B16" s="3">
+        <v>0.15983333333333333</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>2009</v>
+      </c>
+      <c r="B17" s="3">
+        <v>0.16043333333333332</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>2010</v>
+      </c>
+      <c r="B18" s="3">
+        <v>0.16666666666666669</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>2011</v>
+      </c>
+      <c r="B19" s="3">
+        <v>0.16936666666666664</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>2012</v>
+      </c>
+      <c r="B20" s="3">
+        <v>0.17374999999999996</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>2013</v>
+      </c>
+      <c r="B21" s="3">
+        <v>0.17915</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>2014</v>
+      </c>
+      <c r="B22" s="3">
+        <v>0.17576666666666668</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>2015</v>
+      </c>
+      <c r="B23" s="3">
+        <v>0.17913333333333334</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>2016</v>
+      </c>
+      <c r="B24" s="3">
+        <v>0.17950833333333335</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>2017</v>
+      </c>
+      <c r="B25" s="3">
+        <v>0.17944166666666667</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>2018</v>
+      </c>
+      <c r="B26" s="3">
+        <v>0.18666666666666665</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>2019</v>
+      </c>
+      <c r="B27" s="3">
+        <v>0.20248333333333332</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>2020</v>
+      </c>
+      <c r="B28" s="3">
+        <v>0.20790000000000003</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>2021</v>
+      </c>
+      <c r="B29" s="3">
+        <v>0.21439999999999998</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>2022</v>
+      </c>
+      <c r="B30" s="3">
+        <v>0.15704228576200643</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4C9E94E-195D-449C-95FA-8827E1CD938F}">
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>2010</v>
+      </c>
+      <c r="B2">
+        <v>9.0451221008231997</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2011</v>
+      </c>
+      <c r="B3" s="7">
+        <v>9.1220556745181991</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>2012</v>
+      </c>
+      <c r="B4" s="7">
+        <v>8.9177939646201878</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>2013</v>
+      </c>
+      <c r="B5" s="7">
+        <v>8.7106598984771573</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>2014</v>
+      </c>
+      <c r="B6" s="7">
+        <v>8.58</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>2015</v>
+      </c>
+      <c r="B7" s="7">
+        <v>8.7899999999999991</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>2016</v>
+      </c>
+      <c r="B8" s="7">
+        <v>9.1360476663356494</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>2017</v>
+      </c>
+      <c r="B9" s="7">
+        <v>9.2263056092843314</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>2018</v>
+      </c>
+      <c r="B10" s="7">
+        <v>9.3767705382436262</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>2019</v>
+      </c>
+      <c r="B11" s="7">
+        <v>9.6103896103896105</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>2020</v>
+      </c>
+      <c r="B12" s="7">
+        <v>9.9724011039558409</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>2021</v>
+      </c>
+      <c r="B13" s="7">
+        <v>9.9283154121863806</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>2022</v>
+      </c>
+      <c r="B14" s="7">
+        <v>10.012761014679809</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -1121,3010 +4657,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D7429DD-438F-4396-BA37-1ECD20FCD2D9}">
-  <dimension ref="A1:B32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>2010</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>2011</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>2012</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>2013</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>2014</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>2015</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>2016</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>2017</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>2018</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>2019</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>2020</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>2021</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>2022</v>
-      </c>
-      <c r="B14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>2023</v>
-      </c>
-      <c r="B15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A16">
-        <v>2024</v>
-      </c>
-      <c r="B16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17">
-        <v>2025</v>
-      </c>
-      <c r="B17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18">
-        <v>2026</v>
-      </c>
-      <c r="B18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19">
-        <v>2027</v>
-      </c>
-      <c r="B19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20">
-        <v>2028</v>
-      </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A21">
-        <v>2029</v>
-      </c>
-      <c r="B21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22">
-        <v>2030</v>
-      </c>
-      <c r="B22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23">
-        <v>2031</v>
-      </c>
-      <c r="B23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A24">
-        <v>2032</v>
-      </c>
-      <c r="B24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25">
-        <v>2033</v>
-      </c>
-      <c r="B25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A26">
-        <v>2034</v>
-      </c>
-      <c r="B26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A27">
-        <v>2035</v>
-      </c>
-      <c r="B27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A28">
-        <v>2036</v>
-      </c>
-      <c r="B28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A29">
-        <v>2037</v>
-      </c>
-      <c r="B29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A30">
-        <v>2038</v>
-      </c>
-      <c r="B30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A31">
-        <v>2039</v>
-      </c>
-      <c r="B31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A32">
-        <v>2040</v>
-      </c>
-      <c r="B32">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83A8B1C6-B095-49F5-BE52-65A3AD804239}">
-  <dimension ref="A1:B32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>2010</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>2011</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>2012</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>2013</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>2014</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>2015</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>2016</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>2017</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>2018</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>2019</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>2020</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>2021</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>2022</v>
-      </c>
-      <c r="B14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>2023</v>
-      </c>
-      <c r="B15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A16">
-        <v>2024</v>
-      </c>
-      <c r="B16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17">
-        <v>2025</v>
-      </c>
-      <c r="B17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18">
-        <v>2026</v>
-      </c>
-      <c r="B18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19">
-        <v>2027</v>
-      </c>
-      <c r="B19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20">
-        <v>2028</v>
-      </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A21">
-        <v>2029</v>
-      </c>
-      <c r="B21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22">
-        <v>2030</v>
-      </c>
-      <c r="B22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23">
-        <v>2031</v>
-      </c>
-      <c r="B23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A24">
-        <v>2032</v>
-      </c>
-      <c r="B24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25">
-        <v>2033</v>
-      </c>
-      <c r="B25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A26">
-        <v>2034</v>
-      </c>
-      <c r="B26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A27">
-        <v>2035</v>
-      </c>
-      <c r="B27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A28">
-        <v>2036</v>
-      </c>
-      <c r="B28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A29">
-        <v>2037</v>
-      </c>
-      <c r="B29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A30">
-        <v>2038</v>
-      </c>
-      <c r="B30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A31">
-        <v>2039</v>
-      </c>
-      <c r="B31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A32">
-        <v>2040</v>
-      </c>
-      <c r="B32">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5368A556-88DB-4602-9465-944BD364475C}">
-  <dimension ref="A1:B116"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>1947</v>
-      </c>
-      <c r="B2" s="1">
-        <v>16.598309271060831</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="2">
-        <v>1948</v>
-      </c>
-      <c r="B3">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" s="2">
-        <v>1949</v>
-      </c>
-      <c r="B4">
-        <v>17.600000000000001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" s="2">
-        <v>1950</v>
-      </c>
-      <c r="B5">
-        <v>18.2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" s="2">
-        <v>1951</v>
-      </c>
-      <c r="B6">
-        <v>18.899999999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" s="2">
-        <v>1952</v>
-      </c>
-      <c r="B7">
-        <v>19.100000000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" s="2">
-        <v>1953</v>
-      </c>
-      <c r="B8">
-        <v>20.2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" s="2">
-        <v>1954</v>
-      </c>
-      <c r="B9">
-        <v>21.1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" s="2">
-        <v>1955</v>
-      </c>
-      <c r="B10">
-        <v>21.9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" s="2">
-        <v>1956</v>
-      </c>
-      <c r="B11">
-        <v>22.3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12" s="2">
-        <v>1957</v>
-      </c>
-      <c r="B12">
-        <v>22.7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13" s="2">
-        <v>1958</v>
-      </c>
-      <c r="B13">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14" s="2">
-        <v>1959</v>
-      </c>
-      <c r="B14">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A15" s="2">
-        <v>1960</v>
-      </c>
-      <c r="B15">
-        <v>25.5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A16" s="2">
-        <v>1961</v>
-      </c>
-      <c r="B16">
-        <v>26.2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17" s="2">
-        <v>1962</v>
-      </c>
-      <c r="B17">
-        <v>26.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18" s="2">
-        <v>1963</v>
-      </c>
-      <c r="B18">
-        <v>27.8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19" s="2">
-        <v>1964</v>
-      </c>
-      <c r="B19">
-        <v>29.4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20" s="2">
-        <v>1965</v>
-      </c>
-      <c r="B20">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A21" s="2">
-        <v>1966</v>
-      </c>
-      <c r="B21">
-        <v>30.5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22" s="2">
-        <v>1967</v>
-      </c>
-      <c r="B22">
-        <v>31.3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23" s="2">
-        <v>1968</v>
-      </c>
-      <c r="B23">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A24" s="2">
-        <v>1969</v>
-      </c>
-      <c r="B24">
-        <v>33.6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25" s="2">
-        <v>1970</v>
-      </c>
-      <c r="B25">
-        <v>34.5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A26" s="2">
-        <v>1971</v>
-      </c>
-      <c r="B26">
-        <v>35.799999999999997</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A27" s="2">
-        <v>1972</v>
-      </c>
-      <c r="B27">
-        <v>37.299999999999997</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A28" s="2">
-        <v>1973</v>
-      </c>
-      <c r="B28">
-        <v>39.799999999999997</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A29" s="2">
-        <v>1974</v>
-      </c>
-      <c r="B29">
-        <v>38.799999999999997</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A30" s="2">
-        <v>1975</v>
-      </c>
-      <c r="B30">
-        <v>38.200000000000003</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A31" s="2">
-        <v>1976</v>
-      </c>
-      <c r="B31">
-        <v>39.299999999999997</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A32" s="2">
-        <v>1977</v>
-      </c>
-      <c r="B32">
-        <v>40.299999999999997</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A33" s="2">
-        <v>1978</v>
-      </c>
-      <c r="B33">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A34" s="2">
-        <v>1979</v>
-      </c>
-      <c r="B34">
-        <v>43.5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A35" s="2">
-        <v>1980</v>
-      </c>
-      <c r="B35">
-        <v>42.6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A36" s="2">
-        <v>1981</v>
-      </c>
-      <c r="B36">
-        <v>42.3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A37" s="2">
-        <v>1982</v>
-      </c>
-      <c r="B37">
-        <v>43.2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A38" s="2">
-        <v>1983</v>
-      </c>
-      <c r="B38">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A39" s="2">
-        <v>1984</v>
-      </c>
-      <c r="B39">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A40" s="2">
-        <v>1985</v>
-      </c>
-      <c r="B40">
-        <v>47.9</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A41" s="2">
-        <v>1986</v>
-      </c>
-      <c r="B41">
-        <v>49.4</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A42" s="2">
-        <v>1987</v>
-      </c>
-      <c r="B42">
-        <v>52.1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A43" s="2">
-        <v>1988</v>
-      </c>
-      <c r="B43">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A44" s="2">
-        <v>1989</v>
-      </c>
-      <c r="B44">
-        <v>56.3</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A45" s="2">
-        <v>1990</v>
-      </c>
-      <c r="B45">
-        <v>56.7</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A46" s="2">
-        <v>1991</v>
-      </c>
-      <c r="B46">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A47" s="2">
-        <v>1992</v>
-      </c>
-      <c r="B47">
-        <v>56.2</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A48" s="2">
-        <v>1993</v>
-      </c>
-      <c r="B48">
-        <v>57.5</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A49" s="2">
-        <v>1994</v>
-      </c>
-      <c r="B49">
-        <v>59.7</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A50" s="2">
-        <v>1995</v>
-      </c>
-      <c r="B50">
-        <v>61.2</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A51" s="2">
-        <v>1996</v>
-      </c>
-      <c r="B51">
-        <v>62.6</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A52" s="2">
-        <v>1997</v>
-      </c>
-      <c r="B52">
-        <v>65.7</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A53" s="2">
-        <v>1998</v>
-      </c>
-      <c r="B53">
-        <v>67.8</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A54" s="2">
-        <v>1999</v>
-      </c>
-      <c r="B54">
-        <v>69.8</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A55" s="2">
-        <v>2000</v>
-      </c>
-      <c r="B55">
-        <v>72.400000000000006</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A56" s="2">
-        <v>2001</v>
-      </c>
-      <c r="B56">
-        <v>73.900000000000006</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A57" s="2">
-        <v>2002</v>
-      </c>
-      <c r="B57">
-        <v>75.5</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A58" s="2">
-        <v>2003</v>
-      </c>
-      <c r="B58">
-        <v>77.7</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A59" s="2">
-        <v>2004</v>
-      </c>
-      <c r="B59">
-        <v>79.599999999999994</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A60" s="2">
-        <v>2005</v>
-      </c>
-      <c r="B60">
-        <v>81.599999999999994</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A61" s="2">
-        <v>2006</v>
-      </c>
-      <c r="B61">
-        <v>83.7</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A62" s="2">
-        <v>2007</v>
-      </c>
-      <c r="B62">
-        <v>85.7</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A63" s="2">
-        <v>2008</v>
-      </c>
-      <c r="B63">
-        <v>85.4</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A64" s="2">
-        <v>2009</v>
-      </c>
-      <c r="B64">
-        <v>81.8</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A65" s="2">
-        <v>2010</v>
-      </c>
-      <c r="B65">
-        <v>83.6</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A66" s="2">
-        <v>2011</v>
-      </c>
-      <c r="B66">
-        <v>84.8</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A67" s="2">
-        <v>2012</v>
-      </c>
-      <c r="B67">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A68" s="2">
-        <v>2013</v>
-      </c>
-      <c r="B68">
-        <v>87.6</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A69" s="2">
-        <v>2014</v>
-      </c>
-      <c r="B69">
-        <v>90.3</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A70" s="2">
-        <v>2015</v>
-      </c>
-      <c r="B70">
-        <v>92.6</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A71" s="2">
-        <v>2016</v>
-      </c>
-      <c r="B71">
-        <v>94.7</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A72" s="2">
-        <v>2017</v>
-      </c>
-      <c r="B72">
-        <v>96.8</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A73" s="2">
-        <v>2018</v>
-      </c>
-      <c r="B73">
-        <v>98.4</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A74" s="2">
-        <v>2019</v>
-      </c>
-      <c r="B74">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A75" s="2">
-        <v>2020</v>
-      </c>
-      <c r="B75">
-        <v>90.6</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A76" s="2">
-        <v>2021</v>
-      </c>
-      <c r="B76">
-        <v>97.4</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A77" s="2">
-        <v>2022</v>
-      </c>
-      <c r="B77">
-        <v>99.757148331179067</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A78" s="2">
-        <v>2023</v>
-      </c>
-      <c r="B78">
-        <v>102.17134130563514</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A79" s="2">
-        <v>2024</v>
-      </c>
-      <c r="B79">
-        <v>104.64395944375532</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A80" s="2">
-        <v>2025</v>
-      </c>
-      <c r="B80">
-        <v>107.17641667548857</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A81" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B81">
-        <v>109.77016114888056</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A82" s="2">
-        <v>2027</v>
-      </c>
-      <c r="B82">
-        <v>112.42667605817564</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A83" s="2">
-        <v>2028</v>
-      </c>
-      <c r="B83">
-        <v>115.1474804919594</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A84" s="2">
-        <v>2029</v>
-      </c>
-      <c r="B84">
-        <v>117.9341303018269</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A85" s="2">
-        <v>2030</v>
-      </c>
-      <c r="B85">
-        <v>120.78821899207334</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A86" s="2">
-        <v>2031</v>
-      </c>
-      <c r="B86">
-        <v>123.7113786309158</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A87" s="2">
-        <v>2032</v>
-      </c>
-      <c r="B87">
-        <v>126.70528078376718</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A88" s="2">
-        <v>2033</v>
-      </c>
-      <c r="B88">
-        <v>129.77163746909605</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A89" s="2">
-        <v>2034</v>
-      </c>
-      <c r="B89">
-        <v>132.912202137419</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A90" s="2">
-        <v>2035</v>
-      </c>
-      <c r="B90">
-        <v>136.12877067398526</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A91" s="2">
-        <v>2036</v>
-      </c>
-      <c r="B91">
-        <v>139.42318242572699</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A92" s="2">
-        <v>2037</v>
-      </c>
-      <c r="B92">
-        <v>142.79732125306251</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A93" s="2">
-        <v>2038</v>
-      </c>
-      <c r="B93">
-        <v>146.25311660715386</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A94" s="2">
-        <v>2039</v>
-      </c>
-      <c r="B94">
-        <v>149.79254463323488</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A95" s="2">
-        <v>2040</v>
-      </c>
-      <c r="B95">
-        <v>153.41762930064039</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A96" s="2">
-        <v>2041</v>
-      </c>
-      <c r="B96">
-        <v>157.13044356018301</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A97" s="2">
-        <v>2042</v>
-      </c>
-      <c r="B97">
-        <v>160.93311052953939</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A98" s="2">
-        <v>2043</v>
-      </c>
-      <c r="B98">
-        <v>164.82780470732337</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A99" s="2">
-        <v>2044</v>
-      </c>
-      <c r="B99">
-        <v>168.81675321654077</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A100" s="2">
-        <v>2045</v>
-      </c>
-      <c r="B100">
-        <v>172.90223707813664</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A101" s="2">
-        <v>2046</v>
-      </c>
-      <c r="B101">
-        <v>177.08659251536309</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A102" s="2">
-        <v>2047</v>
-      </c>
-      <c r="B102">
-        <v>181.37221228971399</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A103" s="2">
-        <v>2048</v>
-      </c>
-      <c r="B103">
-        <v>185.76154706918993</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A104" s="2">
-        <v>2049</v>
-      </c>
-      <c r="B104">
-        <v>190.25710682967642</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A105" s="2">
-        <v>2050</v>
-      </c>
-      <c r="B105">
-        <v>194.86146229023626</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A106" s="2">
-        <v>2051</v>
-      </c>
-      <c r="B106">
-        <v>199.57724638313712</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A107" s="2">
-        <v>2052</v>
-      </c>
-      <c r="B107">
-        <v>204.40715575945461</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A108" s="2">
-        <v>2053</v>
-      </c>
-      <c r="B108">
-        <v>209.35395233111228</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A109" s="2">
-        <v>2054</v>
-      </c>
-      <c r="B109">
-        <v>214.42046485023982</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A110" s="2">
-        <v>2055</v>
-      </c>
-      <c r="B110">
-        <v>219.60959052675298</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A111" s="2">
-        <v>2056</v>
-      </c>
-      <c r="B111">
-        <v>224.92429668508001</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A112" s="2">
-        <v>2057</v>
-      </c>
-      <c r="B112">
-        <v>230.36762246098209</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A113" s="2">
-        <v>2058</v>
-      </c>
-      <c r="B113">
-        <v>235.9426805394379</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A114" s="2">
-        <v>2059</v>
-      </c>
-      <c r="B114">
-        <v>241.65265893458633</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A115" s="2">
-        <v>2060</v>
-      </c>
-      <c r="B115">
-        <v>247.50082281274493</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A116" s="2">
-        <v>2061</v>
-      </c>
-      <c r="B116">
-        <v>253.49051635954683</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC2B7FF6-C3ED-409F-83AB-FB5EAD53E39E}">
-  <dimension ref="A1:B42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>1987</v>
-      </c>
-      <c r="B2" s="1">
-        <v>48.34160833287882</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="2">
-        <v>1988</v>
-      </c>
-      <c r="B3" s="1">
-        <v>49.6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" s="2">
-        <v>1989</v>
-      </c>
-      <c r="B4" s="1">
-        <v>52.2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" s="2">
-        <v>1990</v>
-      </c>
-      <c r="B5" s="1">
-        <v>55.9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" s="2">
-        <v>1991</v>
-      </c>
-      <c r="B6" s="1">
-        <v>60.1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" s="2">
-        <v>1992</v>
-      </c>
-      <c r="B7" s="1">
-        <v>62.6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" s="2">
-        <v>1993</v>
-      </c>
-      <c r="B8" s="1">
-        <v>64.2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" s="2">
-        <v>1994</v>
-      </c>
-      <c r="B9" s="1">
-        <v>65.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" s="2">
-        <v>1995</v>
-      </c>
-      <c r="B10" s="1">
-        <v>67.2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" s="2">
-        <v>1996</v>
-      </c>
-      <c r="B11" s="1">
-        <v>68.8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12" s="2">
-        <v>1997</v>
-      </c>
-      <c r="B12" s="1">
-        <v>70.099999999999994</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13" s="2">
-        <v>1998</v>
-      </c>
-      <c r="B13" s="1">
-        <v>71.2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14" s="2">
-        <v>1999</v>
-      </c>
-      <c r="B14" s="1">
-        <v>72.099999999999994</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A15" s="2">
-        <v>2000</v>
-      </c>
-      <c r="B15" s="1">
-        <v>72.7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A16" s="2">
-        <v>2001</v>
-      </c>
-      <c r="B16" s="1">
-        <v>73.599999999999994</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17" s="2">
-        <v>2002</v>
-      </c>
-      <c r="B17" s="1">
-        <v>74.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18" s="2">
-        <v>2003</v>
-      </c>
-      <c r="B18" s="1">
-        <v>75.5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19" s="2">
-        <v>2004</v>
-      </c>
-      <c r="B19" s="1">
-        <v>76.5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20" s="2">
-        <v>2005</v>
-      </c>
-      <c r="B20" s="1">
-        <v>78.099999999999994</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A21" s="2">
-        <v>2006</v>
-      </c>
-      <c r="B21" s="1">
-        <v>79.900000000000006</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22" s="2">
-        <v>2007</v>
-      </c>
-      <c r="B22" s="1">
-        <v>81.8</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23" s="2">
-        <v>2008</v>
-      </c>
-      <c r="B23" s="1">
-        <v>84.7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A24" s="2">
-        <v>2009</v>
-      </c>
-      <c r="B24" s="1">
-        <v>86.6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25" s="2">
-        <v>2010</v>
-      </c>
-      <c r="B25" s="1">
-        <v>89.4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A26" s="2">
-        <v>2011</v>
-      </c>
-      <c r="B26" s="1">
-        <v>93.4</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A27" s="2">
-        <v>2012</v>
-      </c>
-      <c r="B27" s="1">
-        <v>96.1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A28" s="2">
-        <v>2013</v>
-      </c>
-      <c r="B28" s="1">
-        <v>98.5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A29" s="2">
-        <v>2014</v>
-      </c>
-      <c r="B29" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A30" s="2">
-        <v>2015</v>
-      </c>
-      <c r="B30" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A31" s="2">
-        <v>2016</v>
-      </c>
-      <c r="B31" s="1">
-        <v>100.7</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A32" s="2">
-        <v>2017</v>
-      </c>
-      <c r="B32" s="1">
-        <v>103.4</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A33" s="2">
-        <v>2018</v>
-      </c>
-      <c r="B33" s="1">
-        <v>105.9</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A34" s="2">
-        <v>2019</v>
-      </c>
-      <c r="B34" s="1">
-        <v>107.8</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A35" s="2">
-        <v>2020</v>
-      </c>
-      <c r="B35" s="1">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A36" s="2">
-        <v>2021</v>
-      </c>
-      <c r="B36" s="1">
-        <v>111.6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A37" s="2">
-        <v>2022</v>
-      </c>
-      <c r="B37" s="1">
-        <v>121.7</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A38" s="2">
-        <v>2023</v>
-      </c>
-      <c r="B38" s="1">
-        <v>124.57395874315898</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A39" s="2">
-        <v>2024</v>
-      </c>
-      <c r="B39" s="1">
-        <v>126.63064241784659</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A40" s="2">
-        <v>2025</v>
-      </c>
-      <c r="B40" s="1">
-        <v>129.11704786530214</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A41" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B41" s="1">
-        <v>131.69938882260817</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A42" s="2">
-        <v>2027</v>
-      </c>
-      <c r="B42" s="1">
-        <v>135.1276862908702</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F3F720F-7C77-40C9-9D26-48C5FF4C5828}">
-  <dimension ref="A1:B30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>2000</v>
-      </c>
-      <c r="B2">
-        <v>143.29576929253196</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="2">
-        <v>2001</v>
-      </c>
-      <c r="B3">
-        <v>143.98221858016308</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" s="2">
-        <v>2002</v>
-      </c>
-      <c r="B4">
-        <v>146.66557346756156</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" s="2">
-        <v>2003</v>
-      </c>
-      <c r="B5">
-        <v>149.63794972406183</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" s="2">
-        <v>2004</v>
-      </c>
-      <c r="B6">
-        <v>154.58310870370369</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" s="2">
-        <v>2005</v>
-      </c>
-      <c r="B7">
-        <v>158.46724928510457</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" s="2">
-        <v>2006</v>
-      </c>
-      <c r="B8">
-        <v>162.59473676470591</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" s="2">
-        <v>2007</v>
-      </c>
-      <c r="B9">
-        <v>165.95105268948654</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" s="2">
-        <v>2008</v>
-      </c>
-      <c r="B10">
-        <v>162.87314316214093</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" s="2">
-        <v>2009</v>
-      </c>
-      <c r="B11">
-        <v>161.37643170708242</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12" s="2">
-        <v>2010</v>
-      </c>
-      <c r="B12">
-        <v>159.65128374347503</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13" s="2">
-        <v>2011</v>
-      </c>
-      <c r="B13">
-        <v>155.56126007316206</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14" s="2">
-        <v>2012</v>
-      </c>
-      <c r="B14">
-        <v>153.17917333506765</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A15" s="2">
-        <v>2013</v>
-      </c>
-      <c r="B15">
-        <v>151.43864936548223</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A16" s="2">
-        <v>2014</v>
-      </c>
-      <c r="B16">
-        <v>151.03810470833329</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17" s="2">
-        <v>2015</v>
-      </c>
-      <c r="B17">
-        <v>154.63866195833333</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18" s="2">
-        <v>2016</v>
-      </c>
-      <c r="B18">
-        <v>157.19974334657394</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19" s="2">
-        <v>2017</v>
-      </c>
-      <c r="B19">
-        <v>156.93085901031591</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20" s="2">
-        <v>2018</v>
-      </c>
-      <c r="B20">
-        <v>157.85818999055712</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A21" s="2">
-        <v>2019</v>
-      </c>
-      <c r="B21">
-        <v>160.03142759740257</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22" s="2">
-        <v>2020</v>
-      </c>
-      <c r="B22">
-        <v>162.12163966045293</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23" s="2">
-        <v>2021</v>
-      </c>
-      <c r="B23">
-        <v>168.45206453568233</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A24" s="2">
-        <v>2022</v>
-      </c>
-      <c r="B24">
-        <v>162.20759979943486</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25" s="2">
-        <v>2023</v>
-      </c>
-      <c r="B25">
-        <v>164.79602326504056</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A26" s="2">
-        <v>2024</v>
-      </c>
-      <c r="B26">
-        <v>163.94277212602779</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A27" s="2">
-        <v>2025</v>
-      </c>
-      <c r="B27">
-        <v>163.18350470648323</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A28" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B28">
-        <v>163.21856984752483</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A29" s="2">
-        <v>2027</v>
-      </c>
-      <c r="B29">
-        <v>163.03155667222143</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A30" s="2">
-        <v>2028</v>
-      </c>
-      <c r="B30">
-        <v>163.81254899663941</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AE1C571-12D2-48EC-9676-C9293E844074}">
-  <dimension ref="A1:B38"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>1986</v>
-      </c>
-      <c r="B2" s="3">
-        <v>4.6286405160227334E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>1987</v>
-      </c>
-      <c r="B3" s="3">
-        <v>3.011788658083403E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>1988</v>
-      </c>
-      <c r="B4" s="3">
-        <v>0.12856812528973971</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>1989</v>
-      </c>
-      <c r="B5" s="3">
-        <v>0.13600529394329053</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>1990</v>
-      </c>
-      <c r="B6" s="3">
-        <v>-4.1070497545090956E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>1991</v>
-      </c>
-      <c r="B7" s="3">
-        <v>5.7350544024686867E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>1992</v>
-      </c>
-      <c r="B8" s="3">
-        <v>5.7631202236563261E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>1993</v>
-      </c>
-      <c r="B9" s="3">
-        <v>7.8989706216779254E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>1994</v>
-      </c>
-      <c r="B10" s="3">
-        <v>-1.128760392020467E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>1995</v>
-      </c>
-      <c r="B11" s="3">
-        <v>9.2160859105373527E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>1996</v>
-      </c>
-      <c r="B12" s="3">
-        <v>8.5586180972958781E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>1997</v>
-      </c>
-      <c r="B13" s="3">
-        <v>0.13646101577698233</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>1998</v>
-      </c>
-      <c r="B14" s="3">
-        <v>0.12375668034877796</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>1999</v>
-      </c>
-      <c r="B15" s="3">
-        <v>0.14456105557563292</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A16">
-        <v>2000</v>
-      </c>
-      <c r="B16" s="3">
-        <v>1.2753813678981984E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17">
-        <v>2001</v>
-      </c>
-      <c r="B17" s="3">
-        <v>-2.1653766849825229E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18">
-        <v>2002</v>
-      </c>
-      <c r="B18" s="3">
-        <v>-3.0859935638595126E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19">
-        <v>2003</v>
-      </c>
-      <c r="B19" s="3">
-        <v>0.13021265938759741</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20">
-        <v>2004</v>
-      </c>
-      <c r="B20" s="3">
-        <v>0.11284628713988498</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A21">
-        <v>2005</v>
-      </c>
-      <c r="B21" s="3">
-        <v>9.5700435119939753E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22">
-        <v>2006</v>
-      </c>
-      <c r="B22" s="3">
-        <v>8.3497102825924818E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23">
-        <v>2007</v>
-      </c>
-      <c r="B23" s="3">
-        <v>5.4036728450648441E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A24">
-        <v>2008</v>
-      </c>
-      <c r="B24" s="3">
-        <v>-0.16066262517109864</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25">
-        <v>2009</v>
-      </c>
-      <c r="B25" s="3">
-        <v>8.877196143526267E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A26">
-        <v>2010</v>
-      </c>
-      <c r="B26" s="3">
-        <v>5.6774110668480482E-2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A27">
-        <v>2011</v>
-      </c>
-      <c r="B27" s="3">
-        <v>-2.7392490880683962E-2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A28">
-        <v>2012</v>
-      </c>
-      <c r="B28" s="3">
-        <v>-2.2124513898473808E-2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A29">
-        <v>2013</v>
-      </c>
-      <c r="B29" s="3">
-        <v>7.5335930021486197E-2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A30">
-        <v>2014</v>
-      </c>
-      <c r="B30" s="3">
-        <v>7.9340966880817376E-2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A31">
-        <v>2015</v>
-      </c>
-      <c r="B31" s="3">
-        <v>4.2381070018058686E-2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A32">
-        <v>2016</v>
-      </c>
-      <c r="B32" s="3">
-        <v>-4.8974784087532974E-2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A33">
-        <v>2017</v>
-      </c>
-      <c r="B33" s="3">
-        <v>7.0170871889905673E-2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A34">
-        <v>2018</v>
-      </c>
-      <c r="B34" s="3">
-        <v>2.840535022977253E-2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A35">
-        <v>2019</v>
-      </c>
-      <c r="B35" s="3">
-        <v>6.3714730205470804E-3</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A36">
-        <v>2020</v>
-      </c>
-      <c r="B36" s="3">
-        <v>-7.3040697759606754E-2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A37">
-        <v>2021</v>
-      </c>
-      <c r="B37" s="3">
-        <v>4.9303785520141474E-2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A38">
-        <v>2022</v>
-      </c>
-      <c r="B38" s="3">
-        <v>4.6286405160227334E-2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF70C8B1-8A2A-4CB2-AE85-70911F99E869}">
-  <dimension ref="A1:B30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>1994</v>
-      </c>
-      <c r="B2" s="3">
-        <v>6.0198436757189541E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>1995</v>
-      </c>
-      <c r="B3" s="3">
-        <v>0.16844999999999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>1996</v>
-      </c>
-      <c r="B4" s="3">
-        <v>0.14020833333333335</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>1997</v>
-      </c>
-      <c r="B5" s="3">
-        <v>0.13783333333333334</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>1998</v>
-      </c>
-      <c r="B6" s="3">
-        <v>0.13462499999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>1999</v>
-      </c>
-      <c r="B7" s="3">
-        <v>0.12176666666666668</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>2000</v>
-      </c>
-      <c r="B8" s="3">
-        <v>0.11730833333333335</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>2001</v>
-      </c>
-      <c r="B9" s="3">
-        <v>0.11916666666666666</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>2002</v>
-      </c>
-      <c r="B10" s="3">
-        <v>0.10499166666666665</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>2003</v>
-      </c>
-      <c r="B11" s="3">
-        <v>8.4600000000000009E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>2004</v>
-      </c>
-      <c r="B12" s="3">
-        <v>8.0033333333333359E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>2005</v>
-      </c>
-      <c r="B13" s="3">
-        <v>7.3700000000000002E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>2006</v>
-      </c>
-      <c r="B14" s="3">
-        <v>7.1808333333333349E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>2007</v>
-      </c>
-      <c r="B15" s="3">
-        <v>7.6283333333333328E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A16">
-        <v>2008</v>
-      </c>
-      <c r="B16" s="3">
-        <v>9.0599999999999972E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17">
-        <v>2009</v>
-      </c>
-      <c r="B17" s="3">
-        <v>0.10090833333333332</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18">
-        <v>2010</v>
-      </c>
-      <c r="B18" s="3">
-        <v>9.2591666666666669E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19">
-        <v>2011</v>
-      </c>
-      <c r="B19" s="3">
-        <v>8.7499999999999981E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20">
-        <v>2012</v>
-      </c>
-      <c r="B20" s="3">
-        <v>7.4383333333333329E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A21">
-        <v>2013</v>
-      </c>
-      <c r="B21" s="3">
-        <v>6.0299999999999999E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22">
-        <v>2014</v>
-      </c>
-      <c r="B22" s="3">
-        <v>4.9799999999999997E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23">
-        <v>2015</v>
-      </c>
-      <c r="B23" s="3">
-        <v>4.331666666666667E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A24">
-        <v>2016</v>
-      </c>
-      <c r="B24" s="3">
-        <v>3.9683333333333334E-2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25">
-        <v>2017</v>
-      </c>
-      <c r="B25" s="3">
-        <v>3.7991666666666667E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A26">
-        <v>2018</v>
-      </c>
-      <c r="B26" s="3">
-        <v>3.7691666666666665E-2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A27">
-        <v>2019</v>
-      </c>
-      <c r="B27" s="3">
-        <v>3.6141666666666662E-2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A28">
-        <v>2020</v>
-      </c>
-      <c r="B28" s="3">
-        <v>3.5466666666666667E-2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A29">
-        <v>2021</v>
-      </c>
-      <c r="B29" s="3">
-        <v>3.8266666666666664E-2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A30">
-        <v>2022</v>
-      </c>
-      <c r="B30" s="3">
-        <v>6.0198436757189541E-2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE5D1202-306C-4A3E-BE31-47D9872C9300}">
-  <dimension ref="A1:B30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>1994</v>
-      </c>
-      <c r="B2" s="3">
-        <v>0.15704228576200643</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>1995</v>
-      </c>
-      <c r="B3" s="3">
-        <v>0.22755833333333339</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>1996</v>
-      </c>
-      <c r="B4" s="3">
-        <v>0.22240833333333332</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>1997</v>
-      </c>
-      <c r="B5" s="3">
-        <v>0.22367499999999996</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>1998</v>
-      </c>
-      <c r="B6" s="3">
-        <v>0.21951666666666669</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>1999</v>
-      </c>
-      <c r="B7" s="3">
-        <v>0.19584999999999997</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>2000</v>
-      </c>
-      <c r="B8" s="3">
-        <v>0.18845833333333334</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>2001</v>
-      </c>
-      <c r="B9" s="3">
-        <v>0.17802499999999999</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>2002</v>
-      </c>
-      <c r="B10" s="3">
-        <v>0.15925000000000003</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>2003</v>
-      </c>
-      <c r="B11" s="3">
-        <v>0.15108333333333335</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>2004</v>
-      </c>
-      <c r="B12" s="3">
-        <v>0.1561916666666667</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>2005</v>
-      </c>
-      <c r="B13" s="3">
-        <v>0.16120833333333334</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>2006</v>
-      </c>
-      <c r="B14" s="3">
-        <v>0.16125833333333334</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>2007</v>
-      </c>
-      <c r="B15" s="3">
-        <v>0.15259999999999999</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A16">
-        <v>2008</v>
-      </c>
-      <c r="B16" s="3">
-        <v>0.15983333333333333</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17">
-        <v>2009</v>
-      </c>
-      <c r="B17" s="3">
-        <v>0.16043333333333332</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18">
-        <v>2010</v>
-      </c>
-      <c r="B18" s="3">
-        <v>0.16666666666666669</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19">
-        <v>2011</v>
-      </c>
-      <c r="B19" s="3">
-        <v>0.16936666666666664</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20">
-        <v>2012</v>
-      </c>
-      <c r="B20" s="3">
-        <v>0.17374999999999996</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A21">
-        <v>2013</v>
-      </c>
-      <c r="B21" s="3">
-        <v>0.17915</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22">
-        <v>2014</v>
-      </c>
-      <c r="B22" s="3">
-        <v>0.17576666666666668</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23">
-        <v>2015</v>
-      </c>
-      <c r="B23" s="3">
-        <v>0.17913333333333334</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A24">
-        <v>2016</v>
-      </c>
-      <c r="B24" s="3">
-        <v>0.17950833333333335</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25">
-        <v>2017</v>
-      </c>
-      <c r="B25" s="3">
-        <v>0.17944166666666667</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A26">
-        <v>2018</v>
-      </c>
-      <c r="B26" s="3">
-        <v>0.18666666666666665</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A27">
-        <v>2019</v>
-      </c>
-      <c r="B27" s="3">
-        <v>0.20248333333333332</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A28">
-        <v>2020</v>
-      </c>
-      <c r="B28" s="3">
-        <v>0.20790000000000003</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A29">
-        <v>2021</v>
-      </c>
-      <c r="B29" s="3">
-        <v>0.21439999999999998</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A30">
-        <v>2022</v>
-      </c>
-      <c r="B30" s="3">
-        <v>0.15704228576200643</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4C9E94E-195D-449C-95FA-8827E1CD938F}">
-  <dimension ref="A1:B14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>2010</v>
-      </c>
-      <c r="B2">
-        <v>9.0451221008231997</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>2011</v>
-      </c>
-      <c r="B3" s="7">
-        <v>9.1220556745181991</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>2012</v>
-      </c>
-      <c r="B4" s="7">
-        <v>8.9177939646201878</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>2013</v>
-      </c>
-      <c r="B5" s="7">
-        <v>8.7106598984771573</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>2014</v>
-      </c>
-      <c r="B6" s="7">
-        <v>8.58</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>2015</v>
-      </c>
-      <c r="B7" s="7">
-        <v>8.7899999999999991</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>2016</v>
-      </c>
-      <c r="B8" s="7">
-        <v>9.1360476663356494</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>2017</v>
-      </c>
-      <c r="B9" s="7">
-        <v>9.2263056092843314</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>2018</v>
-      </c>
-      <c r="B10" s="7">
-        <v>9.3767705382436262</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>2019</v>
-      </c>
-      <c r="B11" s="7">
-        <v>9.6103896103896105</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>2020</v>
-      </c>
-      <c r="B12" s="7">
-        <v>9.9724011039558409</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>2021</v>
-      </c>
-      <c r="B13" s="7">
-        <v>9.9283154121863806</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>2022</v>
-      </c>
-      <c r="B14" s="7">
-        <v>10.012761014679809</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E8E4EE1-1BD6-4E11-9F6E-85D51F484400}">
   <dimension ref="A1:BG120"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -12158,7 +12691,609 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB137BA4-4035-472D-AA2B-29C110ABC52B}">
+  <dimension ref="A1:B74"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1988</v>
+      </c>
+      <c r="B2">
+        <v>49.6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1989</v>
+      </c>
+      <c r="B3">
+        <v>52.2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>1990</v>
+      </c>
+      <c r="B4">
+        <v>55.9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>1991</v>
+      </c>
+      <c r="B5">
+        <v>60.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>1992</v>
+      </c>
+      <c r="B6">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>1993</v>
+      </c>
+      <c r="B7">
+        <v>64.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>1994</v>
+      </c>
+      <c r="B8">
+        <v>65.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>1995</v>
+      </c>
+      <c r="B9">
+        <v>67.2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>1996</v>
+      </c>
+      <c r="B10">
+        <v>68.8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>1997</v>
+      </c>
+      <c r="B11">
+        <v>70.099999999999994</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>1998</v>
+      </c>
+      <c r="B12">
+        <v>71.2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>1999</v>
+      </c>
+      <c r="B13">
+        <v>72.099999999999994</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>2000</v>
+      </c>
+      <c r="B14">
+        <v>72.7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>2001</v>
+      </c>
+      <c r="B15">
+        <v>73.599999999999994</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>2002</v>
+      </c>
+      <c r="B16">
+        <v>74.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>2003</v>
+      </c>
+      <c r="B17">
+        <v>75.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>2004</v>
+      </c>
+      <c r="B18">
+        <v>76.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>2005</v>
+      </c>
+      <c r="B19">
+        <v>78.099999999999994</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>2006</v>
+      </c>
+      <c r="B20">
+        <v>79.900000000000006</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>2007</v>
+      </c>
+      <c r="B21">
+        <v>81.8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>2008</v>
+      </c>
+      <c r="B22">
+        <v>84.7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>2009</v>
+      </c>
+      <c r="B23">
+        <v>86.6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>2010</v>
+      </c>
+      <c r="B24">
+        <v>89.4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>2011</v>
+      </c>
+      <c r="B25">
+        <v>93.4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>2012</v>
+      </c>
+      <c r="B26">
+        <v>96.1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>2013</v>
+      </c>
+      <c r="B27">
+        <v>98.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>2014</v>
+      </c>
+      <c r="B28">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>2015</v>
+      </c>
+      <c r="B29">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>2016</v>
+      </c>
+      <c r="B30">
+        <v>100.7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>2017</v>
+      </c>
+      <c r="B31">
+        <v>103.4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>2018</v>
+      </c>
+      <c r="B32">
+        <v>105.9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>2019</v>
+      </c>
+      <c r="B33">
+        <v>107.8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>2020</v>
+      </c>
+      <c r="B34">
+        <v>108.7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>2021</v>
+      </c>
+      <c r="B35">
+        <v>108.7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>2022</v>
+      </c>
+      <c r="B36">
+        <v>108.7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>2023</v>
+      </c>
+      <c r="B37">
+        <v>108.7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>2024</v>
+      </c>
+      <c r="B38">
+        <v>108.7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>2025</v>
+      </c>
+      <c r="B39">
+        <v>108.7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>2026</v>
+      </c>
+      <c r="B40">
+        <v>108.7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>2027</v>
+      </c>
+      <c r="B41">
+        <v>108.7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>2028</v>
+      </c>
+      <c r="B42">
+        <v>108.7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>2029</v>
+      </c>
+      <c r="B43">
+        <v>108.7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>2030</v>
+      </c>
+      <c r="B44">
+        <v>108.7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>2031</v>
+      </c>
+      <c r="B45">
+        <v>108.7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>2032</v>
+      </c>
+      <c r="B46">
+        <v>108.7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>2033</v>
+      </c>
+      <c r="B47">
+        <v>108.7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A48">
+        <v>2034</v>
+      </c>
+      <c r="B48">
+        <v>108.7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>2035</v>
+      </c>
+      <c r="B49">
+        <v>108.7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <v>2036</v>
+      </c>
+      <c r="B50">
+        <v>108.7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A51">
+        <v>2037</v>
+      </c>
+      <c r="B51">
+        <v>108.7</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A52">
+        <v>2038</v>
+      </c>
+      <c r="B52">
+        <v>108.7</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A53">
+        <v>2039</v>
+      </c>
+      <c r="B53">
+        <v>108.7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A54">
+        <v>2040</v>
+      </c>
+      <c r="B54">
+        <v>108.7</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A55">
+        <v>2041</v>
+      </c>
+      <c r="B55">
+        <v>108.7</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A56">
+        <v>2042</v>
+      </c>
+      <c r="B56">
+        <v>108.7</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A57">
+        <v>2043</v>
+      </c>
+      <c r="B57">
+        <v>108.7</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A58">
+        <v>2044</v>
+      </c>
+      <c r="B58">
+        <v>108.7</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A59">
+        <v>2045</v>
+      </c>
+      <c r="B59">
+        <v>108.7</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A60">
+        <v>2046</v>
+      </c>
+      <c r="B60">
+        <v>108.7</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A61">
+        <v>2047</v>
+      </c>
+      <c r="B61">
+        <v>108.7</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A62">
+        <v>2048</v>
+      </c>
+      <c r="B62">
+        <v>108.7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A63">
+        <v>2049</v>
+      </c>
+      <c r="B63">
+        <v>108.7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A64">
+        <v>2050</v>
+      </c>
+      <c r="B64">
+        <v>108.7</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A65">
+        <v>2051</v>
+      </c>
+      <c r="B65">
+        <v>108.7</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A66">
+        <v>2052</v>
+      </c>
+      <c r="B66">
+        <v>108.7</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A67">
+        <v>2053</v>
+      </c>
+      <c r="B67">
+        <v>108.7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A68">
+        <v>2054</v>
+      </c>
+      <c r="B68">
+        <v>108.7</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A69">
+        <v>2055</v>
+      </c>
+      <c r="B69">
+        <v>108.7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A70">
+        <v>2056</v>
+      </c>
+      <c r="B70">
+        <v>108.7</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A71">
+        <v>2057</v>
+      </c>
+      <c r="B71">
+        <v>108.7</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A72">
+        <v>2058</v>
+      </c>
+      <c r="B72">
+        <v>108.7</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A73">
+        <v>2059</v>
+      </c>
+      <c r="B73">
+        <v>108.7</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A74">
+        <v>2060</v>
+      </c>
+      <c r="B74">
+        <v>108.7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6878765F-1722-41F9-8BBC-D6A1331F5260}">
   <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -12424,609 +13559,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB137BA4-4035-472D-AA2B-29C110ABC52B}">
-  <dimension ref="A1:B74"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>1988</v>
-      </c>
-      <c r="B2">
-        <v>49.6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>1989</v>
-      </c>
-      <c r="B3">
-        <v>52.2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>1990</v>
-      </c>
-      <c r="B4">
-        <v>55.9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>1991</v>
-      </c>
-      <c r="B5">
-        <v>60.1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>1992</v>
-      </c>
-      <c r="B6">
-        <v>62.6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>1993</v>
-      </c>
-      <c r="B7">
-        <v>64.2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>1994</v>
-      </c>
-      <c r="B8">
-        <v>65.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>1995</v>
-      </c>
-      <c r="B9">
-        <v>67.2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>1996</v>
-      </c>
-      <c r="B10">
-        <v>68.8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>1997</v>
-      </c>
-      <c r="B11">
-        <v>70.099999999999994</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>1998</v>
-      </c>
-      <c r="B12">
-        <v>71.2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>1999</v>
-      </c>
-      <c r="B13">
-        <v>72.099999999999994</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>2000</v>
-      </c>
-      <c r="B14">
-        <v>72.7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>2001</v>
-      </c>
-      <c r="B15">
-        <v>73.599999999999994</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A16">
-        <v>2002</v>
-      </c>
-      <c r="B16">
-        <v>74.5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17">
-        <v>2003</v>
-      </c>
-      <c r="B17">
-        <v>75.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18">
-        <v>2004</v>
-      </c>
-      <c r="B18">
-        <v>76.5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19">
-        <v>2005</v>
-      </c>
-      <c r="B19">
-        <v>78.099999999999994</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20">
-        <v>2006</v>
-      </c>
-      <c r="B20">
-        <v>79.900000000000006</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A21">
-        <v>2007</v>
-      </c>
-      <c r="B21">
-        <v>81.8</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22">
-        <v>2008</v>
-      </c>
-      <c r="B22">
-        <v>84.7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23">
-        <v>2009</v>
-      </c>
-      <c r="B23">
-        <v>86.6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A24">
-        <v>2010</v>
-      </c>
-      <c r="B24">
-        <v>89.4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25">
-        <v>2011</v>
-      </c>
-      <c r="B25">
-        <v>93.4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A26">
-        <v>2012</v>
-      </c>
-      <c r="B26">
-        <v>96.1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A27">
-        <v>2013</v>
-      </c>
-      <c r="B27">
-        <v>98.5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A28">
-        <v>2014</v>
-      </c>
-      <c r="B28">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A29">
-        <v>2015</v>
-      </c>
-      <c r="B29">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A30">
-        <v>2016</v>
-      </c>
-      <c r="B30">
-        <v>100.7</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A31">
-        <v>2017</v>
-      </c>
-      <c r="B31">
-        <v>103.4</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A32">
-        <v>2018</v>
-      </c>
-      <c r="B32">
-        <v>105.9</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A33">
-        <v>2019</v>
-      </c>
-      <c r="B33">
-        <v>107.8</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A34">
-        <v>2020</v>
-      </c>
-      <c r="B34">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A35">
-        <v>2021</v>
-      </c>
-      <c r="B35">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A36">
-        <v>2022</v>
-      </c>
-      <c r="B36">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A37">
-        <v>2023</v>
-      </c>
-      <c r="B37">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A38">
-        <v>2024</v>
-      </c>
-      <c r="B38">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A39">
-        <v>2025</v>
-      </c>
-      <c r="B39">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A40">
-        <v>2026</v>
-      </c>
-      <c r="B40">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A41">
-        <v>2027</v>
-      </c>
-      <c r="B41">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A42">
-        <v>2028</v>
-      </c>
-      <c r="B42">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A43">
-        <v>2029</v>
-      </c>
-      <c r="B43">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A44">
-        <v>2030</v>
-      </c>
-      <c r="B44">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A45">
-        <v>2031</v>
-      </c>
-      <c r="B45">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A46">
-        <v>2032</v>
-      </c>
-      <c r="B46">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A47">
-        <v>2033</v>
-      </c>
-      <c r="B47">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A48">
-        <v>2034</v>
-      </c>
-      <c r="B48">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A49">
-        <v>2035</v>
-      </c>
-      <c r="B49">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A50">
-        <v>2036</v>
-      </c>
-      <c r="B50">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A51">
-        <v>2037</v>
-      </c>
-      <c r="B51">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A52">
-        <v>2038</v>
-      </c>
-      <c r="B52">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A53">
-        <v>2039</v>
-      </c>
-      <c r="B53">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A54">
-        <v>2040</v>
-      </c>
-      <c r="B54">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A55">
-        <v>2041</v>
-      </c>
-      <c r="B55">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A56">
-        <v>2042</v>
-      </c>
-      <c r="B56">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A57">
-        <v>2043</v>
-      </c>
-      <c r="B57">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A58">
-        <v>2044</v>
-      </c>
-      <c r="B58">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A59">
-        <v>2045</v>
-      </c>
-      <c r="B59">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A60">
-        <v>2046</v>
-      </c>
-      <c r="B60">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A61">
-        <v>2047</v>
-      </c>
-      <c r="B61">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A62">
-        <v>2048</v>
-      </c>
-      <c r="B62">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A63">
-        <v>2049</v>
-      </c>
-      <c r="B63">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A64">
-        <v>2050</v>
-      </c>
-      <c r="B64">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A65">
-        <v>2051</v>
-      </c>
-      <c r="B65">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A66">
-        <v>2052</v>
-      </c>
-      <c r="B66">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A67">
-        <v>2053</v>
-      </c>
-      <c r="B67">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A68">
-        <v>2054</v>
-      </c>
-      <c r="B68">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A69">
-        <v>2055</v>
-      </c>
-      <c r="B69">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A70">
-        <v>2056</v>
-      </c>
-      <c r="B70">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A71">
-        <v>2057</v>
-      </c>
-      <c r="B71">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A72">
-        <v>2058</v>
-      </c>
-      <c r="B72">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A73">
-        <v>2059</v>
-      </c>
-      <c r="B73">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A74">
-        <v>2060</v>
-      </c>
-      <c r="B74">
-        <v>108.7</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D18E90C-6D91-4744-9FCB-A05B59544AB8}">
   <dimension ref="A1:F62"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -13904,7 +14437,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B00E6D01-ED8F-4196-BCE1-0F54EC92EC33}">
   <dimension ref="A1:F62"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -14782,7 +15315,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{478B000C-A767-DB46-ACA8-B478450706FE}">
   <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -15048,7 +15581,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6CAAB06-EE87-2546-B8E9-00E7C956FA2A}">
   <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -15314,7 +15847,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28B9AB12-0373-1641-9F50-FFC861B8E8F8}">
   <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -15580,7 +16113,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81CF35D1-EA41-4B4F-8246-ED1C76F988F0}">
   <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -15844,270 +16377,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74397DC0-DE0F-5146-BEAF-59D2E8FCDE98}">
-  <dimension ref="A1:B32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>2010</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>2011</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>2012</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>2013</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>2014</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>2015</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>2016</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>2017</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>2018</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>2019</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>2020</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>2021</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>2022</v>
-      </c>
-      <c r="B14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>2023</v>
-      </c>
-      <c r="B15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A16">
-        <v>2024</v>
-      </c>
-      <c r="B16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17">
-        <v>2025</v>
-      </c>
-      <c r="B17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18">
-        <v>2026</v>
-      </c>
-      <c r="B18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19">
-        <v>2027</v>
-      </c>
-      <c r="B19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20">
-        <v>2028</v>
-      </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A21">
-        <v>2029</v>
-      </c>
-      <c r="B21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22">
-        <v>2030</v>
-      </c>
-      <c r="B22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23">
-        <v>2031</v>
-      </c>
-      <c r="B23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A24">
-        <v>2032</v>
-      </c>
-      <c r="B24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25">
-        <v>2033</v>
-      </c>
-      <c r="B25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A26">
-        <v>2034</v>
-      </c>
-      <c r="B26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A27">
-        <v>2035</v>
-      </c>
-      <c r="B27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A28">
-        <v>2036</v>
-      </c>
-      <c r="B28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A29">
-        <v>2037</v>
-      </c>
-      <c r="B29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A30">
-        <v>2038</v>
-      </c>
-      <c r="B30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A31">
-        <v>2039</v>
-      </c>
-      <c r="B31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A32">
-        <v>2040</v>
-      </c>
-      <c r="B32">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/input/time_series_factor.xlsx
+++ b/input/time_series_factor.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pineapple/IdeaProjects/SimPathsUK_refactored/input/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Sonnewald/GitHub/SimPaths/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{598F5936-5705-C244-984C-D3D690C829C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E917B038-602C-1C41-9617-5895C357CAB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23260" yWindow="2060" windowWidth="25440" windowHeight="15400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="UK_students_adjustment" sheetId="24" r:id="rId1"/>
-    <sheet name="Info" sheetId="1" r:id="rId2"/>
+    <sheet name="Info" sheetId="1" r:id="rId1"/>
+    <sheet name="UK_students_adjustment" sheetId="24" r:id="rId2"/>
     <sheet name="UK_care_adjustment" sheetId="14" r:id="rId3"/>
     <sheet name="UK_cohabitation_adjustment" sheetId="15" r:id="rId4"/>
     <sheet name="UK_fertility_adjustment" sheetId="19" r:id="rId5"/>
@@ -33,7 +33,6 @@
     <sheet name="UK_debt_cost_hi" sheetId="11" r:id="rId18"/>
     <sheet name="UK_carer_hourly_wage" sheetId="13" r:id="rId19"/>
     <sheet name="UK raw data" sheetId="12" r:id="rId20"/>
-    <sheet name="IT" sheetId="4" r:id="rId21"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -56,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="56">
   <si>
     <t>Year</t>
   </si>
@@ -1069,264 +1068,52 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A56B41E9-3C32-2C44-B860-85F5893FC338}">
-  <dimension ref="A1:B32"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="12.5" customWidth="1"/>
+    <col min="2" max="2" width="10.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>2010</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
+      <c r="A2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>2011</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
+      <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>2012</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>2013</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
+      <c r="A4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>2014</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>2015</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>2016</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>2017</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>2018</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>2019</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>2020</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>2021</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>2022</v>
-      </c>
-      <c r="B14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>2023</v>
-      </c>
-      <c r="B15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A16">
-        <v>2024</v>
-      </c>
-      <c r="B16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17">
-        <v>2025</v>
-      </c>
-      <c r="B17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18">
-        <v>2026</v>
-      </c>
-      <c r="B18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19">
-        <v>2027</v>
-      </c>
-      <c r="B19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20">
-        <v>2028</v>
-      </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A21">
-        <v>2029</v>
-      </c>
-      <c r="B21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22">
-        <v>2030</v>
-      </c>
-      <c r="B22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23">
-        <v>2031</v>
-      </c>
-      <c r="B23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A24">
-        <v>2032</v>
-      </c>
-      <c r="B24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25">
-        <v>2033</v>
-      </c>
-      <c r="B25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A26">
-        <v>2034</v>
-      </c>
-      <c r="B26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A27">
-        <v>2035</v>
-      </c>
-      <c r="B27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A28">
-        <v>2036</v>
-      </c>
-      <c r="B28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A29">
-        <v>2037</v>
-      </c>
-      <c r="B29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A30">
-        <v>2038</v>
-      </c>
-      <c r="B30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A31">
-        <v>2039</v>
-      </c>
-      <c r="B31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A32">
-        <v>2040</v>
-      </c>
-      <c r="B32">
-        <v>0</v>
+      <c r="A6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -4604,52 +4391,264 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A56B41E9-3C32-2C44-B860-85F5893FC338}">
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="12.5" customWidth="1"/>
-    <col min="2" max="2" width="10.6640625" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>35</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B2" t="s">
-        <v>29</v>
+      <c r="A2">
+        <v>2010</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" t="s">
-        <v>30</v>
+      <c r="A3">
+        <v>2011</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" t="s">
-        <v>30</v>
+      <c r="A4">
+        <v>2012</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>2013</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B6" t="s">
-        <v>44</v>
+      <c r="A6">
+        <v>2014</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>2015</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>2016</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>2017</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>2018</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>2019</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>2020</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>2021</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>2022</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>2023</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>2024</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>2025</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>2026</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>2027</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>2028</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>2029</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>2030</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>2031</v>
+      </c>
+      <c r="B23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>2032</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>2033</v>
+      </c>
+      <c r="B25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>2034</v>
+      </c>
+      <c r="B26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>2035</v>
+      </c>
+      <c r="B27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>2036</v>
+      </c>
+      <c r="B28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>2037</v>
+      </c>
+      <c r="B29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>2038</v>
+      </c>
+      <c r="B30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>2039</v>
+      </c>
+      <c r="B31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>2040</v>
+      </c>
+      <c r="B32">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -12691,608 +12690,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB137BA4-4035-472D-AA2B-29C110ABC52B}">
-  <dimension ref="A1:B74"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>1988</v>
-      </c>
-      <c r="B2">
-        <v>49.6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>1989</v>
-      </c>
-      <c r="B3">
-        <v>52.2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>1990</v>
-      </c>
-      <c r="B4">
-        <v>55.9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>1991</v>
-      </c>
-      <c r="B5">
-        <v>60.1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>1992</v>
-      </c>
-      <c r="B6">
-        <v>62.6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>1993</v>
-      </c>
-      <c r="B7">
-        <v>64.2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>1994</v>
-      </c>
-      <c r="B8">
-        <v>65.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>1995</v>
-      </c>
-      <c r="B9">
-        <v>67.2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>1996</v>
-      </c>
-      <c r="B10">
-        <v>68.8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>1997</v>
-      </c>
-      <c r="B11">
-        <v>70.099999999999994</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>1998</v>
-      </c>
-      <c r="B12">
-        <v>71.2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>1999</v>
-      </c>
-      <c r="B13">
-        <v>72.099999999999994</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>2000</v>
-      </c>
-      <c r="B14">
-        <v>72.7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>2001</v>
-      </c>
-      <c r="B15">
-        <v>73.599999999999994</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A16">
-        <v>2002</v>
-      </c>
-      <c r="B16">
-        <v>74.5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17">
-        <v>2003</v>
-      </c>
-      <c r="B17">
-        <v>75.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18">
-        <v>2004</v>
-      </c>
-      <c r="B18">
-        <v>76.5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19">
-        <v>2005</v>
-      </c>
-      <c r="B19">
-        <v>78.099999999999994</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20">
-        <v>2006</v>
-      </c>
-      <c r="B20">
-        <v>79.900000000000006</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A21">
-        <v>2007</v>
-      </c>
-      <c r="B21">
-        <v>81.8</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22">
-        <v>2008</v>
-      </c>
-      <c r="B22">
-        <v>84.7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23">
-        <v>2009</v>
-      </c>
-      <c r="B23">
-        <v>86.6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A24">
-        <v>2010</v>
-      </c>
-      <c r="B24">
-        <v>89.4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25">
-        <v>2011</v>
-      </c>
-      <c r="B25">
-        <v>93.4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A26">
-        <v>2012</v>
-      </c>
-      <c r="B26">
-        <v>96.1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A27">
-        <v>2013</v>
-      </c>
-      <c r="B27">
-        <v>98.5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A28">
-        <v>2014</v>
-      </c>
-      <c r="B28">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A29">
-        <v>2015</v>
-      </c>
-      <c r="B29">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A30">
-        <v>2016</v>
-      </c>
-      <c r="B30">
-        <v>100.7</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A31">
-        <v>2017</v>
-      </c>
-      <c r="B31">
-        <v>103.4</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A32">
-        <v>2018</v>
-      </c>
-      <c r="B32">
-        <v>105.9</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A33">
-        <v>2019</v>
-      </c>
-      <c r="B33">
-        <v>107.8</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A34">
-        <v>2020</v>
-      </c>
-      <c r="B34">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A35">
-        <v>2021</v>
-      </c>
-      <c r="B35">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A36">
-        <v>2022</v>
-      </c>
-      <c r="B36">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A37">
-        <v>2023</v>
-      </c>
-      <c r="B37">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A38">
-        <v>2024</v>
-      </c>
-      <c r="B38">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A39">
-        <v>2025</v>
-      </c>
-      <c r="B39">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A40">
-        <v>2026</v>
-      </c>
-      <c r="B40">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A41">
-        <v>2027</v>
-      </c>
-      <c r="B41">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A42">
-        <v>2028</v>
-      </c>
-      <c r="B42">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A43">
-        <v>2029</v>
-      </c>
-      <c r="B43">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A44">
-        <v>2030</v>
-      </c>
-      <c r="B44">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A45">
-        <v>2031</v>
-      </c>
-      <c r="B45">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A46">
-        <v>2032</v>
-      </c>
-      <c r="B46">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A47">
-        <v>2033</v>
-      </c>
-      <c r="B47">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A48">
-        <v>2034</v>
-      </c>
-      <c r="B48">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A49">
-        <v>2035</v>
-      </c>
-      <c r="B49">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A50">
-        <v>2036</v>
-      </c>
-      <c r="B50">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A51">
-        <v>2037</v>
-      </c>
-      <c r="B51">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A52">
-        <v>2038</v>
-      </c>
-      <c r="B52">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A53">
-        <v>2039</v>
-      </c>
-      <c r="B53">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A54">
-        <v>2040</v>
-      </c>
-      <c r="B54">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A55">
-        <v>2041</v>
-      </c>
-      <c r="B55">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A56">
-        <v>2042</v>
-      </c>
-      <c r="B56">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A57">
-        <v>2043</v>
-      </c>
-      <c r="B57">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A58">
-        <v>2044</v>
-      </c>
-      <c r="B58">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A59">
-        <v>2045</v>
-      </c>
-      <c r="B59">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A60">
-        <v>2046</v>
-      </c>
-      <c r="B60">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A61">
-        <v>2047</v>
-      </c>
-      <c r="B61">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A62">
-        <v>2048</v>
-      </c>
-      <c r="B62">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A63">
-        <v>2049</v>
-      </c>
-      <c r="B63">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A64">
-        <v>2050</v>
-      </c>
-      <c r="B64">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A65">
-        <v>2051</v>
-      </c>
-      <c r="B65">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A66">
-        <v>2052</v>
-      </c>
-      <c r="B66">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A67">
-        <v>2053</v>
-      </c>
-      <c r="B67">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A68">
-        <v>2054</v>
-      </c>
-      <c r="B68">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A69">
-        <v>2055</v>
-      </c>
-      <c r="B69">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A70">
-        <v>2056</v>
-      </c>
-      <c r="B70">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A71">
-        <v>2057</v>
-      </c>
-      <c r="B71">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A72">
-        <v>2058</v>
-      </c>
-      <c r="B72">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A73">
-        <v>2059</v>
-      </c>
-      <c r="B73">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A74">
-        <v>2060</v>
-      </c>
-      <c r="B74">
-        <v>108.7</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6878765F-1722-41F9-8BBC-D6A1331F5260}">
   <dimension ref="A1:B32"/>
